--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -4,19 +4,19 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Stack" sheetId="1" r:id="rId1"/>
     <sheet name="Interview Questions" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="interview schdule" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>NextJS</t>
   </si>
@@ -76,13 +76,47 @@
   </si>
   <si>
     <t>https://javatechonline.com/elasticsearch-with-spring-boot-spring-data-elasticsearch-crud-examples/</t>
+  </si>
+  <si>
+    <t>https://teams.microsoft.com/light-meetings/launch?context=%7B%22Tid%22%3A%22111483dd-9e03-417d-bd28-5866c2dddaa5%22%2C%22Oid%22%3A%22bb3d7561-ba4a-4aca-b493-be9c0bf07d02%22%7D&amp;anon=true&amp;lightExperience=true&amp;correlationId=24cf8bdb-ddf3-49af-82e4-00405fcb1c1f&amp;agent=web&amp;version=25101311601&amp;coords=eyJjb252ZXJzYXRpb25JZCI6IjE5Om1lZXRpbmdfT0dGaFptRXlaVFV0TlRCbFpTMDBOMkkwTFdFeU5HUXRZamhsWmpRellXTmlZakkzQHRocmVhZC52MiIsInRlbmFudElkIjoiMTExNDgzZGQtOWUwMy00MTdkLWJkMjgtNTg2NmMyZGRkYWE1Iiwib3JnYW5pemVySWQiOiJiYjNkNzU2MS1iYTRhLTRhY2EtYjQ5My1iZTljMGJmMDdkMDIiLCJtZXNzYWdlSWQiOiIwIn0%3D&amp;deeplinkId=1c009563-9659-4583-a4be-dff2b4b69114</t>
+  </si>
+  <si>
+    <t>Mobily</t>
+  </si>
+  <si>
+    <r>
+      <t>Meeting ID: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF242424"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>397 773 642 094 5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Passcode: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF242424"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>q88Uk659</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -97,6 +131,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF616161"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF242424"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -144,13 +190,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -591,9 +639,37 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A3:A8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="99" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="17" x14ac:dyDescent="0.5">
+      <c r="A6" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="17" x14ac:dyDescent="0.5">
+      <c r="A8" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" display="https://teams.microsoft.com/light-meetings/launch?context=%7B%22Tid%22%3A%22111483dd-9e03-417d-bd28-5866c2dddaa5%22%2C%22Oid%22%3A%22bb3d7561-ba4a-4aca-b493-be9c0bf07d02%22%7D&amp;anon=true&amp;lightExperience=true&amp;correlationId=24cf8bdb-ddf3-49af-82e4-00405fcb1c"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -4,19 +4,17 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Stack" sheetId="1" r:id="rId1"/>
-    <sheet name="Interview Questions" sheetId="2" r:id="rId2"/>
-    <sheet name="interview schdule" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>NextJS</t>
   </si>
@@ -45,9 +43,6 @@
     <t>Project explanation.</t>
   </si>
   <si>
-    <t>how to fetch data from two table using jpa.</t>
-  </si>
-  <si>
     <t>CI CD Pipeline</t>
   </si>
   <si>
@@ -60,63 +55,26 @@
     <t>Pyton</t>
   </si>
   <si>
-    <t>https://medium.com/@dulanjayasandaruwan1998/redis-spring-boot-a-powerful-combination-for-high-performance-applications-c0285efc0b25</t>
-  </si>
-  <si>
-    <t>Spring Data Redis:</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=oRGqCz8OLcM</t>
-  </si>
-  <si>
-    <t>spring data elasticsearch example</t>
-  </si>
-  <si>
-    <t>https://medium.com/shoutloudz/elastic-search-with-spring-boot-357bb0f57972</t>
-  </si>
-  <si>
-    <t>https://javatechonline.com/elasticsearch-with-spring-boot-spring-data-elasticsearch-crud-examples/</t>
-  </si>
-  <si>
-    <t>https://teams.microsoft.com/light-meetings/launch?context=%7B%22Tid%22%3A%22111483dd-9e03-417d-bd28-5866c2dddaa5%22%2C%22Oid%22%3A%22bb3d7561-ba4a-4aca-b493-be9c0bf07d02%22%7D&amp;anon=true&amp;lightExperience=true&amp;correlationId=24cf8bdb-ddf3-49af-82e4-00405fcb1c1f&amp;agent=web&amp;version=25101311601&amp;coords=eyJjb252ZXJzYXRpb25JZCI6IjE5Om1lZXRpbmdfT0dGaFptRXlaVFV0TlRCbFpTMDBOMkkwTFdFeU5HUXRZamhsWmpRellXTmlZakkzQHRocmVhZC52MiIsInRlbmFudElkIjoiMTExNDgzZGQtOWUwMy00MTdkLWJkMjgtNTg2NmMyZGRkYWE1Iiwib3JnYW5pemVySWQiOiJiYjNkNzU2MS1iYTRhLTRhY2EtYjQ5My1iZTljMGJmMDdkMDIiLCJtZXNzYWdlSWQiOiIwIn0%3D&amp;deeplinkId=1c009563-9659-4583-a4be-dff2b4b69114</t>
-  </si>
-  <si>
-    <t>Mobily</t>
-  </si>
-  <si>
-    <r>
-      <t>Meeting ID: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF242424"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>397 773 642 094 5</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Passcode: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF242424"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>q88Uk659</t>
-    </r>
+    <t>datastructure and algorithems</t>
+  </si>
+  <si>
+    <t>https://chatgpt.com/c/6943a161-3ff0-8323-8244-5f517f818bac</t>
+  </si>
+  <si>
+    <t>Guardant Healhportal overview.</t>
+  </si>
+  <si>
+    <t>https://chatgpt.com/c/6943a318-5800-832d-a340-005e02f1f4f7</t>
+  </si>
+  <si>
+    <t>Guardant Health Portal architecutre.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,18 +89,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF616161"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF242424"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -190,15 +136,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -507,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38.90625" customWidth="1"/>
@@ -560,116 +505,58 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+    <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
+    <row r="25" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
+      <c r="D26" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="5" t="s">
-        <v>19</v>
-      </c>
+    <row r="28" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="5"/>
+    </row>
+    <row r="30" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A26" r:id="rId1"/>
-    <hyperlink ref="A29" r:id="rId2"/>
-    <hyperlink ref="A30" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="54.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:A8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="99" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="17" x14ac:dyDescent="0.5">
-      <c r="A6" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="17" x14ac:dyDescent="0.5">
-      <c r="A8" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A4" display="https://teams.microsoft.com/light-meetings/launch?context=%7B%22Tid%22%3A%22111483dd-9e03-417d-bd28-5866c2dddaa5%22%2C%22Oid%22%3A%22bb3d7561-ba4a-4aca-b493-be9c0bf07d02%22%7D&amp;anon=true&amp;lightExperience=true&amp;correlationId=24cf8bdb-ddf3-49af-82e4-00405fcb1c"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>NextJS</t>
   </si>
@@ -68,6 +68,21 @@
   </si>
   <si>
     <t>Guardant Health Portal architecutre.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/fNdMcD801XY</t>
+  </si>
+  <si>
+    <t>Magicfor kida</t>
+  </si>
+  <si>
+    <t>Core java+ Programmming on new features + DS + Design patterns + db concepts+ sql + Hibernate.</t>
+  </si>
+  <si>
+    <t>React js + typescript+java script</t>
+  </si>
+  <si>
+    <t>spring + spring boot +Microservices + kafka</t>
   </si>
 </sst>
 </file>
@@ -452,10 +467,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="38.90625" customWidth="1"/>
+    <col min="1" max="1" width="91.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -545,12 +560,34 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
     <row r="29" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
     </row>
     <row r="30" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>NextJS</t>
   </si>
@@ -83,6 +83,9 @@
   </si>
   <si>
     <t>spring + spring boot +Microservices + kafka</t>
+  </si>
+  <si>
+    <t>Jmeter.</t>
   </si>
 </sst>
 </file>
@@ -543,6 +546,11 @@
         <v>13</v>
       </c>
     </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+    </row>
     <row r="24" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>14</v>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>NextJS</t>
   </si>
@@ -86,6 +86,60 @@
   </si>
   <si>
     <t>Jmeter.</t>
+  </si>
+  <si>
+    <t>Holder class Bill Pugh Method. Correct.</t>
+  </si>
+  <si>
+    <t>Enum singleton</t>
+  </si>
+  <si>
+    <t>Edge cases using Double check locking.</t>
+  </si>
+  <si>
+    <t>readResolve method 12</t>
+  </si>
+  <si>
+    <t>what is thread safe and synchronization.</t>
+  </si>
+  <si>
+    <t>Object pooling.</t>
+  </si>
+  <si>
+    <t>how HTTTP Request header contains</t>
+  </si>
+  <si>
+    <t>saga Orchestrator - pattern</t>
+  </si>
+  <si>
+    <t>1. Strategy Pattern</t>
+  </si>
+  <si>
+    <t>2. Observer Pattern</t>
+  </si>
+  <si>
+    <t>3. Command Pattern</t>
+  </si>
+  <si>
+    <t>4. Chain of Responsibility</t>
+  </si>
+  <si>
+    <t>5. State Pattern</t>
+  </si>
+  <si>
+    <t>6. Template Method</t>
+  </si>
+  <si>
+    <t>7. Mediator Pattern</t>
+  </si>
+  <si>
+    <t>8. Iterator Pattern</t>
+  </si>
+  <si>
+    <t>9. Memento Pattern</t>
+  </si>
+  <si>
+    <t>10. Visitor Pattern</t>
   </si>
 </sst>
 </file>
@@ -470,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="91.7265625" customWidth="1"/>
@@ -597,6 +651,101 @@
         <v>22</v>
       </c>
     </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A26" r:id="rId1"/>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -4,17 +4,18 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Stack" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>NextJS</t>
   </si>
@@ -76,77 +77,80 @@
     <t>Magicfor kida</t>
   </si>
   <si>
-    <t>Core java+ Programmming on new features + DS + Design patterns + db concepts+ sql + Hibernate.</t>
-  </si>
-  <si>
-    <t>React js + typescript+java script</t>
-  </si>
-  <si>
     <t>spring + spring boot +Microservices + kafka</t>
   </si>
   <si>
     <t>Jmeter.</t>
   </si>
   <si>
-    <t>Holder class Bill Pugh Method. Correct.</t>
-  </si>
-  <si>
-    <t>Enum singleton</t>
-  </si>
-  <si>
-    <t>Edge cases using Double check locking.</t>
-  </si>
-  <si>
-    <t>readResolve method 12</t>
-  </si>
-  <si>
-    <t>what is thread safe and synchronization.</t>
-  </si>
-  <si>
-    <t>Object pooling.</t>
-  </si>
-  <si>
-    <t>how HTTTP Request header contains</t>
-  </si>
-  <si>
     <t>saga Orchestrator - pattern</t>
   </si>
   <si>
-    <t>1. Strategy Pattern</t>
-  </si>
-  <si>
-    <t>2. Observer Pattern</t>
-  </si>
-  <si>
-    <t>3. Command Pattern</t>
-  </si>
-  <si>
-    <t>4. Chain of Responsibility</t>
-  </si>
-  <si>
-    <t>5. State Pattern</t>
-  </si>
-  <si>
-    <t>6. Template Method</t>
-  </si>
-  <si>
-    <t>7. Mediator Pattern</t>
-  </si>
-  <si>
-    <t>8. Iterator Pattern</t>
-  </si>
-  <si>
-    <t>9. Memento Pattern</t>
-  </si>
-  <si>
-    <t>10. Visitor Pattern</t>
+    <t>Core java+ Programmming on new features + DS + Design patterns + DB Concepts + sql + Hibernate.</t>
+  </si>
+  <si>
+    <t>React js + typescript + java script</t>
+  </si>
+  <si>
+    <t>Does anyone offer paid, on-demand architect-level support for Java and Spring Boot microservices, covering system design, scalability, performance, and best practices?”</t>
+  </si>
+  <si>
+    <t>ChatGPT</t>
+  </si>
+  <si>
+    <t>https://www.flipkart.com/hikvision-ezviz-c6n-wifi-indoor-smart-pan-tilt-night-vision-wireless-security-camera/p/itm6a06aa8fa0745?pid=HSAGBBXSQ6ABGUCC&amp;lid=LSTHSAGBBXSQ6ABGUCCZ5YEDC&amp;marketplace=FLIPKART&amp;cmpid=content_home-security-camera_8965229628_gmc&amp;affExtParam1=YT3-43Zi0Ddj1i5R50PxbifL8-0ysWzcOjF1hLOOgzy8RaV_uLJqDDU_Bi5iLxK2IwQliCtJWt9dbfGBMcql6rtmtpy_&amp;affid=ytflipkart</t>
+  </si>
+  <si>
+    <t>https://www.flipkart.com/accutrust-smart-visual-ear-wax-cleaner-5mp-hd-camera-wifi-connectivity-electric/p/itm0315faef11f13?pid=EECHGXCWFRH6XZHA&amp;lid=LSTEECHGXCWFRH6XZHAISPLFA&amp;marketplace=FLIPKART&amp;cmpid=content_electric-ear-cleaner_8965229628_gmc&amp;affExtParam1=YT3-z2rvmWPrOgxlKmfc_aEoLuOMgI-j9wjho2LRdfrZUYxb7nMHeUixAxq1wdbLmpADGix8YWLsz2ErZwLHghUe8bs&amp;affid=ytflipkart</t>
+  </si>
+  <si>
+    <t>Print all permutations of a string in Java</t>
+  </si>
+  <si>
+    <t>BPMS</t>
+  </si>
+  <si>
+    <r>
+      <t>Share an example of how you have taken a real-world customer problem and converted it into a scalable technical framework or reusable solution.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <color rgb="FFD8372A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Summarize any complex integration project you have designed and implemented, highlighting the architecture, challenges you faced, and how you resolved them.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <color rgb="FFD8372A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <t>Interview Questions</t>
+  </si>
+  <si>
+    <t>AWS Certification.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,6 +165,20 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF282525"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFD8372A"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -208,7 +226,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -216,6 +234,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -524,10 +546,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="91.7265625" customWidth="1"/>
+    <col min="1" max="1" width="91.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -602,7 +624,12 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -638,119 +665,88 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" s="7" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A26" r:id="rId1"/>
+    <hyperlink ref="A51" r:id="rId2" display="https://www.geeksforgeeks.org/dsa/print-all-permutations-of-a-string-in-java/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="96.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8020"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="7080"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Stack" sheetId="1" r:id="rId1"/>
@@ -24,9 +24,6 @@
   </si>
   <si>
     <t>Certification</t>
-  </si>
-  <si>
-    <t>AWS Developer</t>
   </si>
   <si>
     <t>AZURE Certification</t>
@@ -144,6 +141,9 @@
   </si>
   <si>
     <t>AWS Certification.</t>
+  </si>
+  <si>
+    <t>AWS Developer (Ananth : Solution architect associate : azure developer  )</t>
   </si>
 </sst>
 </file>
@@ -547,170 +547,170 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D54"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="91.81640625" customWidth="1"/>
+    <col min="1" max="1" width="91.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="7" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="11" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
+    <row r="15" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+    <row r="16" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    <row r="18" spans="1:4" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+    <row r="20" spans="1:4" s="2" customFormat="1" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
+    <row r="21" spans="1:4" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+    <row r="22" spans="1:4" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="3" customFormat="1" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="D24" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" s="3" customFormat="1" ht="14.55" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:4" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" s="4" customFormat="1" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" s="4" customFormat="1" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A29" s="5"/>
+    </row>
+    <row r="30" spans="1:4" s="4" customFormat="1" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A30" s="5"/>
+    </row>
+    <row r="32" spans="1:4" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="5"/>
-    </row>
-    <row r="30" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="5"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="49" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+    <row r="51" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A51" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A51" s="7" t="s">
+    <row r="54" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -726,24 +726,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="96.26953125" customWidth="1"/>
+    <col min="1" max="1" width="96.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -1,21 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71224664-3916-4594-9028-1F25E35E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="7080"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Stack" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="AWS " sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="122211"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>NextJS</t>
   </si>
@@ -93,9 +101,6 @@
   </si>
   <si>
     <t>ChatGPT</t>
-  </si>
-  <si>
-    <t>https://www.flipkart.com/hikvision-ezviz-c6n-wifi-indoor-smart-pan-tilt-night-vision-wireless-security-camera/p/itm6a06aa8fa0745?pid=HSAGBBXSQ6ABGUCC&amp;lid=LSTHSAGBBXSQ6ABGUCCZ5YEDC&amp;marketplace=FLIPKART&amp;cmpid=content_home-security-camera_8965229628_gmc&amp;affExtParam1=YT3-43Zi0Ddj1i5R50PxbifL8-0ysWzcOjF1hLOOgzy8RaV_uLJqDDU_Bi5iLxK2IwQliCtJWt9dbfGBMcql6rtmtpy_&amp;affid=ytflipkart</t>
   </si>
   <si>
     <t>https://www.flipkart.com/accutrust-smart-visual-ear-wax-cleaner-5mp-hd-camera-wifi-connectivity-electric/p/itm0315faef11f13?pid=EECHGXCWFRH6XZHA&amp;lid=LSTEECHGXCWFRH6XZHAISPLFA&amp;marketplace=FLIPKART&amp;cmpid=content_electric-ear-cleaner_8965229628_gmc&amp;affExtParam1=YT3-z2rvmWPrOgxlKmfc_aEoLuOMgI-j9wjho2LRdfrZUYxb7nMHeUixAxq1wdbLmpADGix8YWLsz2ErZwLHghUe8bs&amp;affid=ytflipkart</t>
@@ -149,7 +154,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -226,7 +231,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -238,6 +243,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -255,14 +261,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -300,7 +309,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -372,7 +381,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -545,94 +554,94 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D54"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="91.77734375" customWidth="1"/>
+    <col min="1" max="1" width="91.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:4" s="2" customFormat="1" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="3" customFormat="1" ht="14.55" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>13</v>
       </c>
@@ -640,8 +649,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:4" s="3" customFormat="1" ht="14.55" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="1:4" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>15</v>
       </c>
@@ -649,7 +658,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:4" s="4" customFormat="1" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>17</v>
       </c>
@@ -657,96 +666,110 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:4" s="4" customFormat="1" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:4" s="4" customFormat="1" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
     </row>
-    <row r="32" spans="1:4" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" s="9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="51" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="A51" s="7" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A26" r:id="rId1"/>
-    <hyperlink ref="A51" r:id="rId2" display="https://www.geeksforgeeks.org/dsa/print-all-permutations-of-a-string-in-java/"/>
+    <hyperlink ref="A26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A51" r:id="rId2" display="https://www.geeksforgeeks.org/dsa/print-all-permutations-of-a-string-in-java/" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A49" r:id="rId3" display="https://www.flipkart.com/accutrust-smart-visual-ear-wax-cleaner-5mp-hd-camera-wifi-connectivity-electric/p/itm0315faef11f13?pid=EECHGXCWFRH6XZHA&amp;lid=LSTEECHGXCWFRH6XZHAISPLFA&amp;marketplace=FLIPKART&amp;cmpid=content_electric-ear-cleaner_8965229628_gmc&amp;affExtParam1=YT3-z2rvmWPrOgxlKmfc_aEoLuOMgI-j9wjho2LRdfrZUYxb7nMHeUixAxq1wdbLmpADGix8YWLsz2ErZwLHghUe8bs&amp;affid=ytflipkart" xr:uid="{43FE7E05-99E0-44FD-92C6-50DC9E76E9D2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="96.21875" customWidth="1"/>
+    <col min="1" max="1" width="96.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD904FA-0FAD-46CD-8773-AE594AFC6DAB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{050693E8-6307-4796-8B6E-36BA576E71FA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,15 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71224664-3916-4594-9028-1F25E35E0E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979C2D43-650D-4CD2-8652-7053696D09E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Stack" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
-    <sheet name="AWS " sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
+    <sheet name="AWS " sheetId="3" r:id="rId2"/>
+    <sheet name="DynPro" sheetId="5" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="122211"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>NextJS</t>
   </si>
@@ -109,7 +109,52 @@
     <t>Print all permutations of a string in Java</t>
   </si>
   <si>
-    <t>BPMS</t>
+    <t>Interview Questions</t>
+  </si>
+  <si>
+    <t>AWS Certification.</t>
+  </si>
+  <si>
+    <t>AWS Developer (Ananth : Solution architect associate : azure developer  )</t>
+  </si>
+  <si>
+    <t>@Mock</t>
+  </si>
+  <si>
+    <t>@InjectMocks</t>
+  </si>
+  <si>
+    <t>@MockBean</t>
+  </si>
+  <si>
+    <t>@WireMock</t>
+  </si>
+  <si>
+    <t>hrassist@dynproindia.com</t>
+  </si>
+  <si>
+    <t>hrassist1@dynproindia.com</t>
+  </si>
+  <si>
+    <t>udaya.c@dynproindia.com</t>
+  </si>
+  <si>
+    <t>meghana.s@dynpro.in</t>
+  </si>
+  <si>
+    <r>
+      <t>Summarize any complex integration project you have designed and implemented, highlighting the architecture, challenges you faced, and how you resolved them.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFD8372A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>*</t>
+    </r>
   </si>
   <si>
     <r>
@@ -118,7 +163,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="7"/>
+        <sz val="12"/>
         <color rgb="FFD8372A"/>
         <rFont val="Arial"/>
         <family val="2"/>
@@ -127,35 +172,23 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Summarize any complex integration project you have designed and implemented, highlighting the architecture, challenges you faced, and how you resolved them.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <color rgb="FFD8372A"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>*</t>
-    </r>
-  </si>
-  <si>
-    <t>Interview Questions</t>
-  </si>
-  <si>
-    <t>AWS Certification.</t>
-  </si>
-  <si>
-    <t>AWS Developer (Ananth : Solution architect associate : azure developer  )</t>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Software compatability  - spring - spring boot and java version compatability</t>
+  </si>
+  <si>
+    <t>BESCOM Bill Pay</t>
+  </si>
+  <si>
+    <t>United Insurance</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,18 +205,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="7"/>
+      <sz val="12"/>
       <color rgb="FF282525"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="7"/>
+      <sz val="12"/>
       <color rgb="FFD8372A"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -231,7 +278,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -242,8 +289,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -578,7 +627,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
@@ -637,8 +686,8 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>32</v>
+      <c r="A23" s="11" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -703,60 +752,26 @@
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="8" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A51" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A51" r:id="rId2" display="https://www.geeksforgeeks.org/dsa/print-all-permutations-of-a-string-in-java/" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="A49" r:id="rId3" display="https://www.flipkart.com/accutrust-smart-visual-ear-wax-cleaner-5mp-hd-camera-wifi-connectivity-electric/p/itm0315faef11f13?pid=EECHGXCWFRH6XZHA&amp;lid=LSTEECHGXCWFRH6XZHAISPLFA&amp;marketplace=FLIPKART&amp;cmpid=content_electric-ear-cleaner_8965229628_gmc&amp;affExtParam1=YT3-z2rvmWPrOgxlKmfc_aEoLuOMgI-j9wjho2LRdfrZUYxb7nMHeUixAxq1wdbLmpADGix8YWLsz2ErZwLHghUe8bs&amp;affid=ytflipkart" xr:uid="{43FE7E05-99E0-44FD-92C6-50DC9E76E9D2}"/>
+    <hyperlink ref="A49" r:id="rId2" display="https://www.flipkart.com/accutrust-smart-visual-ear-wax-cleaner-5mp-hd-camera-wifi-connectivity-electric/p/itm0315faef11f13?pid=EECHGXCWFRH6XZHA&amp;lid=LSTEECHGXCWFRH6XZHAISPLFA&amp;marketplace=FLIPKART&amp;cmpid=content_electric-ear-cleaner_8965229628_gmc&amp;affExtParam1=YT3-z2rvmWPrOgxlKmfc_aEoLuOMgI-j9wjho2LRdfrZUYxb7nMHeUixAxq1wdbLmpADGix8YWLsz2ErZwLHghUe8bs&amp;affid=ytflipkart" xr:uid="{43FE7E05-99E0-44FD-92C6-50DC9E76E9D2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="96.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD904FA-0FAD-46CD-8773-AE594AFC6DAB}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -765,11 +780,106 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97581F73-ACDD-44F9-985C-0540C21B38C5}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="98.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{050693E8-6307-4796-8B6E-36BA576E71FA}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="98.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A15" r:id="rId1" display="https://www.geeksforgeeks.org/dsa/print-all-permutations-of-a-string-in-java/" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979C2D43-650D-4CD2-8652-7053696D09E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB6A7D2-8BA1-4B1D-9F19-BE069A9A94E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
   <si>
     <t>NextJS</t>
   </si>
@@ -182,6 +182,39 @@
   </si>
   <si>
     <t>United Insurance</t>
+  </si>
+  <si>
+    <t>Amazon Creditcard billpayment</t>
+  </si>
+  <si>
+    <t>BESCOM Billpayment credit.</t>
+  </si>
+  <si>
+    <t>ICICIBANK VISIT</t>
+  </si>
+  <si>
+    <t>Standard charter bank visit</t>
+  </si>
+  <si>
+    <t>interupte()   on a thread interupt status of that thread will be set to true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interupted()  </t>
+  </si>
+  <si>
+    <t>isInteruted() to check wheather a thread is interupted or not.</t>
+  </si>
+  <si>
+    <t>how to keep cooling film on spectacles</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/kwfZJYj9LQk</t>
+  </si>
+  <si>
+    <t>Consultants</t>
+  </si>
+  <si>
+    <t>rakash arigopal</t>
   </si>
 </sst>
 </file>
@@ -782,7 +815,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97581F73-ACDD-44F9-985C-0540C21B38C5}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="98.1796875" customWidth="1"/>
@@ -806,6 +839,69 @@
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB6A7D2-8BA1-4B1D-9F19-BE069A9A94E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B7C74C-4CB3-4E80-8974-6120A5ACC37D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -819,6 +819,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="98.1796875" customWidth="1"/>
+    <col min="2" max="2" width="22.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B7C74C-4CB3-4E80-8974-6120A5ACC37D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C118974A-04C3-4980-ACF6-2F1A8A166373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="19200" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Stack" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
   <si>
     <t>NextJS</t>
   </si>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <t>rakash arigopal</t>
+  </si>
+  <si>
+    <t>Insurance bill payment</t>
+  </si>
+  <si>
+    <t>0524012825P103543585</t>
   </si>
 </sst>
 </file>
@@ -815,7 +821,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97581F73-ACDD-44F9-985C-0540C21B38C5}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="98.1796875" customWidth="1"/>
@@ -903,6 +909,16 @@
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C118974A-04C3-4980-ACF6-2F1A8A166373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C58AA6-3D6A-42A9-88DE-E07464B39D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="19200" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Stack" sheetId="1" r:id="rId1"/>
@@ -13,8 +13,19 @@
     <sheet name="DynPro" sheetId="5" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -23,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="88">
   <si>
     <t>NextJS</t>
   </si>
@@ -67,9 +78,6 @@
     <t>https://chatgpt.com/c/6943a161-3ff0-8323-8244-5f517f818bac</t>
   </si>
   <si>
-    <t>Guardant Healhportal overview.</t>
-  </si>
-  <si>
     <t>https://chatgpt.com/c/6943a318-5800-832d-a340-005e02f1f4f7</t>
   </si>
   <si>
@@ -140,6 +148,355 @@
   </si>
   <si>
     <t>meghana.s@dynpro.in</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Software compatability  - spring - spring boot and java version compatability</t>
+  </si>
+  <si>
+    <t>BESCOM Bill Pay</t>
+  </si>
+  <si>
+    <t>United Insurance</t>
+  </si>
+  <si>
+    <t>Amazon Creditcard billpayment</t>
+  </si>
+  <si>
+    <t>BESCOM Billpayment credit.</t>
+  </si>
+  <si>
+    <t>ICICIBANK VISIT</t>
+  </si>
+  <si>
+    <t>Standard charter bank visit</t>
+  </si>
+  <si>
+    <t>interupte()   on a thread interupt status of that thread will be set to true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interupted()  </t>
+  </si>
+  <si>
+    <t>isInteruted() to check wheather a thread is interupted or not.</t>
+  </si>
+  <si>
+    <t>how to keep cooling film on spectacles</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/kwfZJYj9LQk</t>
+  </si>
+  <si>
+    <t>Consultants</t>
+  </si>
+  <si>
+    <t>rakash arigopal</t>
+  </si>
+  <si>
+    <t>Insurance bill payment</t>
+  </si>
+  <si>
+    <t>0524012825P103543585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        SNI  -  Server Name Indicator.
+	    Will load Multiple SSL Certificate onto web server ( to serve multiple websites)
+		with SNI we  can send multiple Certificate  to server.
+		Usual one IP address one certificate,
+		Using SNI we can send multiple certificates to servers.
+		How it works
+			User opens https://example.com
+			Browser send request + domain name (SNI)
+			Server checks domain	
+			Server returns correct SSL certificate
+			Secure connection is established.
+		Simple Definition : SNI is a TLS feature that allows a server to host multiple HTTPS domains on a single IP by selecting the correct SSL Certificate based on the requested domain names.
+		Works with ALB, NLB ,CloudFront
+Connection Draining (In Elastic load balancer)
+			Is feature that allows in-flight(Ongoing) request to complete before terminating or removing an instance from the load balancer.
+			what is connection draining
+				When an instance 
+					Deregistering manually
+					Marked unhealthy
+					Being terminated
+		    with out Connection Draining, connection will be cutoff abruptly,
+			CLB - Connection draining
+			ALB &amp; NLB - Deregistration Dely.
+			default time is 3600 ile 300 seconds
+			setting 0 value means diabled
+	Auto Scalling Group (ASG) -  Are free of cost
+		in cloud we can create and get rid of servers very quickly
+		ASG 
+			Scale out - add new instances to match increased load
+			Scale - in - remove EC2 Instances to match decreased load
+			Ensure we hava a minimu and max number of EC2 instances running
+	Auto Scaling Group Attributes  ( Launch Configurations)
+		AMI + Instance Type
+		EC2 User Data
+		EBS Volumens
+		Security groups
+		SSH Key pair
+		IAM rOLES FOR UR ec2 Instance
+		Network + subNetwork
+		Load Balancer Information
+		Min size/Max size/ Initial Capacity
+		Scaling Policies
+	CloudWatch
+		Based on cloud watch alarms we can scale-out and scale in polices.
+	Scaling Policies - ( ASG)
+		Dynamic Scaling
+			Target Tracing 
+				Simple to set-up
+				Example: I want the average ASG CPU to stay at around 40%				
+			Simple/Step Scaling
+				When a CloudWatch alarm is triggered( example CPU &gt; 70%), then add 2 units
+				When a CloudWatch alarm is triggered. (example CPU &lt; 30%) then remove 1 instance
+		Scheduled Scaling
+			Anticipate a scaling based on know usage patterns
+			Example increase the min capacity to 10 at 5 pm on Fridays.
+	Autoscaling Groups - Scaling Polices
+		Predictive scaling Continuously forecast load and schedule scaling ahead.
+	Auto ci groups - clin downs
+	After scaling down period , cooldown period 
+	default period is 300 sec.
+	During cooldown period, the ASG will not launch or terminate additional instances
+	Use a read to use AMI to reduce configuration time in order to be serving request fasters and reduce
+	cooldown period.
+	RDS, Aurora &amp; Elastic ache.
+   Amazon RDS Proxy is fully Serverless ARCHITECUTRE.
+	Shading : a database shading is horizontal partitioning technique that splits a large
+	database into small, faster and more manageable pieces called "shards" distributing across 
+	multiple database servers.
+		SLA - Service Level Agreement
+		Root Domain - Main domain with out any prefix. Represents primary domain.
+					  Also called apex, or necked domains
+					  Does not include www or any subparts
+			examples
+				google.com	
+				example.com
+		Non-Root Domain :
+				Any domain that is part of the root domain.
+					www.example.com
+					api.example.com
+					blog.example.com
+		CNAME : Points a hostname to any other hostname 
+				Only for non root domain
+		Alias :
+				Points a hostname to any aws resources
+				works for root domains and non root domains.
+		Route 53 - Alias Records.
+				Maps a hostname to an AWS resource
+		Alias Records 
+					is always of type A/AAAA for AWS resources(IPv4/IPv6)
+					You can't set the TTL.
+		Route 53 - Alias Records Target.
+		Top Level Domain : .com, .in, .us
+		second level domain : amazon.com, icicibank.in
+		CIDRs : Classless inter domain Routing.
+				Is a method to define a range of IP address.
+				IP address/prefix
+		Route 53 - Hybrid DNS
+			Hybrid DNS = On-premises network + aws vpc working together for DNS resolution
+		Route 53 Resolver
+			Route 53 Resolver Inbound Endpoint is a feature of Amazon Route 53 that 
+			allows on-premises systems to resolve DNS names hosted inside AWS (private hosted zones).
+			An Amazon Route 53 Resolver outbound endpoint is a feature of Amazon Web Services
+			that allows your VPC (Virtual Private Cloud) to send DNS queries 
+			from AWS to external DNS systems (like your on-premises data center
+			or other DNS servers).			
+	Classic Solution Architecture.
+		These solutions architectures are the best part of this course.
+		Let's understand how all the technologies we've seen work together
+		This is a section you need to be 100% comfortable with 
+	S3 Storage
+		CRR Cross region replication
+		SRR Same region replication
+	Amazon s3 Glacier Storage Classes
+		Amazon S3 Glacier Instant Retrieval
+			Small monthly monitoring and auto-tiering free
+			Moves Objects automatically between Access Tiers based on usage
+			There are no retrieval charges in S3 Intelligent-Tiering.
+			Frequent Access tier : default tier
+			Infrequent Access tier 30days
+			archive instant access tier : 90days
+			Archive Access tier 90 to 700+ days
+			Deep archive Access tier : 180 days to 700+ days
+	S3 storage classes comparison
+		Your application on EC2 creates images thumbnails after profile photos are uploaded to amazon S3. 
+		These thumbnails can be easily recreated, and only need to be kept for 60days, The source images should be
+		able to be immediately retrieved for these 60 days, and afterwards, the user can wait upto 6 hours.
+		How would you design this ?
+		s3 standard -Glacier after 60days	
+		s3 thumbnail can be on One-Zone IA with a lifecycle configuration to repire them after 60days.
+		A rule in your company states that you should be able to recover your deleted S3 objects immediately for 30days,
+		A rule in ur company states that you should be able to recover ur deleted S objects 
+		Amazon S3 Glacier Flexible Retrieval
+		Amazon S3 Glacier Deep Archive - for long term storage.
+		S3 Standard.
+		S3 Standard Infrequent Access. - Need very fast access
+		S3 Intelligent Tiering. - Almost same as Infrequent access s3
+		S3 One Zone-Infrequent Access. 
+			Frequent Access tier		: Default tier		
+			Infrequent Access tier		: Object not accessed for 30days
+			Archive Instant Access tier	: Object not accessed for 90days
+			Archive Access tier 		: Configurable from 90 days to 700+ days
+			Deep archive Access tier.	: Config from 180 dyas to 700+ days
+		Switching between classes manually or using S3 Lifecycle configurations.
+30
+Infrequent access tier 30
+archive instant access tier 90dyas
+archive access tier 90 -700+days configuration
+deep archive access 180 days to 700+days		
+	WORM Write Once Read Many model
+	ASG - Auto Scaling groups	
+	OAC - Origin Access Control
+	VPC - Virtual Private cloud.
+	CRR - Cross region replication
+	SRR - Shared region replication.
+	SMP - Protocol
+	HPC - High Performance computing
+	IOPS - Input output per second
+	SMB - Server Message Blocks.
+	iSCSI - Internet Small computer system interface.
+	VTL - Virtual Tape library
+	POSIX - a set of standards for compatibility between operating systems,
+		not a single network communication protocol itself.
+	ZFS - Zettabyte File system.
+	NGW - NAT Gateway
+	CSI - Container storage interface.
+	ENI - Elastic Network Interface.
+	RCU - Read Capacity Unit
+	WCU - Write Capacity Unit.
+	DAX - Dynamo DB Accelerator 
+	PITR - Point in time recovery
+	ENI -	Elastic network interface
+	EMR - Elastic Map Reducer.
+	SSML- Speech Synthasis Markup Language.
+	EBS - Elastic Block storage
+	SCP - Service Control policies
+	WAP - Web Application Fire wall	
+	ACL - Access Control List
+	NACL - Network Access control list
+	Athene - Run sql queries on data stored in S3
+	SSM - AWS System Manager.
+	IANA - Internet Assigned Number Authority 
+	IGW - Internet Gateway
+	NAT - Network address traslation.
+	EIP - Elastic ip
+	SCT - Schema Conversion Toll.
+	CDC - Change data capture.
+	DMS - Data Migration Service
+	WORM - Write Once Read Many times.
+	EFA - Elastic Fabric adapter
+	MPI Message Passing Interface
+	DKIM - DomainKeys Identified Mail
+	SPF - Sender Ploicy Framework
+	teraforms ? 
+	Transit Gateway, Internet Gateway, NAT Gateway, VPN Gateway
+	YD9NP-Y2V7F-H9KV4-MGJ7T-687GD₹=
+YD9NP-Y2V7F-H9KV4-MGJ7T-687GD₹=
+</t>
+  </si>
+  <si>
+    <t>what is enterprise architecture ?</t>
+  </si>
+  <si>
+    <t>Architected federated identity and secure authentication systems leveraging SAML, OAuth2, JWT, LDAP, Okta, and Keyclocak with deep expertise in SSO and API security best practices.</t>
+  </si>
+  <si>
+    <t>TDD/BDD using JUnit 5, Mockito</t>
+  </si>
+  <si>
+    <t>Test containers</t>
+  </si>
+  <si>
+    <t>•</t>
+  </si>
+  <si>
+    <t>Extensive experience in federated identity (SAML, OAuth2, KEYCLOCK, and OKTA) and web services (SOAP, REST, and JMS).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hands-on design and deployment of AWS cloud-native solutions including </t>
+  </si>
+  <si>
+    <t>, Event Bridge, Step Functions, SQS.</t>
+  </si>
+  <si>
+    <t>AWS(IAM, RDS, EC2, SQS, SES, Lambda, Step Functions, Cloud Formation, aws gateway)</t>
+  </si>
+  <si>
+    <t>Event-Driven Architecture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jprofiler, JMeter, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python </t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>Provided technical guidance on Kubernetes-native deployments, observability (logging, tracing, metrics), and performance optimization.</t>
+  </si>
+  <si>
+    <t>clusters</t>
+  </si>
+  <si>
+    <t>AWS(IAM, RDS, EC2, SQS, SES, Lambda, Step Functions, Cloud Formation)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=upfNrn8g_WE  -- Java Interview| 10+ years experience|</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=lGFX1gY_zUg -Java Interview| 9+ years experience</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=6dSkRUIDlDc - solution architecture questions</t>
+  </si>
+  <si>
+    <t>AWS Certification:</t>
+  </si>
+  <si>
+    <t>Solutions Architect Professional (MANDATORY for architects)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Solutions Architect Associate (MANDATORY)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     https://chatgpt.com/c/69312748-4b1c-8321-84d5-daf7ce18eca0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     		https://chatgpt.com/c/69315e97-d070-8325-9a21-5e0c8ee52691</t>
+  </si>
+  <si>
+    <t>Guardant Healhportal/Project overview.</t>
+  </si>
+  <si>
+    <t>Required New scope in outer context.</t>
+  </si>
+  <si>
+    <t>Behaviour of Prototype class in singleton class -  Spring bean scope.</t>
+  </si>
+  <si>
+    <t>Jpa on lock behaviour (optimastic and passimstive lock.)</t>
+  </si>
+  <si>
+    <r>
+      <t>Share an example of how you have taken a real-world customer problem and converted it into a scalable technical framework or reusable solution.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFD8372A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>*</t>
+    </r>
   </si>
   <si>
     <r>
@@ -148,7 +505,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="12"/>
+        <sz val="14"/>
         <color rgb="FFD8372A"/>
         <rFont val="Arial"/>
         <family val="2"/>
@@ -157,77 +514,17 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Share an example of how you have taken a real-world customer problem and converted it into a scalable technical framework or reusable solution.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFD8372A"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>*</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Software compatability  - spring - spring boot and java version compatability</t>
-  </si>
-  <si>
-    <t>BESCOM Bill Pay</t>
-  </si>
-  <si>
-    <t>United Insurance</t>
-  </si>
-  <si>
-    <t>Amazon Creditcard billpayment</t>
-  </si>
-  <si>
-    <t>BESCOM Billpayment credit.</t>
-  </si>
-  <si>
-    <t>ICICIBANK VISIT</t>
-  </si>
-  <si>
-    <t>Standard charter bank visit</t>
-  </si>
-  <si>
-    <t>interupte()   on a thread interupt status of that thread will be set to true</t>
-  </si>
-  <si>
-    <t xml:space="preserve">interupted()  </t>
-  </si>
-  <si>
-    <t>isInteruted() to check wheather a thread is interupted or not.</t>
-  </si>
-  <si>
-    <t>how to keep cooling film on spectacles</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/shorts/kwfZJYj9LQk</t>
-  </si>
-  <si>
-    <t>Consultants</t>
-  </si>
-  <si>
-    <t>rakash arigopal</t>
-  </si>
-  <si>
-    <t>Insurance bill payment</t>
-  </si>
-  <si>
-    <t>0524012825P103543585</t>
+    <t>what is @Lookup in context onf Cache.</t>
+  </si>
+  <si>
+    <t>Alex a default channel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -244,35 +541,64 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="12"/>
+      <sz val="14"/>
       <color rgb="FF282525"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="14"/>
       <color rgb="FFD8372A"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -303,6 +629,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -317,21 +649,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -341,8 +682,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF0066"/>
       <color rgb="FFCC3300"/>
-      <color rgb="FFFF0066"/>
     </mruColors>
   </colors>
   <extLst>
@@ -643,167 +984,188 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D54"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D55"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="91.81640625" customWidth="1"/>
+    <col min="1" max="1" width="91.81640625" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>30</v>
+      <c r="A5" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="A22" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="11"/>
+    </row>
+    <row r="30" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="11"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="5"/>
-    </row>
-    <row r="30" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="5"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A49" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>41</v>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A49" r:id="rId2" display="https://www.flipkart.com/accutrust-smart-visual-ear-wax-cleaner-5mp-hd-camera-wifi-connectivity-electric/p/itm0315faef11f13?pid=EECHGXCWFRH6XZHA&amp;lid=LSTEECHGXCWFRH6XZHAISPLFA&amp;marketplace=FLIPKART&amp;cmpid=content_electric-ear-cleaner_8965229628_gmc&amp;affExtParam1=YT3-z2rvmWPrOgxlKmfc_aEoLuOMgI-j9wjho2LRdfrZUYxb7nMHeUixAxq1wdbLmpADGix8YWLsz2ErZwLHghUe8bs&amp;affid=ytflipkart" xr:uid="{43FE7E05-99E0-44FD-92C6-50DC9E76E9D2}"/>
+    <hyperlink ref="A45" r:id="rId2" display="https://www.flipkart.com/accutrust-smart-visual-ear-wax-cleaner-5mp-hd-camera-wifi-connectivity-electric/p/itm0315faef11f13?pid=EECHGXCWFRH6XZHA&amp;lid=LSTEECHGXCWFRH6XZHAISPLFA&amp;marketplace=FLIPKART&amp;cmpid=content_electric-ear-cleaner_8965229628_gmc&amp;affExtParam1=YT3-z2rvmWPrOgxlKmfc_aEoLuOMgI-j9wjho2LRdfrZUYxb7nMHeUixAxq1wdbLmpADGix8YWLsz2ErZwLHghUe8bs&amp;affid=ytflipkart" xr:uid="{43FE7E05-99E0-44FD-92C6-50DC9E76E9D2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
@@ -812,113 +1174,243 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD904FA-0FAD-46CD-8773-AE594AFC6DAB}">
-  <dimension ref="A1"/>
+  <dimension ref="F10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="2" width="8.7265625" customWidth="1"/>
+    <col min="6" max="6" width="130.1796875" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="10" spans="6:6" ht="409.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F10" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97581F73-ACDD-44F9-985C-0540C21B38C5}">
-  <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C73"/>
+  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="98.1796875" customWidth="1"/>
-    <col min="2" max="2" width="22.36328125" customWidth="1"/>
+    <col min="1" max="1" width="98.1796875" style="16" customWidth="1"/>
+    <col min="2" max="2" width="22.36328125" style="16" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="16" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="16" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="16" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="16" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="B22" s="16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="16" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B22" t="s">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="16" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="16" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="16" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C54" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -929,64 +1421,65 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="98.7265625" customWidth="1"/>
+    <col min="1" max="1" width="98.7265625" style="4" customWidth="1"/>
+    <col min="2" max="16384" width="8.7265625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A1" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" s="14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A7" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A9" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A10" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A11" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A15" s="15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A17" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A21" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>44</v>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A22" s="13" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C58AA6-3D6A-42A9-88DE-E07464B39D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4DAD910-D505-4335-A288-120F8F2DF495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Stack" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="91">
   <si>
     <t>NextJS</t>
   </si>
@@ -518,6 +518,15 @@
   </si>
   <si>
     <t>Alex a default channel</t>
+  </si>
+  <si>
+    <t>LIC Date's</t>
+  </si>
+  <si>
+    <t>LIC</t>
+  </si>
+  <si>
+    <t>Medical insurnce claim for incometax</t>
   </si>
 </sst>
 </file>
@@ -984,7 +993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="91.81640625" style="1" customWidth="1"/>
@@ -1160,6 +1169,11 @@
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1420,7 +1434,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="98.7265625" style="4" customWidth="1"/>
@@ -1482,6 +1496,16 @@
         <v>41</v>
       </c>
     </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A24" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A25" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A15" r:id="rId1" display="https://www.geeksforgeeks.org/dsa/print-all-permutations-of-a-string-in-java/" xr:uid="{00000000-0004-0000-0000-000001000000}"/>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4DAD910-D505-4335-A288-120F8F2DF495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD8DF20-3439-4E92-AE77-764E9799D752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Stack" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="114">
   <si>
     <t>NextJS</t>
   </si>
@@ -199,6 +199,135 @@
   </si>
   <si>
     <t>0524012825P103543585</t>
+  </si>
+  <si>
+    <t>what is enterprise architecture ?</t>
+  </si>
+  <si>
+    <t>Architected federated identity and secure authentication systems leveraging SAML, OAuth2, JWT, LDAP, Okta, and Keyclocak with deep expertise in SSO and API security best practices.</t>
+  </si>
+  <si>
+    <t>TDD/BDD using JUnit 5, Mockito</t>
+  </si>
+  <si>
+    <t>Test containers</t>
+  </si>
+  <si>
+    <t>•</t>
+  </si>
+  <si>
+    <t>Extensive experience in federated identity (SAML, OAuth2, KEYCLOCK, and OKTA) and web services (SOAP, REST, and JMS).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hands-on design and deployment of AWS cloud-native solutions including </t>
+  </si>
+  <si>
+    <t>, Event Bridge, Step Functions, SQS.</t>
+  </si>
+  <si>
+    <t>AWS(IAM, RDS, EC2, SQS, SES, Lambda, Step Functions, Cloud Formation, aws gateway)</t>
+  </si>
+  <si>
+    <t>Event-Driven Architecture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jprofiler, JMeter, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python </t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>Provided technical guidance on Kubernetes-native deployments, observability (logging, tracing, metrics), and performance optimization.</t>
+  </si>
+  <si>
+    <t>clusters</t>
+  </si>
+  <si>
+    <t>AWS(IAM, RDS, EC2, SQS, SES, Lambda, Step Functions, Cloud Formation)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=upfNrn8g_WE  -- Java Interview| 10+ years experience|</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=lGFX1gY_zUg -Java Interview| 9+ years experience</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=6dSkRUIDlDc - solution architecture questions</t>
+  </si>
+  <si>
+    <t>AWS Certification:</t>
+  </si>
+  <si>
+    <t>Solutions Architect Professional (MANDATORY for architects)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Solutions Architect Associate (MANDATORY)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     https://chatgpt.com/c/69312748-4b1c-8321-84d5-daf7ce18eca0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     		https://chatgpt.com/c/69315e97-d070-8325-9a21-5e0c8ee52691</t>
+  </si>
+  <si>
+    <t>Guardant Healhportal/Project overview.</t>
+  </si>
+  <si>
+    <t>Required New scope in outer context.</t>
+  </si>
+  <si>
+    <t>Behaviour of Prototype class in singleton class -  Spring bean scope.</t>
+  </si>
+  <si>
+    <t>Jpa on lock behaviour (optimastic and passimstive lock.)</t>
+  </si>
+  <si>
+    <r>
+      <t>Share an example of how you have taken a real-world customer problem and converted it into a scalable technical framework or reusable solution.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFD8372A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Summarize any complex integration project you have designed and implemented, highlighting the architecture, challenges you faced, and how you resolved them.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFD8372A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <t>what is @Lookup in context onf Cache.</t>
+  </si>
+  <si>
+    <t>Alex a default channel</t>
+  </si>
+  <si>
+    <t>LIC</t>
+  </si>
+  <si>
+    <t>Medical insurnce claim for incometax</t>
+  </si>
+  <si>
+    <t>https://www.xbox.com/en-US/promotions/landing-page/game-pass/pc-offer  - pc game pass</t>
   </si>
   <si>
     <t xml:space="preserve">        SNI  -  Server Name Indicator.
@@ -396,144 +525,84 @@
 	teraforms ? 
 	Transit Gateway, Internet Gateway, NAT Gateway, VPN Gateway
 	YD9NP-Y2V7F-H9KV4-MGJ7T-687GD₹=
-YD9NP-Y2V7F-H9KV4-MGJ7T-687GD₹=
-</t>
-  </si>
-  <si>
-    <t>what is enterprise architecture ?</t>
-  </si>
-  <si>
-    <t>Architected federated identity and secure authentication systems leveraging SAML, OAuth2, JWT, LDAP, Okta, and Keyclocak with deep expertise in SSO and API security best practices.</t>
-  </si>
-  <si>
-    <t>TDD/BDD using JUnit 5, Mockito</t>
-  </si>
-  <si>
-    <t>Test containers</t>
-  </si>
-  <si>
-    <t>•</t>
-  </si>
-  <si>
-    <t>Extensive experience in federated identity (SAML, OAuth2, KEYCLOCK, and OKTA) and web services (SOAP, REST, and JMS).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hands-on design and deployment of AWS cloud-native solutions including </t>
-  </si>
-  <si>
-    <t>, Event Bridge, Step Functions, SQS.</t>
-  </si>
-  <si>
-    <t>AWS(IAM, RDS, EC2, SQS, SES, Lambda, Step Functions, Cloud Formation, aws gateway)</t>
-  </si>
-  <si>
-    <t>Event-Driven Architecture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jprofiler, JMeter, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python </t>
-  </si>
-  <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t>Provided technical guidance on Kubernetes-native deployments, observability (logging, tracing, metrics), and performance optimization.</t>
-  </si>
-  <si>
-    <t>clusters</t>
-  </si>
-  <si>
-    <t>AWS(IAM, RDS, EC2, SQS, SES, Lambda, Step Functions, Cloud Formation)</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=upfNrn8g_WE  -- Java Interview| 10+ years experience|</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=lGFX1gY_zUg -Java Interview| 9+ years experience</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=6dSkRUIDlDc - solution architecture questions</t>
-  </si>
-  <si>
-    <t>AWS Certification:</t>
-  </si>
-  <si>
-    <t>Solutions Architect Professional (MANDATORY for architects)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Solutions Architect Associate (MANDATORY)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     https://chatgpt.com/c/69312748-4b1c-8321-84d5-daf7ce18eca0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     		https://chatgpt.com/c/69315e97-d070-8325-9a21-5e0c8ee52691</t>
-  </si>
-  <si>
-    <t>Guardant Healhportal/Project overview.</t>
-  </si>
-  <si>
-    <t>Required New scope in outer context.</t>
-  </si>
-  <si>
-    <t>Behaviour of Prototype class in singleton class -  Spring bean scope.</t>
-  </si>
-  <si>
-    <t>Jpa on lock behaviour (optimastic and passimstive lock.)</t>
-  </si>
-  <si>
-    <r>
-      <t>Share an example of how you have taken a real-world customer problem and converted it into a scalable technical framework or reusable solution.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFD8372A"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>*</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Summarize any complex integration project you have designed and implemented, highlighting the architecture, challenges you faced, and how you resolved them.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFD8372A"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>*</t>
-    </r>
-  </si>
-  <si>
-    <t>what is @Lookup in context onf Cache.</t>
-  </si>
-  <si>
-    <t>Alex a default channel</t>
-  </si>
-  <si>
-    <t>LIC Date's</t>
-  </si>
-  <si>
-    <t>LIC</t>
-  </si>
-  <si>
-    <t>Medical insurnce claim for incometax</t>
+YD9NP-Y2V7F-H9KV4-MGJ7T-687GD₹=    
+AWS Managed Services    </t>
+  </si>
+  <si>
+    <t>AWS Managed Services</t>
+  </si>
+  <si>
+    <t>Elastic Load Balancing</t>
+  </si>
+  <si>
+    <t>Elastic Bean Stack</t>
+  </si>
+  <si>
+    <t>Amazon Elastic Container Service ECS</t>
+  </si>
+  <si>
+    <t>Amazon Elastic Kubernetes Service</t>
+  </si>
+  <si>
+    <t>Amazon RDS</t>
+  </si>
+  <si>
+    <t>AWS Fargate  (Serverless compute for Containers)</t>
+  </si>
+  <si>
+    <t>SBI Online check</t>
+  </si>
+  <si>
+    <t>MR2320557</t>
+  </si>
+  <si>
+    <t>VPC</t>
+  </si>
+  <si>
+    <t>VPC SubNets</t>
+  </si>
+  <si>
+    <t>CIDR Classless Inter-Domain Routing  Blocks</t>
+  </si>
+  <si>
+    <t>VPC CIDR Block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public SubNet </t>
+  </si>
+  <si>
+    <t>Routing on internet</t>
+  </si>
+  <si>
+    <t>Routing inside AWS</t>
+  </si>
+  <si>
+    <t>Exectuion of RouteTable</t>
+  </si>
+  <si>
+    <t>Public SubNet vs Private Subnet</t>
+  </si>
+  <si>
+    <t>Internet Gateway</t>
+  </si>
+  <si>
+    <t>NAT (Network Address Traslation) instance and gateway  (NAT Instance and NAT Gateway)</t>
+  </si>
+  <si>
+    <t>VPC Routetable, and subnet routetable</t>
+  </si>
+  <si>
+    <t>Security groups in vpc and subnets</t>
+  </si>
+  <si>
+    <t>Network access control list ( NACL or ACL)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -606,6 +675,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -658,7 +734,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -682,6 +758,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1085,7 +1164,7 @@
         <v>13</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35"/>
@@ -1148,32 +1227,32 @@
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1188,7 +1267,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD904FA-0FAD-46CD-8773-AE594AFC6DAB}">
-  <dimension ref="F10"/>
+  <dimension ref="E10:F78"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="8.7265625" customWidth="1"/>
@@ -1197,8 +1276,225 @@
   <sheetData>
     <row r="10" spans="6:6" ht="409.5" x14ac:dyDescent="0.55000000000000004">
       <c r="F10" s="3" t="s">
-        <v>55</v>
-      </c>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F32" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F33" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F34" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F35" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F36" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F37" s="17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F38" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F39" s="17"/>
+    </row>
+    <row r="40" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F40" s="17"/>
+    </row>
+    <row r="41" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F41" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F42" s="17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="43" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F43" s="17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="44" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F44" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E45" s="17"/>
+      <c r="F45" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="46" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E46" s="17"/>
+      <c r="F46" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E47" s="17"/>
+      <c r="F47" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="48" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E48" s="17"/>
+      <c r="F48" s="17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="49" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E49" s="17"/>
+      <c r="F49" s="17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="50" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E50" s="17"/>
+      <c r="F50" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="51" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E51" s="17"/>
+      <c r="F51" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="52" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E52" s="17"/>
+      <c r="F52" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="53" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E53" s="17"/>
+      <c r="F53" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="54" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E54" s="17"/>
+      <c r="F54" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E55" s="17"/>
+      <c r="F55" s="17"/>
+    </row>
+    <row r="56" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E56" s="17"/>
+      <c r="F56" s="17"/>
+    </row>
+    <row r="57" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E57" s="17"/>
+      <c r="F57" s="17"/>
+    </row>
+    <row r="58" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E58" s="17"/>
+      <c r="F58" s="17"/>
+    </row>
+    <row r="59" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E59" s="17"/>
+      <c r="F59" s="17"/>
+    </row>
+    <row r="60" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E60" s="17"/>
+      <c r="F60" s="17"/>
+    </row>
+    <row r="61" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E61" s="17"/>
+      <c r="F61" s="17"/>
+    </row>
+    <row r="62" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
+    </row>
+    <row r="63" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E63" s="17"/>
+      <c r="F63" s="17"/>
+    </row>
+    <row r="64" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E64" s="17"/>
+      <c r="F64" s="17"/>
+    </row>
+    <row r="65" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E65" s="17"/>
+      <c r="F65" s="17"/>
+    </row>
+    <row r="66" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E66" s="17"/>
+      <c r="F66" s="17"/>
+    </row>
+    <row r="67" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E67" s="17"/>
+      <c r="F67" s="17"/>
+    </row>
+    <row r="68" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E68" s="17"/>
+      <c r="F68" s="17"/>
+    </row>
+    <row r="69" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E69" s="17"/>
+      <c r="F69" s="17"/>
+    </row>
+    <row r="70" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E70" s="17"/>
+      <c r="F70" s="17"/>
+    </row>
+    <row r="71" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E71" s="17"/>
+      <c r="F71" s="17"/>
+    </row>
+    <row r="72" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E72" s="17"/>
+      <c r="F72" s="17"/>
+    </row>
+    <row r="73" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E73" s="17"/>
+      <c r="F73" s="17"/>
+    </row>
+    <row r="74" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E74" s="17"/>
+      <c r="F74" s="17"/>
+    </row>
+    <row r="75" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E75" s="17"/>
+      <c r="F75" s="17"/>
+    </row>
+    <row r="76" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E76" s="17"/>
+      <c r="F76" s="17"/>
+    </row>
+    <row r="77" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E77" s="17"/>
+      <c r="F77" s="17"/>
+    </row>
+    <row r="78" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E78" s="17"/>
+      <c r="F78" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1207,7 +1503,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97581F73-ACDD-44F9-985C-0540C21B38C5}">
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="98.1796875" style="16" customWidth="1"/>
@@ -1310,121 +1606,126 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B37" s="16" t="s">
         <v>60</v>
-      </c>
-      <c r="B37" s="16" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B38" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" s="16" t="s">
         <v>62</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="C54" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="16" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1434,7 +1735,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="98.7265625" style="4" customWidth="1"/>
@@ -1448,12 +1749,12 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
@@ -1498,12 +1799,22 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A26" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A31" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD8DF20-3439-4E92-AE77-764E9799D752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A795532-05F1-4DFF-B28C-FFFD2140AD87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="115">
   <si>
     <t>NextJS</t>
   </si>
@@ -596,6 +596,9 @@
   </si>
   <si>
     <t>Network access control list ( NACL or ACL)</t>
+  </si>
+  <si>
+    <t>availability and durability</t>
   </si>
 </sst>
 </file>
@@ -1406,7 +1409,9 @@
     </row>
     <row r="56" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E56" s="17"/>
-      <c r="F56" s="17"/>
+      <c r="F56" s="17" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="57" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E57" s="17"/>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A795532-05F1-4DFF-B28C-FFFD2140AD87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36EEA3B-BD7C-4CFD-AF3A-FBA14C97FE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12,6 +12,7 @@
     <sheet name="AWS " sheetId="3" r:id="rId2"/>
     <sheet name="DynPro" sheetId="5" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId4"/>
+    <sheet name="Need to address" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="200">
   <si>
     <t>NextJS</t>
   </si>
@@ -556,18 +557,6 @@
     <t>MR2320557</t>
   </si>
   <si>
-    <t>VPC</t>
-  </si>
-  <si>
-    <t>VPC SubNets</t>
-  </si>
-  <si>
-    <t>CIDR Classless Inter-Domain Routing  Blocks</t>
-  </si>
-  <si>
-    <t>VPC CIDR Block</t>
-  </si>
-  <si>
     <t xml:space="preserve">Public SubNet </t>
   </si>
   <si>
@@ -589,16 +578,283 @@
     <t>NAT (Network Address Traslation) instance and gateway  (NAT Instance and NAT Gateway)</t>
   </si>
   <si>
-    <t>VPC Routetable, and subnet routetable</t>
-  </si>
-  <si>
     <t>Security groups in vpc and subnets</t>
   </si>
   <si>
     <t>Network access control list ( NACL or ACL)</t>
   </si>
   <si>
-    <t>availability and durability</t>
+    <t>Availability and Durability</t>
+  </si>
+  <si>
+    <t>VPC    Virtual Private Cloud  - Fundamentals</t>
+  </si>
+  <si>
+    <t>What is need for Amazon VPC</t>
+  </si>
+  <si>
+    <t>What is need for VPC SubNets</t>
+  </si>
+  <si>
+    <t>VPC SubNets  - Addressing for Resources - IP address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIDR ( Classless Inter-Domain Routing  Blocks) </t>
+  </si>
+  <si>
+    <t>CIDR Block Example - Security Group</t>
+  </si>
+  <si>
+    <t>VPC CIDR Blocks   (Choosing a CIDR Block for VPC)</t>
+  </si>
+  <si>
+    <t>VPC and Subnet Demo</t>
+  </si>
+  <si>
+    <t>NAT Gateway VS NAT Instance</t>
+  </si>
+  <si>
+    <t>VPC Main Route table, and subnet main route table</t>
+  </si>
+  <si>
+    <t>Security groups VS NACL</t>
+  </si>
+  <si>
+    <t>S3 Fundamentals</t>
+  </si>
+  <si>
+    <t>AWS - Simple storage service</t>
+  </si>
+  <si>
+    <t>S3 Objects and Buckets , Key value Example</t>
+  </si>
+  <si>
+    <t>S3 Versioning</t>
+  </si>
+  <si>
+    <t>S3 Static Website Hosting.</t>
+  </si>
+  <si>
+    <t>Resource based Polocies - Bucket Policies</t>
+  </si>
+  <si>
+    <t>Amazon S3 Tags</t>
+  </si>
+  <si>
+    <t>S3 Event Notifications</t>
+  </si>
+  <si>
+    <t>S3 Prefix</t>
+  </si>
+  <si>
+    <t>Bucket ACLs and Object ACLs</t>
+  </si>
+  <si>
+    <t>S3 Storage classes - Introduction</t>
+  </si>
+  <si>
+    <t>s3 Lifecycle configuration</t>
+  </si>
+  <si>
+    <t>Amazon S3 Replication - Same region and Multiple Regions</t>
+  </si>
+  <si>
+    <t>S3 - Object Level Configuration</t>
+  </si>
+  <si>
+    <t>S3 consistency</t>
+  </si>
+  <si>
+    <t>S3 Presigned URL</t>
+  </si>
+  <si>
+    <t>S3 access Points</t>
+  </si>
+  <si>
+    <t>S3 Senarios - Security</t>
+  </si>
+  <si>
+    <t>S3 Cost</t>
+  </si>
+  <si>
+    <t>S3 Performance</t>
+  </si>
+  <si>
+    <t>S3 Glaciar</t>
+  </si>
+  <si>
+    <t>s3 vs s3 Glaciar</t>
+  </si>
+  <si>
+    <t>Retrieving archives from S3 Glaciar</t>
+  </si>
+  <si>
+    <t>I AM FUNDAMENTALS</t>
+  </si>
+  <si>
+    <t>Typical identity management in the cloud</t>
+  </si>
+  <si>
+    <t>AWS Identity and accesmanagement</t>
+  </si>
+  <si>
+    <t>Important IAM Concepts</t>
+  </si>
+  <si>
+    <t>IAM Policies -  Authorization</t>
+  </si>
+  <si>
+    <t>AWS Managed Policy</t>
+  </si>
+  <si>
+    <t>Customer Managed Polocy</t>
+  </si>
+  <si>
+    <t>IAM Scenarios</t>
+  </si>
+  <si>
+    <t>Instance Profile</t>
+  </si>
+  <si>
+    <t>I am Role Use case 1 : EC2 talking with S3</t>
+  </si>
+  <si>
+    <t>I am Role Use case 2 : Cross account access</t>
+  </si>
+  <si>
+    <t>Corporate Directory Fedaration</t>
+  </si>
+  <si>
+    <t>IAM - Web Identity Fedaration</t>
+  </si>
+  <si>
+    <t>Identity based and Resource based policies</t>
+  </si>
+  <si>
+    <t>IAM Scenarios Questions</t>
+  </si>
+  <si>
+    <t>Authentication with IAM</t>
+  </si>
+  <si>
+    <t>Data Encription KMS &amp; Cloud HSM</t>
+  </si>
+  <si>
+    <t>Data States</t>
+  </si>
+  <si>
+    <t>Encryption</t>
+  </si>
+  <si>
+    <t>Symmetric Key Encription</t>
+  </si>
+  <si>
+    <t>Asymmetric Key Encription</t>
+  </si>
+  <si>
+    <t>KMS and Cloud HSM</t>
+  </si>
+  <si>
+    <t>AWS KMS</t>
+  </si>
+  <si>
+    <t>Server side Encryption with KMS</t>
+  </si>
+  <si>
+    <t>Envelope Encryption.</t>
+  </si>
+  <si>
+    <t>Decryption of data using KMS</t>
+  </si>
+  <si>
+    <t>AWS CloudHSM</t>
+  </si>
+  <si>
+    <t>Server side Encryption and Client Side Encryption</t>
+  </si>
+  <si>
+    <t>Storage Fundamentals</t>
+  </si>
+  <si>
+    <t>AWS Storage types</t>
+  </si>
+  <si>
+    <t>Block storage</t>
+  </si>
+  <si>
+    <t>File storage</t>
+  </si>
+  <si>
+    <t>instance storage</t>
+  </si>
+  <si>
+    <t>AWS EBS - Elastic block storage</t>
+  </si>
+  <si>
+    <t>Hard disk drive vs Solid state drive</t>
+  </si>
+  <si>
+    <t>EBS SSD Types</t>
+  </si>
+  <si>
+    <t>EBS HDD Types</t>
+  </si>
+  <si>
+    <t>EBS Snapshots</t>
+  </si>
+  <si>
+    <t>EBS Encryption</t>
+  </si>
+  <si>
+    <t>Faster I/O Performance between EC2 and EBS</t>
+  </si>
+  <si>
+    <t>EC2 Instance lifecycle</t>
+  </si>
+  <si>
+    <t>RAID</t>
+  </si>
+  <si>
+    <t>EBS Snapshots and AMI's</t>
+  </si>
+  <si>
+    <t>Using an AMI from different AWS Account or region</t>
+  </si>
+  <si>
+    <t>Amazon EBS Scenarios - EC2</t>
+  </si>
+  <si>
+    <t>Amazon EBS Scenarios - snapshots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon EFS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Amazon FSx for Lustre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     Amazon  FSx for window File Server</t>
+  </si>
+  <si>
+    <t>Review of storage Options</t>
+  </si>
+  <si>
+    <t>AWS Storage Gateways</t>
+  </si>
+  <si>
+    <t>AWS Storage File Gateways</t>
+  </si>
+  <si>
+    <t>AWS Storage Tape Gateways</t>
+  </si>
+  <si>
+    <t>AWS Storage Volume Gateways</t>
+  </si>
+  <si>
+    <t>AWS Storage Volume Gateways - Cached and Stored.</t>
+  </si>
+  <si>
+    <t>Database fundamentals</t>
   </si>
 </sst>
 </file>
@@ -1270,7 +1526,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD904FA-0FAD-46CD-8773-AE594AFC6DAB}">
-  <dimension ref="E10:F78"/>
+  <dimension ref="E10:G206"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="8.7265625" customWidth="1"/>
@@ -1287,147 +1543,153 @@
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="33" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F33" s="17" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="34" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F34" s="17" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="35" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F35" s="17" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="36" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F36" s="17" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="37" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="37" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F37" s="17" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="38" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="38" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F38" s="17" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="39" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="39" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F39" s="17"/>
     </row>
-    <row r="40" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="40" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F40" s="17"/>
     </row>
-    <row r="41" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="41" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F41" s="17" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F42" s="17" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="43" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F43" s="17" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="44" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F44" s="17" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="45" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E45" s="17"/>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="45" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F45" s="17" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="46" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E46" s="17"/>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F46" s="17" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="47" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E47" s="17"/>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F47" s="17" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="48" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E48" s="17"/>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="48" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F48" s="17" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E49" s="17"/>
       <c r="F49" s="17" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E50" s="17"/>
       <c r="F50" s="17" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E51" s="17"/>
       <c r="F51" s="17" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E52" s="17"/>
       <c r="F52" s="17" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E53" s="17"/>
       <c r="F53" s="17" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E54" s="17"/>
       <c r="F54" s="17" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E55" s="17"/>
-      <c r="F55" s="17"/>
+      <c r="F55" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="56" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E56" s="17"/>
       <c r="F56" s="17" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E57" s="17"/>
-      <c r="F57" s="17"/>
+      <c r="F57" s="17" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="58" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E58" s="17"/>
-      <c r="F58" s="17"/>
+      <c r="F58" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="59" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E59" s="17"/>
-      <c r="F59" s="17"/>
+      <c r="F59" s="17" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="60" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E60" s="17"/>
-      <c r="F60" s="17"/>
+      <c r="F60" s="17" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="61" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E61" s="17"/>
@@ -1443,63 +1705,736 @@
     </row>
     <row r="64" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E64" s="17"/>
-      <c r="F64" s="17"/>
+      <c r="F64" s="17" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="65" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E65" s="17"/>
-      <c r="F65" s="17"/>
+      <c r="F65" s="17" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="66" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E66" s="17"/>
-      <c r="F66" s="17"/>
+      <c r="F66" s="17" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="67" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E67" s="17"/>
-      <c r="F67" s="17"/>
+      <c r="F67" s="17" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="68" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E68" s="17"/>
-      <c r="F68" s="17"/>
+      <c r="F68" s="17" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="69" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E69" s="17"/>
-      <c r="F69" s="17"/>
+      <c r="F69" s="17" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="70" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E70" s="17"/>
-      <c r="F70" s="17"/>
+      <c r="F70" s="17" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="71" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E71" s="17"/>
-      <c r="F71" s="17"/>
+      <c r="F71" s="17" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="72" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E72" s="17"/>
-      <c r="F72" s="17"/>
+      <c r="F72" s="17" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="73" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E73" s="17"/>
-      <c r="F73" s="17"/>
+      <c r="F73" s="17" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="74" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E74" s="17"/>
-      <c r="F74" s="17"/>
+      <c r="F74" s="17" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="75" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E75" s="17"/>
-      <c r="F75" s="17"/>
+      <c r="F75" s="17" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="76" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E76" s="17"/>
-      <c r="F76" s="17"/>
+      <c r="F76" s="17" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="77" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E77" s="17"/>
-      <c r="F77" s="17"/>
+      <c r="F77" s="17" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="78" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E78" s="17"/>
-      <c r="F78" s="17"/>
+      <c r="F78" s="17" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="79" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E79" s="17"/>
+      <c r="F79" s="17" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="80" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E80" s="17"/>
+      <c r="F80" s="17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="81" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E81" s="17"/>
+      <c r="F81" s="17" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="82" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E82" s="17"/>
+      <c r="F82" s="17" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="83" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E83" s="17"/>
+      <c r="F83" s="17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="84" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E84" s="17"/>
+      <c r="F84" s="17"/>
+    </row>
+    <row r="85" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E85" s="17"/>
+      <c r="F85" s="17"/>
+    </row>
+    <row r="86" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E86" s="17"/>
+      <c r="F86" s="17" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="87" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E87" s="17"/>
+      <c r="F87" s="17" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="88" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E88" s="17"/>
+      <c r="F88" s="17" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="89" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E89" s="17"/>
+      <c r="F89" s="17"/>
+    </row>
+    <row r="90" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E90" s="17"/>
+      <c r="F90" s="17"/>
+    </row>
+    <row r="91" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E91" s="17"/>
+      <c r="F91" s="17" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="92" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E92" s="17"/>
+      <c r="F92" s="17" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="93" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E93" s="17"/>
+      <c r="F93" s="17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="94" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E94" s="17"/>
+      <c r="F94" s="17" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="95" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E95" s="17"/>
+      <c r="F95" s="17" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="96" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E96" s="17"/>
+      <c r="F96" s="17" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="97" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E97" s="17"/>
+      <c r="F97" s="17" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="98" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E98" s="17"/>
+      <c r="F98" s="17" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="99" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E99" s="17"/>
+      <c r="F99" s="17" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="100" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E100" s="17"/>
+      <c r="F100" s="17" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="101" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E101" s="17"/>
+      <c r="F101" s="17" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="102" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E102" s="17"/>
+      <c r="F102" s="17" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="103" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E103" s="17"/>
+      <c r="F103" s="17" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="104" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E104" s="17"/>
+      <c r="F104" s="17" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="105" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E105" s="17"/>
+      <c r="F105" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="G105" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="106" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E106" s="17"/>
+      <c r="F106" s="17" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="107" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E107" s="17"/>
+      <c r="F107" s="17"/>
+    </row>
+    <row r="108" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E108" s="17"/>
+      <c r="F108" s="17"/>
+    </row>
+    <row r="109" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E109" s="17"/>
+      <c r="F109" s="17" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="110" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E110" s="17"/>
+      <c r="F110" s="17" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="111" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E111" s="17"/>
+      <c r="F111" s="17" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="112" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E112" s="17"/>
+      <c r="F112" s="17" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="113" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E113" s="17"/>
+      <c r="F113" s="17" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="114" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E114" s="17"/>
+      <c r="F114" s="17" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="115" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E115" s="17"/>
+      <c r="F115" s="17" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="116" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E116" s="17"/>
+      <c r="F116" s="17" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="117" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E117" s="17"/>
+      <c r="F117" s="17" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="118" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E118" s="17"/>
+      <c r="F118" s="17" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="119" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E119" s="17"/>
+      <c r="F119" s="17" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="120" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E120" s="17"/>
+      <c r="F120" s="17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="121" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E121" s="17"/>
+      <c r="F121" s="17"/>
+    </row>
+    <row r="122" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E122" s="17"/>
+      <c r="F122" s="17"/>
+    </row>
+    <row r="123" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E123" s="17"/>
+      <c r="F123" s="17"/>
+    </row>
+    <row r="124" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E124" s="17"/>
+      <c r="F124" s="17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="125" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E125" s="17"/>
+      <c r="F125" s="17" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="126" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E126" s="17"/>
+      <c r="F126" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="127" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E127" s="17"/>
+      <c r="F127" s="17" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="128" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E128" s="17"/>
+      <c r="F128" s="17" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="129" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E129" s="17"/>
+      <c r="F129" s="17" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="130" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E130" s="17"/>
+      <c r="F130" s="17" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="131" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E131" s="17"/>
+      <c r="F131" s="17" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="132" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E132" s="17"/>
+      <c r="F132" s="17" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="133" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E133" s="17"/>
+      <c r="F133" s="17" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="134" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E134" s="17"/>
+      <c r="F134" s="17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="135" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E135" s="17"/>
+      <c r="F135" s="17" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="136" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E136" s="17"/>
+      <c r="F136" s="17" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="137" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E137" s="17"/>
+      <c r="F137" s="17" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="138" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E138" s="17"/>
+      <c r="F138" s="17" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="139" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E139" s="17"/>
+      <c r="F139" s="17" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="140" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E140" s="17"/>
+      <c r="F140" s="17" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="141" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E141" s="17"/>
+      <c r="F141" s="17" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="142" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E142" s="17"/>
+      <c r="F142" s="17" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="143" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E143" s="17"/>
+      <c r="F143" s="17" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="144" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E144" s="17"/>
+      <c r="F144" s="17" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="145" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E145" s="17"/>
+      <c r="F145" s="17" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="146" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E146" s="17"/>
+      <c r="F146" s="17" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="147" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E147" s="17"/>
+      <c r="F147" s="17" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="148" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E148" s="17"/>
+      <c r="F148" s="17" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="149" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E149" s="17"/>
+      <c r="F149" s="17" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="150" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E150" s="17"/>
+      <c r="F150" s="17" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="151" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E151" s="17"/>
+      <c r="F151" s="17"/>
+    </row>
+    <row r="152" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E152" s="17"/>
+      <c r="F152" s="17"/>
+    </row>
+    <row r="153" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E153" s="17"/>
+      <c r="F153" s="17" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="154" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E154" s="17"/>
+      <c r="F154" s="17"/>
+    </row>
+    <row r="155" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E155" s="17"/>
+      <c r="F155" s="17"/>
+    </row>
+    <row r="156" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E156" s="17"/>
+      <c r="F156" s="17"/>
+    </row>
+    <row r="157" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E157" s="17"/>
+      <c r="F157" s="17"/>
+    </row>
+    <row r="158" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E158" s="17"/>
+      <c r="F158" s="17"/>
+    </row>
+    <row r="159" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E159" s="17"/>
+      <c r="F159" s="17"/>
+    </row>
+    <row r="160" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E160" s="17"/>
+      <c r="F160" s="17"/>
+    </row>
+    <row r="161" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E161" s="17"/>
+      <c r="F161" s="17"/>
+    </row>
+    <row r="162" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E162" s="17"/>
+      <c r="F162" s="17"/>
+    </row>
+    <row r="163" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E163" s="17"/>
+      <c r="F163" s="17"/>
+    </row>
+    <row r="164" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E164" s="17"/>
+      <c r="F164" s="17"/>
+    </row>
+    <row r="165" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E165" s="17"/>
+      <c r="F165" s="17"/>
+    </row>
+    <row r="166" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E166" s="17"/>
+      <c r="F166" s="17"/>
+    </row>
+    <row r="167" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E167" s="17"/>
+      <c r="F167" s="17"/>
+    </row>
+    <row r="168" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E168" s="17"/>
+      <c r="F168" s="17"/>
+    </row>
+    <row r="169" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E169" s="17"/>
+      <c r="F169" s="17"/>
+    </row>
+    <row r="170" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E170" s="17"/>
+      <c r="F170" s="17"/>
+    </row>
+    <row r="171" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E171" s="17"/>
+      <c r="F171" s="17"/>
+    </row>
+    <row r="172" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E172" s="17"/>
+      <c r="F172" s="17"/>
+    </row>
+    <row r="173" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E173" s="17"/>
+      <c r="F173" s="17"/>
+    </row>
+    <row r="174" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E174" s="17"/>
+      <c r="F174" s="17"/>
+    </row>
+    <row r="175" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E175" s="17"/>
+      <c r="F175" s="17"/>
+    </row>
+    <row r="176" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E176" s="17"/>
+      <c r="F176" s="17"/>
+    </row>
+    <row r="177" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E177" s="17"/>
+      <c r="F177" s="17"/>
+    </row>
+    <row r="178" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E178" s="17"/>
+      <c r="F178" s="17"/>
+    </row>
+    <row r="179" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E179" s="17"/>
+      <c r="F179" s="17"/>
+    </row>
+    <row r="180" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E180" s="17"/>
+      <c r="F180" s="17"/>
+    </row>
+    <row r="181" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E181" s="17"/>
+      <c r="F181" s="17"/>
+    </row>
+    <row r="182" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E182" s="17"/>
+      <c r="F182" s="17"/>
+    </row>
+    <row r="183" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E183" s="17"/>
+      <c r="F183" s="17"/>
+    </row>
+    <row r="184" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E184" s="17"/>
+      <c r="F184" s="17"/>
+    </row>
+    <row r="185" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E185" s="17"/>
+      <c r="F185" s="17"/>
+    </row>
+    <row r="186" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E186" s="17"/>
+      <c r="F186" s="17"/>
+    </row>
+    <row r="187" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E187" s="17"/>
+      <c r="F187" s="17"/>
+    </row>
+    <row r="188" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E188" s="17"/>
+      <c r="F188" s="17"/>
+    </row>
+    <row r="189" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E189" s="17"/>
+      <c r="F189" s="17"/>
+    </row>
+    <row r="190" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E190" s="17"/>
+      <c r="F190" s="17"/>
+    </row>
+    <row r="191" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E191" s="17"/>
+      <c r="F191" s="17"/>
+    </row>
+    <row r="192" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E192" s="17"/>
+      <c r="F192" s="17"/>
+    </row>
+    <row r="193" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E193" s="17"/>
+      <c r="F193" s="17"/>
+    </row>
+    <row r="194" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E194" s="17"/>
+      <c r="F194" s="17"/>
+    </row>
+    <row r="195" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E195" s="17"/>
+      <c r="F195" s="17"/>
+    </row>
+    <row r="196" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E196" s="17"/>
+      <c r="F196" s="17"/>
+    </row>
+    <row r="197" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E197" s="17"/>
+      <c r="F197" s="17"/>
+    </row>
+    <row r="198" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E198" s="17"/>
+      <c r="F198" s="17"/>
+    </row>
+    <row r="199" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E199" s="17"/>
+      <c r="F199" s="17"/>
+    </row>
+    <row r="200" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E200" s="17"/>
+      <c r="F200" s="17"/>
+    </row>
+    <row r="201" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E201" s="17"/>
+      <c r="F201" s="17"/>
+    </row>
+    <row r="202" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E202" s="17"/>
+      <c r="F202" s="17"/>
+    </row>
+    <row r="203" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E203" s="17"/>
+      <c r="F203" s="17"/>
+    </row>
+    <row r="204" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E204" s="17"/>
+      <c r="F204" s="17"/>
+    </row>
+    <row r="205" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E205" s="17"/>
+      <c r="F205" s="17"/>
+    </row>
+    <row r="206" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E206" s="17"/>
+      <c r="F206" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1828,4 +2763,22 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD312072-87FE-40B5-A445-1591614412BD}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="123.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36EEA3B-BD7C-4CFD-AF3A-FBA14C97FE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A5FEF8-CE3A-4E6E-B5F7-4600DCCBED95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Stack" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="345">
   <si>
     <t>NextJS</t>
   </si>
@@ -856,6 +856,441 @@
   <si>
     <t>Database fundamentals</t>
   </si>
+  <si>
+    <t>Avalability  : Will be able to access data now and when I need it.  Four 9 is conider as goot 99.99%</t>
+  </si>
+  <si>
+    <t>Durability : Data will be available after 100 years  : eleven 9 considera ad good durability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read-after-write consistency : </t>
+  </si>
+  <si>
+    <t>Eventtual consistency : Asynchrous replication.    Used when scalability is more important than data integrity</t>
+  </si>
+  <si>
+    <t>Database snapshots</t>
+  </si>
+  <si>
+    <t>Database Terminology RTO  &amp; RPO</t>
+  </si>
+  <si>
+    <t>Questions on RTO and RPO</t>
+  </si>
+  <si>
+    <t>Reporting and Analitics Application</t>
+  </si>
+  <si>
+    <t>Consistency</t>
+  </si>
+  <si>
+    <t>Database Categories</t>
+  </si>
+  <si>
+    <t>Relational Database  - OLTP</t>
+  </si>
+  <si>
+    <t>Relational Database  - OLAP</t>
+  </si>
+  <si>
+    <t>Document Database</t>
+  </si>
+  <si>
+    <t>Key-Value</t>
+  </si>
+  <si>
+    <t>Graph</t>
+  </si>
+  <si>
+    <t>In-memory database</t>
+  </si>
+  <si>
+    <t>Amazon Arora</t>
+  </si>
+  <si>
+    <t>RDS Scaling</t>
+  </si>
+  <si>
+    <t>RDS Operations</t>
+  </si>
+  <si>
+    <t>Security and Encription</t>
+  </si>
+  <si>
+    <t>Amazon Dynamo DB</t>
+  </si>
+  <si>
+    <t>Dynamo DB Tables</t>
+  </si>
+  <si>
+    <t>Dynamo DB Keys</t>
+  </si>
+  <si>
+    <t>Dynamo DB Index</t>
+  </si>
+  <si>
+    <t>Dynamo DB Query vs Scan</t>
+  </si>
+  <si>
+    <t>Dynamo DB Consistency Levels</t>
+  </si>
+  <si>
+    <t>Dynamo DB Read/Write Capacity Mode</t>
+  </si>
+  <si>
+    <t>Dynamo DB Read/Write Capacity Used</t>
+  </si>
+  <si>
+    <t>Dynamp DB Operations</t>
+  </si>
+  <si>
+    <t>Dynamo DB - IAM and Encryption</t>
+  </si>
+  <si>
+    <t>Dynamo DB Accelerator  DAX</t>
+  </si>
+  <si>
+    <t>Amazon ElasticCache</t>
+  </si>
+  <si>
+    <t>Amazon ElasticCache for Redis</t>
+  </si>
+  <si>
+    <t>Amazon ElasticCache for Redis - Cluster</t>
+  </si>
+  <si>
+    <t>ElasticCache Redis - Backup and snapshot</t>
+  </si>
+  <si>
+    <t>Amazon ElasticCache for Memcached</t>
+  </si>
+  <si>
+    <t>Amazon ElasticCache for Memcached -  Limistations</t>
+  </si>
+  <si>
+    <t>Memcached vs Redis</t>
+  </si>
+  <si>
+    <t>CloudTrail, Config and CloudWatch</t>
+  </si>
+  <si>
+    <t>AWS Cloud Trail</t>
+  </si>
+  <si>
+    <t>AWS Config</t>
+  </si>
+  <si>
+    <t>AWS Config Rules</t>
+  </si>
+  <si>
+    <t>AWS Config + AWS Cloud Trail</t>
+  </si>
+  <si>
+    <t>Monitoring AWS with Amazon CloudWatch</t>
+  </si>
+  <si>
+    <t>CloudWatch Logs</t>
+  </si>
+  <si>
+    <t>Amazon Cloud watch Alarms</t>
+  </si>
+  <si>
+    <t>Amazon Cloud watch Dash boards</t>
+  </si>
+  <si>
+    <t>Amzon CloudWatch Events</t>
+  </si>
+  <si>
+    <t>Decoupling Applications with SQS , SNS and MQ</t>
+  </si>
+  <si>
+    <t>Synchronous Communication</t>
+  </si>
+  <si>
+    <t>Asynchronous Communication - Decoupled</t>
+  </si>
+  <si>
+    <t>Asynchronous Communication - Scale-up</t>
+  </si>
+  <si>
+    <t>Asynchronous Communication - Pull Model SQS</t>
+  </si>
+  <si>
+    <t>Scaling or Scalability</t>
+  </si>
+  <si>
+    <t>Reliability</t>
+  </si>
+  <si>
+    <t>Asynchronous Communication - PUSH Model SNS</t>
+  </si>
+  <si>
+    <t>Simple Queueing Service.</t>
+  </si>
+  <si>
+    <t>Standard and FIFO Queues</t>
+  </si>
+  <si>
+    <t>throughput</t>
+  </si>
+  <si>
+    <t>Sending and reciving a SQS Message - Best case senario</t>
+  </si>
+  <si>
+    <t>Simple Queueing Service Lifecycle of a message</t>
+  </si>
+  <si>
+    <t>SQS Auto scaling</t>
+  </si>
+  <si>
+    <t>SQS Queue - Important configuration</t>
+  </si>
+  <si>
+    <t>Simple Queuing Service Security</t>
+  </si>
+  <si>
+    <t>Amaznon Simple Notification Service. (SNS)</t>
+  </si>
+  <si>
+    <t>Amazon MQ</t>
+  </si>
+  <si>
+    <t>Routing and Content Delivery</t>
+  </si>
+  <si>
+    <t>Content Delivery Network</t>
+  </si>
+  <si>
+    <t>Amazon cloudFront</t>
+  </si>
+  <si>
+    <t>Amazon Cloud Front Distribution</t>
+  </si>
+  <si>
+    <t>Amazon Cloud Front - Cache Behaviors</t>
+  </si>
+  <si>
+    <t>Amazon Cloud Front - Private Content</t>
+  </si>
+  <si>
+    <t>Amazon Cloud Front - Signed URLs and Cookies</t>
+  </si>
+  <si>
+    <t>Amazon Cloud Front - Origin Access Identities (OAI)</t>
+  </si>
+  <si>
+    <t>Bucket Policy - S3 ONLY through Cloud Front</t>
+  </si>
+  <si>
+    <t>Route 53</t>
+  </si>
+  <si>
+    <t>Route 53 DNS</t>
+  </si>
+  <si>
+    <t>Route 53 Hosted Zone</t>
+  </si>
+  <si>
+    <t>Standard DNS Records</t>
+  </si>
+  <si>
+    <t>Route 53 Specific Extention  - Alias records</t>
+  </si>
+  <si>
+    <t>Route 53 - Routing</t>
+  </si>
+  <si>
+    <t>Route 53 Routing Policies</t>
+  </si>
+  <si>
+    <t>Route 53 Routing Policies - Geolocations</t>
+  </si>
+  <si>
+    <t>Need for AWS Global accelerator</t>
+  </si>
+  <si>
+    <t>ETL AND Big Data RedShift and EMR</t>
+  </si>
+  <si>
+    <t>Amazon Redshift</t>
+  </si>
+  <si>
+    <t>Redshift Cluster</t>
+  </si>
+  <si>
+    <t>Redshift Design tables</t>
+  </si>
+  <si>
+    <t>Redshift workload Management</t>
+  </si>
+  <si>
+    <t>Redshift Security</t>
+  </si>
+  <si>
+    <t>Redshift Operations</t>
+  </si>
+  <si>
+    <t>Redshift spectrum</t>
+  </si>
+  <si>
+    <t>Amazon EMR - Elastic map reducer</t>
+  </si>
+  <si>
+    <t>Handling data Streams</t>
+  </si>
+  <si>
+    <t>Amazon Simple Workflow Service  (SWS)</t>
+  </si>
+  <si>
+    <t>Streaming data</t>
+  </si>
+  <si>
+    <t>S3 Notifications</t>
+  </si>
+  <si>
+    <t>DynamoDB Streams</t>
+  </si>
+  <si>
+    <t>Amazon Kinesis</t>
+  </si>
+  <si>
+    <t>AWS Data Lakes</t>
+  </si>
+  <si>
+    <t>AWS Data Lakes -Storage and Ingestion</t>
+  </si>
+  <si>
+    <t>Amazon S3 Query in Place</t>
+  </si>
+  <si>
+    <t>More ServerLess</t>
+  </si>
+  <si>
+    <t>Serverless Option Compute</t>
+  </si>
+  <si>
+    <t>AWS LAMBDA</t>
+  </si>
+  <si>
+    <t>AWS LAMBDA@EDGE</t>
+  </si>
+  <si>
+    <t>AWS FarGate</t>
+  </si>
+  <si>
+    <t>Serverless Options  - Database</t>
+  </si>
+  <si>
+    <t>Serverlsess Option - API Proxy and Orchestration</t>
+  </si>
+  <si>
+    <t>Serverlsess Option - Application Integration and Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serverlsess Option - other </t>
+  </si>
+  <si>
+    <t>Serverless use case 1 - Full stack web application</t>
+  </si>
+  <si>
+    <t>Serverless use case 2 - Real time event Processing</t>
+  </si>
+  <si>
+    <t>Amaznon API Gateway Features</t>
+  </si>
+  <si>
+    <t>\</t>
+  </si>
+  <si>
+    <t>Amaznon API Gateway - Authentication and Authorization approaches</t>
+  </si>
+  <si>
+    <t>Amaznon Cognito</t>
+  </si>
+  <si>
+    <t>Amazon congnito Pool</t>
+  </si>
+  <si>
+    <t>Amazon congnito identity pool</t>
+  </si>
+  <si>
+    <t>Amazon congnito - how it works</t>
+  </si>
+  <si>
+    <t>Lambda@edge</t>
+  </si>
+  <si>
+    <t>Serverless Application Model</t>
+  </si>
+  <si>
+    <t>AWS AppSync</t>
+  </si>
+  <si>
+    <t>AWS Step Function</t>
+  </si>
+  <si>
+    <t>Extend and secure  your VPC'S  In AWS and to on premises</t>
+  </si>
+  <si>
+    <t>VPC Peering</t>
+  </si>
+  <si>
+    <t>vpc Endpoints</t>
+  </si>
+  <si>
+    <t>VPC Flowlogs</t>
+  </si>
+  <si>
+    <t>Troubleshooting using VPC Flow Logs</t>
+  </si>
+  <si>
+    <t>AWS and On-Premises  - Overview</t>
+  </si>
+  <si>
+    <t>AWS Managed VPN</t>
+  </si>
+  <si>
+    <t>AWS Direct connect</t>
+  </si>
+  <si>
+    <t>AWS Direct connect Plus VPN</t>
+  </si>
+  <si>
+    <t>Software VPN</t>
+  </si>
+  <si>
+    <t>AWS VPN CloudHub</t>
+  </si>
+  <si>
+    <t>VPN Connection -Review</t>
+  </si>
+  <si>
+    <t>AWS Trasit Gateway</t>
+  </si>
+  <si>
+    <t>Moving data between aws and onpremise</t>
+  </si>
+  <si>
+    <t>Amazon s3 Trasfer Accleration</t>
+  </si>
+  <si>
+    <t>aws snowball</t>
+  </si>
+  <si>
+    <t>AWS Snowmobile</t>
+  </si>
+  <si>
+    <t>AWS Data Sync Transfer File storeage to cloud</t>
+  </si>
+  <si>
+    <t>AWS Schema conversion tools</t>
+  </si>
+  <si>
+    <t>Database Migration service vs schema conversion tools</t>
+  </si>
+  <si>
+    <t>Powerschool shares</t>
+  </si>
 </sst>
 </file>
 
@@ -993,7 +1428,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1018,6 +1453,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1526,7 +1967,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD904FA-0FAD-46CD-8773-AE594AFC6DAB}">
-  <dimension ref="E10:G206"/>
+  <dimension ref="B10:G321"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="8.7265625" customWidth="1"/>
@@ -2226,139 +2667,207 @@
     </row>
     <row r="154" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E154" s="17"/>
-      <c r="F154" s="17"/>
+      <c r="F154" s="17" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="155" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E155" s="17"/>
-      <c r="F155" s="17"/>
+      <c r="F155" s="17" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="156" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E156" s="17"/>
-      <c r="F156" s="17"/>
+      <c r="F156" s="17" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="157" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E157" s="17"/>
-      <c r="F157" s="17"/>
+      <c r="F157" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="158" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E158" s="17"/>
-      <c r="F158" s="17"/>
+      <c r="F158" s="17" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="159" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E159" s="17"/>
-      <c r="F159" s="17"/>
+      <c r="F159" s="17" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="160" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E160" s="17"/>
-      <c r="F160" s="17"/>
+      <c r="F160" s="17" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="161" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E161" s="17"/>
-      <c r="F161" s="17"/>
+      <c r="F161" s="17" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="162" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E162" s="17"/>
-      <c r="F162" s="17"/>
+      <c r="F162" s="17" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="163" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E163" s="17"/>
-      <c r="F163" s="17"/>
+      <c r="F163" s="17" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="164" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E164" s="17"/>
-      <c r="F164" s="17"/>
+      <c r="F164" s="17" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="165" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E165" s="17"/>
-      <c r="F165" s="17"/>
+      <c r="F165" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="166" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E166" s="17"/>
-      <c r="F166" s="17"/>
+      <c r="F166" s="17" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="167" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E167" s="17"/>
-      <c r="F167" s="17"/>
+      <c r="F167" s="17" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="168" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E168" s="17"/>
-      <c r="F168" s="17"/>
+      <c r="F168" s="17" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="169" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E169" s="17"/>
-      <c r="F169" s="17"/>
+      <c r="F169" s="17" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="170" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E170" s="17"/>
-      <c r="F170" s="17"/>
+      <c r="F170" s="17" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="171" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E171" s="17"/>
-      <c r="F171" s="17"/>
+      <c r="F171" s="17" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="172" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E172" s="17"/>
-      <c r="F172" s="17"/>
+      <c r="F172" s="17" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="173" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E173" s="17"/>
-      <c r="F173" s="17"/>
+      <c r="F173" s="17" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="174" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E174" s="17"/>
-      <c r="F174" s="17"/>
+      <c r="F174" s="17" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="175" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E175" s="17"/>
-      <c r="F175" s="17"/>
+      <c r="F175" s="17" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="176" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E176" s="17"/>
-      <c r="F176" s="17"/>
+      <c r="F176" s="17" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="177" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E177" s="17"/>
-      <c r="F177" s="17"/>
+      <c r="F177" s="17" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="178" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E178" s="17"/>
-      <c r="F178" s="17"/>
+      <c r="F178" s="17" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="179" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E179" s="17"/>
-      <c r="F179" s="17"/>
+      <c r="F179" s="17" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="180" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E180" s="17"/>
-      <c r="F180" s="17"/>
+      <c r="F180" s="17" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="181" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E181" s="17"/>
-      <c r="F181" s="17"/>
+      <c r="F181" s="17" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="182" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E182" s="17"/>
-      <c r="F182" s="17"/>
+      <c r="F182" s="17" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="183" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E183" s="17"/>
-      <c r="F183" s="17"/>
+      <c r="F183" s="17" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="184" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E184" s="17"/>
-      <c r="F184" s="17"/>
+      <c r="F184" s="17" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="185" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E185" s="17"/>
-      <c r="F185" s="17"/>
+      <c r="F185" s="17" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="186" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E186" s="17"/>
-      <c r="F186" s="17"/>
+      <c r="F186" s="17" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="187" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E187" s="17"/>
-      <c r="F187" s="17"/>
+      <c r="F187" s="17" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="188" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E188" s="17"/>
@@ -2374,69 +2883,878 @@
     </row>
     <row r="191" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E191" s="17"/>
-      <c r="F191" s="17"/>
+      <c r="F191" s="17" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="192" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E192" s="17"/>
-      <c r="F192" s="17"/>
-    </row>
-    <row r="193" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F192" s="17" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="193" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E193" s="17"/>
-      <c r="F193" s="17"/>
-    </row>
-    <row r="194" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F193" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="194" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E194" s="17"/>
-      <c r="F194" s="17"/>
-    </row>
-    <row r="195" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F194" s="17" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="195" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E195" s="17"/>
-      <c r="F195" s="17"/>
-    </row>
-    <row r="196" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F195" s="17" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="196" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E196" s="17"/>
-      <c r="F196" s="17"/>
-    </row>
-    <row r="197" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F196" s="17" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="197" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E197" s="17"/>
-      <c r="F197" s="17"/>
-    </row>
-    <row r="198" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F197" s="17" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="198" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E198" s="17"/>
-      <c r="F198" s="17"/>
-    </row>
-    <row r="199" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F198" s="17" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="199" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E199" s="17"/>
-      <c r="F199" s="17"/>
-    </row>
-    <row r="200" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F199" s="17" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="200" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E200" s="17"/>
-      <c r="F200" s="17"/>
-    </row>
-    <row r="201" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F200" s="17" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="201" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E201" s="17"/>
       <c r="F201" s="17"/>
     </row>
-    <row r="202" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="202" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E202" s="17"/>
       <c r="F202" s="17"/>
     </row>
-    <row r="203" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="203" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E203" s="17"/>
-      <c r="F203" s="17"/>
-    </row>
-    <row r="204" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F203" s="17" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="204" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E204" s="17"/>
-      <c r="F204" s="17"/>
-    </row>
-    <row r="205" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F204" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="G204" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="205" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E205" s="17"/>
-      <c r="F205" s="17"/>
-    </row>
-    <row r="206" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F205" s="17" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="206" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E206" s="17"/>
-      <c r="F206" s="17"/>
+      <c r="F206" s="17" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="207" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="F207" s="17" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="208" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="B208" s="4"/>
+      <c r="C208" s="4"/>
+      <c r="D208" s="4"/>
+      <c r="E208" s="4"/>
+      <c r="F208" s="17" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="209" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B209" s="4"/>
+      <c r="C209" s="4"/>
+      <c r="D209" s="4"/>
+      <c r="E209" s="4"/>
+      <c r="F209" s="18" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="210" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B210" s="4"/>
+      <c r="C210" s="4"/>
+      <c r="D210" s="4"/>
+      <c r="E210" s="4"/>
+      <c r="F210" s="18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="211" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B211" s="4"/>
+      <c r="C211" s="4"/>
+      <c r="D211" s="4"/>
+      <c r="E211" s="4"/>
+      <c r="F211" s="18" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="212" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B212" s="4"/>
+      <c r="C212" s="4"/>
+      <c r="D212" s="4"/>
+      <c r="E212" s="4"/>
+      <c r="F212" s="18" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="213" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B213" s="4"/>
+      <c r="C213" s="4"/>
+      <c r="D213" s="4"/>
+      <c r="E213" s="4"/>
+      <c r="F213" s="18" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="214" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B214" s="4"/>
+      <c r="C214" s="4"/>
+      <c r="D214" s="4"/>
+      <c r="E214" s="4"/>
+      <c r="F214" s="18" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="215" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B215" s="4"/>
+      <c r="C215" s="4"/>
+      <c r="D215" s="4"/>
+      <c r="E215" s="4"/>
+      <c r="F215" s="18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="216" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B216" s="4"/>
+      <c r="C216" s="4"/>
+      <c r="D216" s="4"/>
+      <c r="E216" s="4"/>
+      <c r="F216" s="18" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="217" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B217" s="4"/>
+      <c r="C217" s="4"/>
+      <c r="D217" s="4"/>
+      <c r="E217" s="4"/>
+      <c r="F217" s="18" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="218" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B218" s="4"/>
+      <c r="C218" s="4"/>
+      <c r="D218" s="4"/>
+      <c r="E218" s="4"/>
+      <c r="F218" s="18"/>
+    </row>
+    <row r="219" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B219" s="4"/>
+      <c r="C219" s="4"/>
+      <c r="D219" s="4"/>
+      <c r="E219" s="4"/>
+      <c r="F219" s="18"/>
+    </row>
+    <row r="220" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B220" s="4"/>
+      <c r="C220" s="4"/>
+      <c r="D220" s="4"/>
+      <c r="E220" s="4"/>
+      <c r="F220" s="18"/>
+    </row>
+    <row r="221" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B221" s="4"/>
+      <c r="C221" s="4"/>
+      <c r="D221" s="4"/>
+      <c r="E221" s="4"/>
+      <c r="F221" s="18" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="222" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B222" s="4"/>
+      <c r="C222" s="4"/>
+      <c r="D222" s="4"/>
+      <c r="E222" s="4"/>
+      <c r="F222" s="18" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="223" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B223" s="4"/>
+      <c r="C223" s="4"/>
+      <c r="D223" s="4"/>
+      <c r="E223" s="4"/>
+      <c r="F223" s="18" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="224" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B224" s="4"/>
+      <c r="C224" s="4"/>
+      <c r="D224" s="4"/>
+      <c r="E224" s="4"/>
+      <c r="F224" s="18" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="225" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B225" s="4"/>
+      <c r="C225" s="4"/>
+      <c r="D225" s="4"/>
+      <c r="E225" s="4"/>
+      <c r="F225" s="18" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="226" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B226" s="4"/>
+      <c r="C226" s="4"/>
+      <c r="D226" s="4"/>
+      <c r="E226" s="4"/>
+      <c r="F226" s="18" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="227" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B227" s="4"/>
+      <c r="C227" s="4"/>
+      <c r="D227" s="4"/>
+      <c r="E227" s="4"/>
+      <c r="F227" s="18" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="228" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B228" s="4"/>
+      <c r="C228" s="4"/>
+      <c r="D228" s="4"/>
+      <c r="E228" s="4"/>
+      <c r="F228" s="18" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="229" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B229" s="4"/>
+      <c r="C229" s="4"/>
+      <c r="D229" s="4"/>
+      <c r="E229" s="4"/>
+      <c r="F229" s="18" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="230" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B230" s="4"/>
+      <c r="C230" s="4"/>
+      <c r="D230" s="4"/>
+      <c r="E230" s="4"/>
+      <c r="F230" s="18"/>
+    </row>
+    <row r="231" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B231" s="4"/>
+      <c r="C231" s="4"/>
+      <c r="D231" s="4"/>
+      <c r="E231" s="4"/>
+      <c r="F231" s="18"/>
+    </row>
+    <row r="232" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B232" s="4"/>
+      <c r="C232" s="4"/>
+      <c r="D232" s="4"/>
+      <c r="E232" s="4"/>
+      <c r="F232" s="18"/>
+    </row>
+    <row r="233" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B233" s="4"/>
+      <c r="C233" s="4"/>
+      <c r="D233" s="4"/>
+      <c r="E233" s="4"/>
+      <c r="F233" s="18"/>
+    </row>
+    <row r="234" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B234" s="4"/>
+      <c r="C234" s="4"/>
+      <c r="D234" s="4"/>
+      <c r="E234" s="4"/>
+      <c r="F234" s="18" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="235" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B235" s="4"/>
+      <c r="C235" s="4"/>
+      <c r="D235" s="4"/>
+      <c r="E235" s="4"/>
+      <c r="F235" s="18" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="236" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B236" s="4"/>
+      <c r="C236" s="4"/>
+      <c r="D236" s="4"/>
+      <c r="E236" s="4"/>
+      <c r="F236" s="18" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="237" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B237" s="4"/>
+      <c r="C237" s="4"/>
+      <c r="D237" s="4"/>
+      <c r="E237" s="4"/>
+      <c r="F237" s="18" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="238" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B238" s="4"/>
+      <c r="C238" s="4"/>
+      <c r="D238" s="4"/>
+      <c r="E238" s="4"/>
+      <c r="F238" s="18" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="239" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B239" s="4"/>
+      <c r="C239" s="4"/>
+      <c r="D239" s="4"/>
+      <c r="E239" s="4"/>
+      <c r="F239" s="18" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="240" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B240" s="4"/>
+      <c r="C240" s="4"/>
+      <c r="D240" s="4"/>
+      <c r="E240" s="4"/>
+      <c r="F240" s="18" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="241" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B241" s="4"/>
+      <c r="C241" s="4"/>
+      <c r="D241" s="4"/>
+      <c r="E241" s="4"/>
+      <c r="F241" s="18" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="242" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B242" s="4"/>
+      <c r="C242" s="4"/>
+      <c r="D242" s="4"/>
+      <c r="E242" s="4"/>
+      <c r="F242" s="18" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="243" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B243" s="4"/>
+      <c r="C243" s="4"/>
+      <c r="D243" s="4"/>
+      <c r="E243" s="4"/>
+      <c r="F243" s="18"/>
+    </row>
+    <row r="244" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B244" s="4"/>
+      <c r="C244" s="4"/>
+      <c r="D244" s="4"/>
+      <c r="E244" s="4"/>
+      <c r="F244" s="18"/>
+    </row>
+    <row r="245" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B245" s="4"/>
+      <c r="C245" s="4"/>
+      <c r="D245" s="4"/>
+      <c r="E245" s="4"/>
+      <c r="F245" s="18"/>
+    </row>
+    <row r="246" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B246" s="4"/>
+      <c r="C246" s="4"/>
+      <c r="D246" s="4"/>
+      <c r="E246" s="4"/>
+      <c r="F246" s="18" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="247" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B247" s="4"/>
+      <c r="C247" s="4"/>
+      <c r="D247" s="4"/>
+      <c r="E247" s="4"/>
+      <c r="F247" s="18" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="248" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B248" s="4"/>
+      <c r="C248" s="4"/>
+      <c r="D248" s="4"/>
+      <c r="E248" s="4"/>
+      <c r="F248" s="18" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="249" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B249" s="4"/>
+      <c r="C249" s="4"/>
+      <c r="D249" s="4"/>
+      <c r="E249" s="4"/>
+      <c r="F249" s="18" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="250" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B250" s="4"/>
+      <c r="C250" s="4"/>
+      <c r="D250" s="4"/>
+      <c r="E250" s="4"/>
+      <c r="F250" s="18" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="251" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B251" s="4"/>
+      <c r="C251" s="4"/>
+      <c r="D251" s="4"/>
+      <c r="E251" s="4"/>
+      <c r="F251" s="18" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="252" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B252" s="4"/>
+      <c r="C252" s="4"/>
+      <c r="D252" s="4"/>
+      <c r="E252" s="4"/>
+      <c r="F252" s="18" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="253" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B253" s="4"/>
+      <c r="C253" s="4"/>
+      <c r="D253" s="4"/>
+      <c r="E253" s="4"/>
+      <c r="F253" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="254" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B254" s="4"/>
+      <c r="C254" s="4"/>
+      <c r="D254" s="4"/>
+      <c r="E254" s="4"/>
+      <c r="F254" s="18" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="255" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B255" s="4"/>
+      <c r="C255" s="4"/>
+      <c r="D255" s="4"/>
+      <c r="E255" s="4"/>
+      <c r="F255" s="18"/>
+    </row>
+    <row r="256" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B256" s="4"/>
+      <c r="C256" s="4"/>
+      <c r="D256" s="4"/>
+      <c r="E256" s="4"/>
+      <c r="F256" s="18"/>
+    </row>
+    <row r="257" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B257" s="4"/>
+      <c r="C257" s="4"/>
+      <c r="D257" s="4"/>
+      <c r="E257" s="4"/>
+      <c r="F257" s="18"/>
+    </row>
+    <row r="258" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B258" s="4"/>
+      <c r="C258" s="4"/>
+      <c r="D258" s="4"/>
+      <c r="E258" s="4"/>
+      <c r="F258" s="18" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="259" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B259" s="4"/>
+      <c r="C259" s="4"/>
+      <c r="D259" s="4"/>
+      <c r="E259" s="4"/>
+      <c r="F259" s="18"/>
+    </row>
+    <row r="260" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B260" s="4"/>
+      <c r="C260" s="4"/>
+      <c r="D260" s="4"/>
+      <c r="E260" s="4"/>
+      <c r="F260" s="18"/>
+    </row>
+    <row r="261" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B261" s="4"/>
+      <c r="C261" s="4"/>
+      <c r="D261" s="4"/>
+      <c r="E261" s="4"/>
+      <c r="F261" s="18" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="262" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B262" s="4"/>
+      <c r="C262" s="4"/>
+      <c r="D262" s="4"/>
+      <c r="E262" s="4"/>
+      <c r="F262" s="18" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="263" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B263" s="4"/>
+      <c r="C263" s="4"/>
+      <c r="D263" s="4"/>
+      <c r="E263" s="4"/>
+      <c r="F263" s="18" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="264" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B264" s="4"/>
+      <c r="C264" s="4"/>
+      <c r="D264" s="4"/>
+      <c r="E264" s="4"/>
+      <c r="F264" s="18" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="265" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B265" s="4"/>
+      <c r="C265" s="4"/>
+      <c r="D265" s="4"/>
+      <c r="E265" s="4"/>
+      <c r="F265" s="18" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="266" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B266" s="4"/>
+      <c r="C266" s="4"/>
+      <c r="D266" s="4"/>
+      <c r="E266" s="4"/>
+      <c r="F266" s="18"/>
+    </row>
+    <row r="267" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B267" s="4"/>
+      <c r="C267" s="4"/>
+      <c r="D267" s="4"/>
+      <c r="E267" s="4"/>
+      <c r="F267" s="18"/>
+    </row>
+    <row r="268" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B268" s="4"/>
+      <c r="C268" s="4"/>
+      <c r="D268" s="4"/>
+      <c r="E268" s="4"/>
+      <c r="F268" s="18" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="269" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B269" s="4"/>
+      <c r="C269" s="4"/>
+      <c r="D269" s="4"/>
+      <c r="E269" s="4"/>
+      <c r="F269" s="18" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="270" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B270" s="4"/>
+      <c r="C270" s="4"/>
+      <c r="D270" s="4"/>
+      <c r="E270" s="4"/>
+      <c r="F270" s="18" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="271" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B271" s="4"/>
+      <c r="C271" s="4"/>
+      <c r="D271" s="4"/>
+      <c r="E271" s="4"/>
+      <c r="F271" s="18"/>
+    </row>
+    <row r="272" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B272" s="4"/>
+      <c r="C272" s="4"/>
+      <c r="D272" s="4"/>
+      <c r="E272" s="4"/>
+      <c r="F272" s="18"/>
+    </row>
+    <row r="273" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B273" s="4"/>
+      <c r="C273" s="4"/>
+      <c r="D273" s="4"/>
+      <c r="E273" s="4"/>
+      <c r="F273" s="18"/>
+    </row>
+    <row r="274" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B274" s="4"/>
+      <c r="C274" s="4"/>
+      <c r="D274" s="4"/>
+      <c r="E274" s="4"/>
+      <c r="F274" s="18" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="275" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B275" s="4"/>
+      <c r="C275" s="4"/>
+      <c r="D275" s="4"/>
+      <c r="E275" s="4"/>
+      <c r="F275" s="18" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="276" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F276" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="277" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F277" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="278" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F278" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="279" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F279" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="280" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F280" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="281" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F281" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="282" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F282" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="283" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F283" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="284" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F284" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="285" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F285" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="286" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F286" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="G286" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="287" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F287" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="288" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F288" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="289" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F289" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="290" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F290" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="291" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F291" s="19" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="292" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F292" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="293" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F293" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="294" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F294" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="298" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F298" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="299" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F299" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="300" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F300" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="301" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F301" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="302" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F302" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="303" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F303" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="304" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F304" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="305" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F305" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="306" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F306" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="307" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F307" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="308" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F308" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="309" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F309" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="310" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F310" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="315" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F315" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="316" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F316" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="317" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F317" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="318" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F318" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="319" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F319" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="320" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F320" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="321" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F321" s="2" t="s">
+        <v>343</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F291" r:id="rId1" xr:uid="{5B4939E1-0F97-4A79-B4A5-1D09873EBA1F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2675,7 +3993,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="98.7265625" style="4" customWidth="1"/>
@@ -2755,6 +4073,11 @@
     <row r="31" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A31" s="4" t="s">
         <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A33" s="4" t="s">
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -2767,7 +4090,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD312072-87FE-40B5-A445-1591614412BD}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="123.36328125" customWidth="1"/>
@@ -2778,6 +4101,46 @@
         <v>109</v>
       </c>
     </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>258</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A5FEF8-CE3A-4E6E-B5F7-4600DCCBED95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF87F28-FC4F-4CF9-9C17-AC7D7F671F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Stack" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="389">
   <si>
     <t>NextJS</t>
   </si>
@@ -1291,12 +1291,144 @@
   <si>
     <t>Powerschool shares</t>
   </si>
+  <si>
+    <t>DynPro Documents</t>
+  </si>
+  <si>
+    <t>AWS Certified Solutions Architect Associate - SAA C03</t>
+  </si>
+  <si>
+    <t>Cloud Migration Approaches</t>
+  </si>
+  <si>
+    <t>Dev Ops</t>
+  </si>
+  <si>
+    <t>Dev Ops - CI, CD</t>
+  </si>
+  <si>
+    <t>Dev Ops - CI, CD Tools</t>
+  </si>
+  <si>
+    <t>Dev Ops - IAAC</t>
+  </si>
+  <si>
+    <t>AWS CloudFormation - Advantages</t>
+  </si>
+  <si>
+    <t>AWS CloudFormation - Intraduction</t>
+  </si>
+  <si>
+    <t>AWS CloudFormation - Terminology</t>
+  </si>
+  <si>
+    <t>AWS CloudFormation - Important template elements</t>
+  </si>
+  <si>
+    <t>AWS CloudFormation - Mapping Example</t>
+  </si>
+  <si>
+    <t>AWS CloudFormation - Remember</t>
+  </si>
+  <si>
+    <t>CloudFormation vs EBS</t>
+  </si>
+  <si>
+    <t>AWS OpsWorks - Configuration Management</t>
+  </si>
+  <si>
+    <t>Fault Tolerance</t>
+  </si>
+  <si>
+    <t>AWS Certification FAQ'S</t>
+  </si>
+  <si>
+    <t>Zero chance of Failure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Security Service </t>
+  </si>
+  <si>
+    <t>AWS Shield</t>
+  </si>
+  <si>
+    <t>AWS Shield Standard &amp; Advanced</t>
+  </si>
+  <si>
+    <t>AWS WAF - Web Application Firewall</t>
+  </si>
+  <si>
+    <t>AWS System Manager Parameter Store</t>
+  </si>
+  <si>
+    <t>AWS Secrets Manager</t>
+  </si>
+  <si>
+    <t>Amazon Macie</t>
+  </si>
+  <si>
+    <t>AWS Single Sign On</t>
+  </si>
+  <si>
+    <t>More security Services in AWS</t>
+  </si>
+  <si>
+    <t>More AWS Services</t>
+  </si>
+  <si>
+    <t>AWS Organisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Organisations Features </t>
+  </si>
+  <si>
+    <t>AWS Resource Access Manager</t>
+  </si>
+  <si>
+    <t>One Enterprise - Many AWS accounts  -  AWS  Control Tower</t>
+  </si>
+  <si>
+    <t>AWS trusted advisor</t>
+  </si>
+  <si>
+    <t>AWS trusted advisor - Recommendations</t>
+  </si>
+  <si>
+    <t>AWS Service Quotas</t>
+  </si>
+  <si>
+    <t>AWS Directory Service</t>
+  </si>
+  <si>
+    <t>AWS Workspace</t>
+  </si>
+  <si>
+    <t>AWS Elemental Media Convert</t>
+  </si>
+  <si>
+    <t>Observability in AWS</t>
+  </si>
+  <si>
+    <t>More Management Services</t>
+  </si>
+  <si>
+    <t>AWS Proton</t>
+  </si>
+  <si>
+    <t>Machine Learning</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence - All around you</t>
+  </si>
+  <si>
+    <t>Architecture and Best Practice</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1376,6 +1508,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1428,7 +1567,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1459,6 +1598,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1967,7 +2110,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD904FA-0FAD-46CD-8773-AE594AFC6DAB}">
-  <dimension ref="B10:G321"/>
+  <dimension ref="B10:G380"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="8.7265625" customWidth="1"/>
@@ -3732,23 +3875,226 @@
       </c>
     </row>
     <row r="318" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F318" s="2" t="s">
+      <c r="F318" s="21" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="319" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F319" s="2" t="s">
+      <c r="F319" s="21" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="320" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F320" s="2" t="s">
+      <c r="F320" s="21" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="321" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F321" s="2" t="s">
+    <row r="321" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F321" s="21" t="s">
         <v>343</v>
+      </c>
+    </row>
+    <row r="322" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F322" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="325" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F325" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="326" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F326" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="327" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F327" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="G327" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="328" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F328" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="329" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F329" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="330" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F330" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="331" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F331" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="332" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F332" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="333" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F333" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="334" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F334" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="335" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F335" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="336" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F336" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="339" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F339" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="342" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F342" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="343" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F343" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="344" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F344" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="345" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F345" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="346" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F346" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="347" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F347" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="348" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F348" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="349" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F349" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="350" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F350" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="355" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F355" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="356" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F356" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="357" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F357" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="358" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F358" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="359" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F359" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="360" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F360" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="361" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F361" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="362" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F362" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="363" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F363" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="364" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F364" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="365" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F365" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="366" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F366" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="367" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F367" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="368" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F368" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="371" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F371" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="373" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F373" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="380" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F380" s="2" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -3993,7 +4339,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="98.7265625" style="4" customWidth="1"/>
@@ -4078,6 +4424,16 @@
     <row r="33" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A33" s="4" t="s">
         <v>344</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" s="20" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="20" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A35" s="4" t="s">
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -4090,55 +4446,63 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD312072-87FE-40B5-A445-1591614412BD}">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="123.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>258</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>360</v>
+      </c>
+      <c r="B10" t="s">
+        <v>362</v>
       </c>
     </row>
   </sheetData>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF87F28-FC4F-4CF9-9C17-AC7D7F671F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE2BF6D-87CB-4912-9205-79B36172728F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE2BF6D-87CB-4912-9205-79B36172728F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41FF54F-6BF5-4616-9D5C-89A286D7F307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="489">
   <si>
     <t>NextJS</t>
   </si>
@@ -155,12 +155,6 @@
   </si>
   <si>
     <t>Software compatability  - spring - spring boot and java version compatability</t>
-  </si>
-  <si>
-    <t>BESCOM Bill Pay</t>
-  </si>
-  <si>
-    <t>United Insurance</t>
   </si>
   <si>
     <t>Amazon Creditcard billpayment</t>
@@ -1292,9 +1286,6 @@
     <t>Powerschool shares</t>
   </si>
   <si>
-    <t>DynPro Documents</t>
-  </si>
-  <si>
     <t>AWS Certified Solutions Architect Associate - SAA C03</t>
   </si>
   <si>
@@ -1422,6 +1413,315 @@
   </si>
   <si>
     <t>Architecture and Best Practice</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/aws-certified-solutions-architect-associate-saa-c03/?couponCode=MT260615G2A1</t>
+  </si>
+  <si>
+    <t>Operational Excellence</t>
+  </si>
+  <si>
+    <t>AWS Lambda</t>
+  </si>
+  <si>
+    <t>CloudFormation</t>
+  </si>
+  <si>
+    <t>Codepipeline</t>
+  </si>
+  <si>
+    <t>AWS Coding</t>
+  </si>
+  <si>
+    <t>Cloudwatch</t>
+  </si>
+  <si>
+    <t>Security Pillar</t>
+  </si>
+  <si>
+    <t>AWS IAM</t>
+  </si>
+  <si>
+    <t>AWS WAF</t>
+  </si>
+  <si>
+    <t>AWS KMF</t>
+  </si>
+  <si>
+    <t>Cloud HSM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Lambda </t>
+  </si>
+  <si>
+    <t>Amazon SQA</t>
+  </si>
+  <si>
+    <t>Amazon SAN</t>
+  </si>
+  <si>
+    <t>API Gateway</t>
+  </si>
+  <si>
+    <t>AutoScaling</t>
+  </si>
+  <si>
+    <t>DynPro Documents - Arrangements</t>
+  </si>
+  <si>
+    <t>https://aws.amazon.com/ec2/autoscaling/faqs/</t>
+  </si>
+  <si>
+    <t>https://aws.amazon.com/architecture/</t>
+  </si>
+  <si>
+    <t>Regions and Zones</t>
+  </si>
+  <si>
+    <t>EC2 Fundamentals</t>
+  </si>
+  <si>
+    <t>EC2 Feature</t>
+  </si>
+  <si>
+    <t>EC2 Handson</t>
+  </si>
+  <si>
+    <t>EC2 Instance type</t>
+  </si>
+  <si>
+    <t>EC2 Instance Metadata Service and Dynamic Data</t>
+  </si>
+  <si>
+    <t>Security Groups</t>
+  </si>
+  <si>
+    <t>EC2 IP Address</t>
+  </si>
+  <si>
+    <t>Elastic IP Address</t>
+  </si>
+  <si>
+    <t>Simplify EC2 HTTP Server</t>
+  </si>
+  <si>
+    <t>Bootstraping with data</t>
+  </si>
+  <si>
+    <t>Launch Template</t>
+  </si>
+  <si>
+    <t>Reduce Launch time with customized AMI</t>
+  </si>
+  <si>
+    <t>AMI</t>
+  </si>
+  <si>
+    <t>EC2 Security key pair</t>
+  </si>
+  <si>
+    <t>Important EC2 senarios</t>
+  </si>
+  <si>
+    <t>Load Balancing</t>
+  </si>
+  <si>
+    <t>Elastic Load balancing</t>
+  </si>
+  <si>
+    <t>HTTP vs HTTPS vs TCP vs TLS vs UDP</t>
+  </si>
+  <si>
+    <t>Types of Load balancers</t>
+  </si>
+  <si>
+    <t>class Load Balancer</t>
+  </si>
+  <si>
+    <t>Application Load Balancer</t>
+  </si>
+  <si>
+    <t>Network Load Balancer</t>
+  </si>
+  <si>
+    <t>Load Balancers - Security Group Best Pratice</t>
+  </si>
+  <si>
+    <t>Listeners</t>
+  </si>
+  <si>
+    <t>Multiple Listeners</t>
+  </si>
+  <si>
+    <t>Target Groups</t>
+  </si>
+  <si>
+    <t>Target Group Configuration - Sticky session</t>
+  </si>
+  <si>
+    <t>Target Group Configuration - Deregistration delay</t>
+  </si>
+  <si>
+    <t>Micros service architecture - Multiple target groups</t>
+  </si>
+  <si>
+    <t>Listeners Rules</t>
+  </si>
+  <si>
+    <t>Listeners Rules  - Possibilities</t>
+  </si>
+  <si>
+    <t>Architecture summary</t>
+  </si>
+  <si>
+    <t>Introducing auto scaling group</t>
+  </si>
+  <si>
+    <t>auto scaling components</t>
+  </si>
+  <si>
+    <t>Auto scaling group use case</t>
+  </si>
+  <si>
+    <t>Dynamic scaling policy type</t>
+  </si>
+  <si>
+    <t>scaling policy  background</t>
+  </si>
+  <si>
+    <t>Autoscaling senarios</t>
+  </si>
+  <si>
+    <t>EC2 AND ELB for architects</t>
+  </si>
+  <si>
+    <t>Availability</t>
+  </si>
+  <si>
+    <t>Availability Basics EC2 and ELB</t>
+  </si>
+  <si>
+    <t>Scalability</t>
+  </si>
+  <si>
+    <t>Vertical scaling</t>
+  </si>
+  <si>
+    <t>vertical scaling for ec2</t>
+  </si>
+  <si>
+    <t>Horizantal Scaling</t>
+  </si>
+  <si>
+    <t>Horizantal Scaling for EC2</t>
+  </si>
+  <si>
+    <t>EC2 instance Families</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC2 Burstable Instance </t>
+  </si>
+  <si>
+    <t>EC2 Tenancy - Shared vs Dedicated</t>
+  </si>
+  <si>
+    <t>EC2 Dedicated instance vs Hosts</t>
+  </si>
+  <si>
+    <t>EC2 Placement groups</t>
+  </si>
+  <si>
+    <t>EC2 Cluster Placement Group</t>
+  </si>
+  <si>
+    <t>EC2 Spread Placement Group</t>
+  </si>
+  <si>
+    <t>EC2 Partition Placement Group - Use Case</t>
+  </si>
+  <si>
+    <t>EC2 Partition Placement Group - Best Pratices</t>
+  </si>
+  <si>
+    <t>Elastic Network Interface</t>
+  </si>
+  <si>
+    <t>Elastic Network Interface  - Primary and Secondary</t>
+  </si>
+  <si>
+    <t>EC2 Pricing Models Overview</t>
+  </si>
+  <si>
+    <t>EC2 on demand</t>
+  </si>
+  <si>
+    <t>EC2 Sport instances</t>
+  </si>
+  <si>
+    <t>EC2 SpotBlock and Sport Fleet</t>
+  </si>
+  <si>
+    <t>EC2 Linux Spot instances - Pricing</t>
+  </si>
+  <si>
+    <t>EC2 Linux Spot instances - Remember</t>
+  </si>
+  <si>
+    <t>EC2 Resered Instances</t>
+  </si>
+  <si>
+    <t>EC2 Standard Reserved Instances</t>
+  </si>
+  <si>
+    <t>EC2 Convertible Reserved Instances</t>
+  </si>
+  <si>
+    <t>EC2 Scheduled Reserved Instances</t>
+  </si>
+  <si>
+    <t>EC2 Compute saving plan</t>
+  </si>
+  <si>
+    <t>Monitoring ec2 instances</t>
+  </si>
+  <si>
+    <t>Monitoring ec2 instances - Custom Matrics</t>
+  </si>
+  <si>
+    <t>Elastic Load Balancers</t>
+  </si>
+  <si>
+    <t>Secure Communication - HTTPS</t>
+  </si>
+  <si>
+    <t>Elastic Load Balancer -  Two Communications Hops</t>
+  </si>
+  <si>
+    <t>Elastic Load Balancer - SSL/TLS Termination</t>
+  </si>
+  <si>
+    <t>Server Name indicator</t>
+  </si>
+  <si>
+    <t>Elastic Load Balancer - Logs and Heads</t>
+  </si>
+  <si>
+    <t>ALB vs NLB vs CLB -1</t>
+  </si>
+  <si>
+    <t>ALB vs NLB vs CLB - Routing</t>
+  </si>
+  <si>
+    <t>Import Load Balancer scenarios</t>
+  </si>
+  <si>
+    <t>Architecture Conciderations for EC2 and ELB</t>
+  </si>
+  <si>
+    <t>Application Load Balancer - Health Check a Settings</t>
+  </si>
+  <si>
+    <t>ELB Terminology</t>
   </si>
 </sst>
 </file>
@@ -1585,7 +1885,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1604,6 +1903,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2007,7 +2307,7 @@
         <v>13</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35"/>
@@ -2070,27 +2370,27 @@
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
@@ -2110,7 +2410,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD904FA-0FAD-46CD-8773-AE594AFC6DAB}">
-  <dimension ref="B10:G380"/>
+  <dimension ref="B10:G502"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="8.7265625" customWidth="1"/>
@@ -2119,1009 +2419,1009 @@
   <sheetData>
     <row r="10" spans="6:6" ht="409.5" x14ac:dyDescent="0.55000000000000004">
       <c r="F10" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F32" s="16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F33" s="16" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F32" s="17" t="s">
+    <row r="34" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F34" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F33" s="17" t="s">
+    <row r="35" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F35" s="16" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F34" s="17" t="s">
+    <row r="36" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F36" s="16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F37" s="16" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F35" s="17" t="s">
+    <row r="38" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F38" s="16" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F36" s="17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="37" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F37" s="17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F38" s="17" t="s">
-        <v>96</v>
-      </c>
-    </row>
     <row r="39" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F39" s="17"/>
+      <c r="F39" s="16"/>
     </row>
     <row r="40" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F40" s="17"/>
+      <c r="F40" s="16"/>
     </row>
     <row r="41" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F41" s="17" t="s">
+      <c r="F41" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F42" s="16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="43" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F43" s="16" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="42" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F42" s="17" t="s">
+    <row r="44" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F44" s="16" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="43" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F43" s="17" t="s">
+    <row r="45" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F45" s="16" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F44" s="17" t="s">
+    <row r="46" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F46" s="16" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="45" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F45" s="17" t="s">
+    <row r="47" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F47" s="16" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="46" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F46" s="17" t="s">
+    <row r="48" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F48" s="16" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="47" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F47" s="17" t="s">
+    <row r="49" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E49" s="16"/>
+      <c r="F49" s="16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E50" s="16"/>
+      <c r="F50" s="16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E51" s="16"/>
+      <c r="F51" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E52" s="16"/>
+      <c r="F52" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E53" s="16"/>
+      <c r="F53" s="16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="54" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E54" s="16"/>
+      <c r="F54" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="55" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E55" s="16"/>
+      <c r="F55" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="56" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E56" s="16"/>
+      <c r="F56" s="16" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="48" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F48" s="17" t="s">
+    <row r="57" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E57" s="16"/>
+      <c r="F57" s="16" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="49" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E49" s="17"/>
-      <c r="F49" s="17" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E50" s="17"/>
-      <c r="F50" s="17" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="51" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E51" s="17"/>
-      <c r="F51" s="17" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="52" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E52" s="17"/>
-      <c r="F52" s="17" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="53" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E53" s="17"/>
-      <c r="F53" s="17" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="54" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E54" s="17"/>
-      <c r="F54" s="17" t="s">
+    <row r="58" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E58" s="16"/>
+      <c r="F58" s="16" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="55" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E55" s="17"/>
-      <c r="F55" s="17" t="s">
+    <row r="59" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E59" s="16"/>
+      <c r="F59" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="56" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E56" s="17"/>
-      <c r="F56" s="17" t="s">
+    <row r="60" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E60" s="16"/>
+      <c r="F60" s="16" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="57" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E57" s="17"/>
-      <c r="F57" s="17" t="s">
+    <row r="61" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E61" s="16"/>
+      <c r="F61" s="16"/>
+    </row>
+    <row r="62" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+    </row>
+    <row r="63" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E63" s="16"/>
+      <c r="F63" s="16"/>
+    </row>
+    <row r="64" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E64" s="16"/>
+      <c r="F64" s="16" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="58" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E58" s="17"/>
-      <c r="F58" s="17" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="59" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E59" s="17"/>
-      <c r="F59" s="17" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="60" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E60" s="17"/>
-      <c r="F60" s="17" t="s">
+    <row r="65" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E65" s="16"/>
+      <c r="F65" s="16" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E61" s="17"/>
-      <c r="F61" s="17"/>
-    </row>
-    <row r="62" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E62" s="17"/>
-      <c r="F62" s="17"/>
-    </row>
-    <row r="63" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E63" s="17"/>
-      <c r="F63" s="17"/>
-    </row>
-    <row r="64" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E64" s="17"/>
-      <c r="F64" s="17" t="s">
+    <row r="66" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E66" s="16"/>
+      <c r="F66" s="16" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="65" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E65" s="17"/>
-      <c r="F65" s="17" t="s">
+    <row r="67" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E67" s="16"/>
+      <c r="F67" s="16" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="66" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E66" s="17"/>
-      <c r="F66" s="17" t="s">
+    <row r="68" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E68" s="16"/>
+      <c r="F68" s="16" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="67" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E67" s="17"/>
-      <c r="F67" s="17" t="s">
+    <row r="69" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E69" s="16"/>
+      <c r="F69" s="16" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="68" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E68" s="17"/>
-      <c r="F68" s="17" t="s">
+    <row r="70" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E70" s="16"/>
+      <c r="F70" s="16" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="69" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E69" s="17"/>
-      <c r="F69" s="17" t="s">
+    <row r="71" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E71" s="16"/>
+      <c r="F71" s="16" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="70" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E70" s="17"/>
-      <c r="F70" s="17" t="s">
+    <row r="72" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E72" s="16"/>
+      <c r="F72" s="16" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="71" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E71" s="17"/>
-      <c r="F71" s="17" t="s">
+    <row r="73" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E73" s="16"/>
+      <c r="F73" s="16" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="72" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E72" s="17"/>
-      <c r="F72" s="17" t="s">
+    <row r="74" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E74" s="16"/>
+      <c r="F74" s="16" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="73" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E73" s="17"/>
-      <c r="F73" s="17" t="s">
+    <row r="75" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E75" s="16"/>
+      <c r="F75" s="16" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="74" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E74" s="17"/>
-      <c r="F74" s="17" t="s">
+    <row r="76" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E76" s="16"/>
+      <c r="F76" s="16" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="75" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E75" s="17"/>
-      <c r="F75" s="17" t="s">
+    <row r="77" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E77" s="16"/>
+      <c r="F77" s="16" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="76" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E76" s="17"/>
-      <c r="F76" s="17" t="s">
+    <row r="78" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E78" s="16"/>
+      <c r="F78" s="16" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="77" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E77" s="17"/>
-      <c r="F77" s="17" t="s">
+    <row r="79" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E79" s="16"/>
+      <c r="F79" s="16" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="78" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E78" s="17"/>
-      <c r="F78" s="17" t="s">
+    <row r="80" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E80" s="16"/>
+      <c r="F80" s="16" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="79" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E79" s="17"/>
-      <c r="F79" s="17" t="s">
+    <row r="81" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E81" s="16"/>
+      <c r="F81" s="16" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="80" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E80" s="17"/>
-      <c r="F80" s="17" t="s">
+    <row r="82" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E82" s="16"/>
+      <c r="F82" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="81" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E81" s="17"/>
-      <c r="F81" s="17" t="s">
+    <row r="83" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E83" s="16"/>
+      <c r="F83" s="16" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="82" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E82" s="17"/>
-      <c r="F82" s="17" t="s">
+    <row r="84" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E84" s="16"/>
+      <c r="F84" s="16"/>
+    </row>
+    <row r="85" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E85" s="16"/>
+      <c r="F85" s="16"/>
+    </row>
+    <row r="86" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E86" s="16"/>
+      <c r="F86" s="16" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="83" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E83" s="17"/>
-      <c r="F83" s="17" t="s">
+    <row r="87" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E87" s="16"/>
+      <c r="F87" s="16" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="84" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E84" s="17"/>
-      <c r="F84" s="17"/>
-    </row>
-    <row r="85" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E85" s="17"/>
-      <c r="F85" s="17"/>
-    </row>
-    <row r="86" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E86" s="17"/>
-      <c r="F86" s="17" t="s">
+    <row r="88" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E88" s="16"/>
+      <c r="F88" s="16" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="87" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E87" s="17"/>
-      <c r="F87" s="17" t="s">
+    <row r="89" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E89" s="16"/>
+      <c r="F89" s="16"/>
+    </row>
+    <row r="90" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E90" s="16"/>
+      <c r="F90" s="16"/>
+    </row>
+    <row r="91" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E91" s="16"/>
+      <c r="F91" s="16" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="88" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E88" s="17"/>
-      <c r="F88" s="17" t="s">
+    <row r="92" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E92" s="16"/>
+      <c r="F92" s="16" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="89" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E89" s="17"/>
-      <c r="F89" s="17"/>
-    </row>
-    <row r="90" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E90" s="17"/>
-      <c r="F90" s="17"/>
-    </row>
-    <row r="91" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E91" s="17"/>
-      <c r="F91" s="17" t="s">
+    <row r="93" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E93" s="16"/>
+      <c r="F93" s="16" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="92" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E92" s="17"/>
-      <c r="F92" s="17" t="s">
+    <row r="94" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E94" s="16"/>
+      <c r="F94" s="16" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="93" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E93" s="17"/>
-      <c r="F93" s="17" t="s">
+    <row r="95" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E95" s="16"/>
+      <c r="F95" s="16" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="94" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E94" s="17"/>
-      <c r="F94" s="17" t="s">
+    <row r="96" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E96" s="16"/>
+      <c r="F96" s="16" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="95" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E95" s="17"/>
-      <c r="F95" s="17" t="s">
+    <row r="97" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E97" s="16"/>
+      <c r="F97" s="16" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="96" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E96" s="17"/>
-      <c r="F96" s="17" t="s">
+    <row r="98" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E98" s="16"/>
+      <c r="F98" s="16" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="97" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E97" s="17"/>
-      <c r="F97" s="17" t="s">
+    <row r="99" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E99" s="16"/>
+      <c r="F99" s="16" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="98" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E98" s="17"/>
-      <c r="F98" s="17" t="s">
+    <row r="100" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E100" s="16"/>
+      <c r="F100" s="16" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="99" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E99" s="17"/>
-      <c r="F99" s="17" t="s">
+    <row r="101" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E101" s="16"/>
+      <c r="F101" s="16" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="100" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E100" s="17"/>
-      <c r="F100" s="17" t="s">
+    <row r="102" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E102" s="16"/>
+      <c r="F102" s="16" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="101" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E101" s="17"/>
-      <c r="F101" s="17" t="s">
+    <row r="103" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E103" s="16"/>
+      <c r="F103" s="16" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="102" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E102" s="17"/>
-      <c r="F102" s="17" t="s">
+    <row r="104" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E104" s="16"/>
+      <c r="F104" s="16" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="103" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E103" s="17"/>
-      <c r="F103" s="17" t="s">
+    <row r="105" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E105" s="16"/>
+      <c r="F105" s="16" t="s">
         <v>156</v>
-      </c>
-    </row>
-    <row r="104" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E104" s="17"/>
-      <c r="F104" s="17" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="105" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E105" s="17"/>
-      <c r="F105" s="17" t="s">
-        <v>158</v>
       </c>
       <c r="G105" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="106" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E106" s="17"/>
-      <c r="F106" s="17" t="s">
+      <c r="E106" s="16"/>
+      <c r="F106" s="16" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="107" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E107" s="16"/>
+      <c r="F107" s="16"/>
+    </row>
+    <row r="108" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E108" s="16"/>
+      <c r="F108" s="16"/>
+    </row>
+    <row r="109" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E109" s="16"/>
+      <c r="F109" s="16" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="110" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E110" s="16"/>
+      <c r="F110" s="16" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="107" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E107" s="17"/>
-      <c r="F107" s="17"/>
-    </row>
-    <row r="108" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E108" s="17"/>
-      <c r="F108" s="17"/>
-    </row>
-    <row r="109" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E109" s="17"/>
-      <c r="F109" s="17" t="s">
+    <row r="111" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E111" s="16"/>
+      <c r="F111" s="16" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="110" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E110" s="17"/>
-      <c r="F110" s="17" t="s">
+    <row r="112" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E112" s="16"/>
+      <c r="F112" s="16" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="111" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E111" s="17"/>
-      <c r="F111" s="17" t="s">
+    <row r="113" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E113" s="16"/>
+      <c r="F113" s="16" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="112" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E112" s="17"/>
-      <c r="F112" s="17" t="s">
+    <row r="114" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E114" s="16"/>
+      <c r="F114" s="16" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="113" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E113" s="17"/>
-      <c r="F113" s="17" t="s">
+    <row r="115" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E115" s="16"/>
+      <c r="F115" s="16" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="114" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E114" s="17"/>
-      <c r="F114" s="17" t="s">
+    <row r="116" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E116" s="16"/>
+      <c r="F116" s="16" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="115" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E115" s="17"/>
-      <c r="F115" s="17" t="s">
+    <row r="117" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E117" s="16"/>
+      <c r="F117" s="16" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="116" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E116" s="17"/>
-      <c r="F116" s="17" t="s">
+    <row r="118" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E118" s="16"/>
+      <c r="F118" s="16" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="117" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E117" s="17"/>
-      <c r="F117" s="17" t="s">
+    <row r="119" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E119" s="16"/>
+      <c r="F119" s="16" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="118" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E118" s="17"/>
-      <c r="F118" s="17" t="s">
+    <row r="120" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E120" s="16"/>
+      <c r="F120" s="16" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="119" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E119" s="17"/>
-      <c r="F119" s="17" t="s">
+    <row r="121" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E121" s="16"/>
+      <c r="F121" s="16"/>
+    </row>
+    <row r="122" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E122" s="16"/>
+      <c r="F122" s="16"/>
+    </row>
+    <row r="123" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E123" s="16"/>
+      <c r="F123" s="16"/>
+    </row>
+    <row r="124" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E124" s="16"/>
+      <c r="F124" s="16" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="120" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E120" s="17"/>
-      <c r="F120" s="17" t="s">
+    <row r="125" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E125" s="16"/>
+      <c r="F125" s="16" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="121" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E121" s="17"/>
-      <c r="F121" s="17"/>
-    </row>
-    <row r="122" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E122" s="17"/>
-      <c r="F122" s="17"/>
-    </row>
-    <row r="123" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E123" s="17"/>
-      <c r="F123" s="17"/>
-    </row>
-    <row r="124" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E124" s="17"/>
-      <c r="F124" s="17" t="s">
+    <row r="126" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E126" s="16"/>
+      <c r="F126" s="16" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="125" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E125" s="17"/>
-      <c r="F125" s="17" t="s">
+    <row r="127" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E127" s="16"/>
+      <c r="F127" s="16" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="126" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E126" s="17"/>
-      <c r="F126" s="17" t="s">
+    <row r="128" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E128" s="16"/>
+      <c r="F128" s="16" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="127" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E127" s="17"/>
-      <c r="F127" s="17" t="s">
+    <row r="129" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E129" s="16"/>
+      <c r="F129" s="16" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="128" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E128" s="17"/>
-      <c r="F128" s="17" t="s">
+    <row r="130" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E130" s="16"/>
+      <c r="F130" s="16" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="129" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E129" s="17"/>
-      <c r="F129" s="17" t="s">
+    <row r="131" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E131" s="16"/>
+      <c r="F131" s="16" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="130" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E130" s="17"/>
-      <c r="F130" s="17" t="s">
+    <row r="132" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E132" s="16"/>
+      <c r="F132" s="16" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="131" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E131" s="17"/>
-      <c r="F131" s="17" t="s">
+    <row r="133" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E133" s="16"/>
+      <c r="F133" s="16" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="132" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E132" s="17"/>
-      <c r="F132" s="17" t="s">
+    <row r="134" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E134" s="16"/>
+      <c r="F134" s="16" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="133" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E133" s="17"/>
-      <c r="F133" s="17" t="s">
+    <row r="135" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E135" s="16"/>
+      <c r="F135" s="16" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="134" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E134" s="17"/>
-      <c r="F134" s="17" t="s">
+    <row r="136" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E136" s="16"/>
+      <c r="F136" s="16" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="135" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E135" s="17"/>
-      <c r="F135" s="17" t="s">
+    <row r="137" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E137" s="16"/>
+      <c r="F137" s="16" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="136" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E136" s="17"/>
-      <c r="F136" s="17" t="s">
+    <row r="138" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E138" s="16"/>
+      <c r="F138" s="16" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="137" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E137" s="17"/>
-      <c r="F137" s="17" t="s">
+    <row r="139" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E139" s="16"/>
+      <c r="F139" s="16" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="138" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E138" s="17"/>
-      <c r="F138" s="17" t="s">
+    <row r="140" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E140" s="16"/>
+      <c r="F140" s="16" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="139" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E139" s="17"/>
-      <c r="F139" s="17" t="s">
+    <row r="141" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E141" s="16"/>
+      <c r="F141" s="16" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="140" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E140" s="17"/>
-      <c r="F140" s="17" t="s">
+    <row r="142" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E142" s="16"/>
+      <c r="F142" s="16" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="141" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E141" s="17"/>
-      <c r="F141" s="17" t="s">
+    <row r="143" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E143" s="16"/>
+      <c r="F143" s="16" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="142" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E142" s="17"/>
-      <c r="F142" s="17" t="s">
+    <row r="144" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E144" s="16"/>
+      <c r="F144" s="16" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="143" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E143" s="17"/>
-      <c r="F143" s="17" t="s">
+    <row r="145" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E145" s="16"/>
+      <c r="F145" s="16" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="144" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E144" s="17"/>
-      <c r="F144" s="17" t="s">
+    <row r="146" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E146" s="16"/>
+      <c r="F146" s="16" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="145" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E145" s="17"/>
-      <c r="F145" s="17" t="s">
+    <row r="147" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E147" s="16"/>
+      <c r="F147" s="16" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="146" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E146" s="17"/>
-      <c r="F146" s="17" t="s">
+    <row r="148" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E148" s="16"/>
+      <c r="F148" s="16" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="147" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E147" s="17"/>
-      <c r="F147" s="17" t="s">
+    <row r="149" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E149" s="16"/>
+      <c r="F149" s="16" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="148" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E148" s="17"/>
-      <c r="F148" s="17" t="s">
+    <row r="150" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E150" s="16"/>
+      <c r="F150" s="16" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="149" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E149" s="17"/>
-      <c r="F149" s="17" t="s">
+    <row r="151" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E151" s="16"/>
+      <c r="F151" s="16"/>
+    </row>
+    <row r="152" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E152" s="16"/>
+      <c r="F152" s="16"/>
+    </row>
+    <row r="153" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E153" s="16"/>
+      <c r="F153" s="16" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="150" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E150" s="17"/>
-      <c r="F150" s="17" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="151" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E151" s="17"/>
-      <c r="F151" s="17"/>
-    </row>
-    <row r="152" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E152" s="17"/>
-      <c r="F152" s="17"/>
-    </row>
-    <row r="153" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E153" s="17"/>
-      <c r="F153" s="17" t="s">
-        <v>199</v>
-      </c>
-    </row>
     <row r="154" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E154" s="17"/>
-      <c r="F154" s="17" t="s">
+      <c r="E154" s="16"/>
+      <c r="F154" s="16" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="155" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E155" s="16"/>
+      <c r="F155" s="16" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="156" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E156" s="16"/>
+      <c r="F156" s="16" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="155" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E155" s="17"/>
-      <c r="F155" s="17" t="s">
+    <row r="157" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E157" s="16"/>
+      <c r="F157" s="16" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="156" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E156" s="17"/>
-      <c r="F156" s="17" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="157" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E157" s="17"/>
-      <c r="F157" s="17" t="s">
+    <row r="158" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E158" s="16"/>
+      <c r="F158" s="16" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="158" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E158" s="17"/>
-      <c r="F158" s="17" t="s">
+    <row r="159" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E159" s="16"/>
+      <c r="F159" s="16" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="160" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E160" s="16"/>
+      <c r="F160" s="16" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="159" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E159" s="17"/>
-      <c r="F159" s="17" t="s">
+    <row r="161" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E161" s="16"/>
+      <c r="F161" s="16" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="160" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E160" s="17"/>
-      <c r="F160" s="17" t="s">
+    <row r="162" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E162" s="16"/>
+      <c r="F162" s="16" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="161" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E161" s="17"/>
-      <c r="F161" s="17" t="s">
+    <row r="163" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E163" s="16"/>
+      <c r="F163" s="16" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="162" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E162" s="17"/>
-      <c r="F162" s="17" t="s">
+    <row r="164" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E164" s="16"/>
+      <c r="F164" s="16" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="163" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E163" s="17"/>
-      <c r="F163" s="17" t="s">
+    <row r="165" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E165" s="16"/>
+      <c r="F165" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="166" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E166" s="16"/>
+      <c r="F166" s="16" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="164" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E164" s="17"/>
-      <c r="F164" s="17" t="s">
+    <row r="167" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E167" s="16"/>
+      <c r="F167" s="16" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="165" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E165" s="17"/>
-      <c r="F165" s="17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="166" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E166" s="17"/>
-      <c r="F166" s="17" t="s">
+    <row r="168" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E168" s="16"/>
+      <c r="F168" s="16" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="167" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E167" s="17"/>
-      <c r="F167" s="17" t="s">
+    <row r="169" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E169" s="16"/>
+      <c r="F169" s="16" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="168" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E168" s="17"/>
-      <c r="F168" s="17" t="s">
+    <row r="170" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E170" s="16"/>
+      <c r="F170" s="16" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="169" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E169" s="17"/>
-      <c r="F169" s="17" t="s">
+    <row r="171" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E171" s="16"/>
+      <c r="F171" s="16" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="170" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E170" s="17"/>
-      <c r="F170" s="17" t="s">
+    <row r="172" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E172" s="16"/>
+      <c r="F172" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="171" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E171" s="17"/>
-      <c r="F171" s="17" t="s">
+    <row r="173" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E173" s="16"/>
+      <c r="F173" s="16" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="172" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E172" s="17"/>
-      <c r="F172" s="17" t="s">
+    <row r="174" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E174" s="16"/>
+      <c r="F174" s="16" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="173" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E173" s="17"/>
-      <c r="F173" s="17" t="s">
+    <row r="175" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E175" s="16"/>
+      <c r="F175" s="16" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="174" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E174" s="17"/>
-      <c r="F174" s="17" t="s">
+    <row r="176" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E176" s="16"/>
+      <c r="F176" s="16" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="175" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E175" s="17"/>
-      <c r="F175" s="17" t="s">
+    <row r="177" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E177" s="16"/>
+      <c r="F177" s="16" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="176" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E176" s="17"/>
-      <c r="F176" s="17" t="s">
+    <row r="178" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E178" s="16"/>
+      <c r="F178" s="16" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="177" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E177" s="17"/>
-      <c r="F177" s="17" t="s">
+    <row r="179" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E179" s="16"/>
+      <c r="F179" s="16" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="178" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E178" s="17"/>
-      <c r="F178" s="17" t="s">
+    <row r="180" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E180" s="16"/>
+      <c r="F180" s="16" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="179" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E179" s="17"/>
-      <c r="F179" s="17" t="s">
+    <row r="181" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E181" s="16"/>
+      <c r="F181" s="16" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="180" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E180" s="17"/>
-      <c r="F180" s="17" t="s">
+    <row r="182" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E182" s="16"/>
+      <c r="F182" s="16" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="181" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E181" s="17"/>
-      <c r="F181" s="17" t="s">
+    <row r="183" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E183" s="16"/>
+      <c r="F183" s="16" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="182" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E182" s="17"/>
-      <c r="F182" s="17" t="s">
+    <row r="184" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E184" s="16"/>
+      <c r="F184" s="16" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="183" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E183" s="17"/>
-      <c r="F183" s="17" t="s">
+    <row r="185" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E185" s="16"/>
+      <c r="F185" s="16" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="184" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E184" s="17"/>
-      <c r="F184" s="17" t="s">
+    <row r="186" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E186" s="16"/>
+      <c r="F186" s="16" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="185" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E185" s="17"/>
-      <c r="F185" s="17" t="s">
+    <row r="187" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E187" s="16"/>
+      <c r="F187" s="16" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="186" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E186" s="17"/>
-      <c r="F186" s="17" t="s">
+    <row r="188" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E188" s="16"/>
+      <c r="F188" s="16"/>
+    </row>
+    <row r="189" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E189" s="16"/>
+      <c r="F189" s="16"/>
+    </row>
+    <row r="190" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E190" s="16"/>
+      <c r="F190" s="16"/>
+    </row>
+    <row r="191" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E191" s="16"/>
+      <c r="F191" s="16" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="187" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E187" s="17"/>
-      <c r="F187" s="17" t="s">
+    <row r="192" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E192" s="16"/>
+      <c r="F192" s="16" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="188" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E188" s="17"/>
-      <c r="F188" s="17"/>
-    </row>
-    <row r="189" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E189" s="17"/>
-      <c r="F189" s="17"/>
-    </row>
-    <row r="190" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E190" s="17"/>
-      <c r="F190" s="17"/>
-    </row>
-    <row r="191" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E191" s="17"/>
-      <c r="F191" s="17" t="s">
+    <row r="193" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E193" s="16"/>
+      <c r="F193" s="16" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="192" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E192" s="17"/>
-      <c r="F192" s="17" t="s">
+    <row r="194" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E194" s="16"/>
+      <c r="F194" s="16" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="193" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E193" s="17"/>
-      <c r="F193" s="17" t="s">
+    <row r="195" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E195" s="16"/>
+      <c r="F195" s="16" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="194" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E194" s="17"/>
-      <c r="F194" s="17" t="s">
+    <row r="196" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E196" s="16"/>
+      <c r="F196" s="16" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="195" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E195" s="17"/>
-      <c r="F195" s="17" t="s">
+    <row r="197" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E197" s="16"/>
+      <c r="F197" s="16" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="196" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E196" s="17"/>
-      <c r="F196" s="17" t="s">
+    <row r="198" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E198" s="16"/>
+      <c r="F198" s="16" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="197" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E197" s="17"/>
-      <c r="F197" s="17" t="s">
+    <row r="199" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E199" s="16"/>
+      <c r="F199" s="16" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="198" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E198" s="17"/>
-      <c r="F198" s="17" t="s">
+    <row r="200" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E200" s="16"/>
+      <c r="F200" s="16" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="199" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E199" s="17"/>
-      <c r="F199" s="17" t="s">
+    <row r="201" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E201" s="16"/>
+      <c r="F201" s="16"/>
+    </row>
+    <row r="202" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E202" s="16"/>
+      <c r="F202" s="16"/>
+    </row>
+    <row r="203" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E203" s="16"/>
+      <c r="F203" s="16" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="200" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E200" s="17"/>
-      <c r="F200" s="17" t="s">
+    <row r="204" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E204" s="16"/>
+      <c r="F204" s="16" t="s">
         <v>247</v>
-      </c>
-    </row>
-    <row r="201" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E201" s="17"/>
-      <c r="F201" s="17"/>
-    </row>
-    <row r="202" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E202" s="17"/>
-      <c r="F202" s="17"/>
-    </row>
-    <row r="203" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E203" s="17"/>
-      <c r="F203" s="17" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="204" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E204" s="17"/>
-      <c r="F204" s="17" t="s">
-        <v>249</v>
       </c>
       <c r="G204" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="205" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E205" s="17"/>
-      <c r="F205" s="17" t="s">
+      <c r="E205" s="16"/>
+      <c r="F205" s="16" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="206" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E206" s="16"/>
+      <c r="F206" s="16" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="207" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="F207" s="16" t="s">
         <v>250</v>
-      </c>
-    </row>
-    <row r="206" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E206" s="17"/>
-      <c r="F206" s="17" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="207" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="F207" s="17" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="208" spans="2:7" ht="21" x14ac:dyDescent="0.5">
@@ -3129,8 +3429,8 @@
       <c r="C208" s="4"/>
       <c r="D208" s="4"/>
       <c r="E208" s="4"/>
-      <c r="F208" s="17" t="s">
-        <v>255</v>
+      <c r="F208" s="16" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="209" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3138,8 +3438,8 @@
       <c r="C209" s="4"/>
       <c r="D209" s="4"/>
       <c r="E209" s="4"/>
-      <c r="F209" s="18" t="s">
-        <v>256</v>
+      <c r="F209" s="17" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="210" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3147,8 +3447,8 @@
       <c r="C210" s="4"/>
       <c r="D210" s="4"/>
       <c r="E210" s="4"/>
-      <c r="F210" s="18" t="s">
-        <v>257</v>
+      <c r="F210" s="17" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="211" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3156,8 +3456,8 @@
       <c r="C211" s="4"/>
       <c r="D211" s="4"/>
       <c r="E211" s="4"/>
-      <c r="F211" s="18" t="s">
-        <v>259</v>
+      <c r="F211" s="17" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="212" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3165,8 +3465,8 @@
       <c r="C212" s="4"/>
       <c r="D212" s="4"/>
       <c r="E212" s="4"/>
-      <c r="F212" s="18" t="s">
-        <v>260</v>
+      <c r="F212" s="17" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="213" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3174,8 +3474,8 @@
       <c r="C213" s="4"/>
       <c r="D213" s="4"/>
       <c r="E213" s="4"/>
-      <c r="F213" s="18" t="s">
-        <v>261</v>
+      <c r="F213" s="17" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="214" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3183,8 +3483,8 @@
       <c r="C214" s="4"/>
       <c r="D214" s="4"/>
       <c r="E214" s="4"/>
-      <c r="F214" s="18" t="s">
-        <v>262</v>
+      <c r="F214" s="17" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="215" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3192,8 +3492,8 @@
       <c r="C215" s="4"/>
       <c r="D215" s="4"/>
       <c r="E215" s="4"/>
-      <c r="F215" s="18" t="s">
-        <v>263</v>
+      <c r="F215" s="17" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="216" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3201,8 +3501,8 @@
       <c r="C216" s="4"/>
       <c r="D216" s="4"/>
       <c r="E216" s="4"/>
-      <c r="F216" s="18" t="s">
-        <v>264</v>
+      <c r="F216" s="17" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="217" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3210,8 +3510,8 @@
       <c r="C217" s="4"/>
       <c r="D217" s="4"/>
       <c r="E217" s="4"/>
-      <c r="F217" s="18" t="s">
-        <v>265</v>
+      <c r="F217" s="17" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="218" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3219,29 +3519,29 @@
       <c r="C218" s="4"/>
       <c r="D218" s="4"/>
       <c r="E218" s="4"/>
-      <c r="F218" s="18"/>
+      <c r="F218" s="17"/>
     </row>
     <row r="219" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
-      <c r="F219" s="18"/>
+      <c r="F219" s="17"/>
     </row>
     <row r="220" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
       <c r="D220" s="4"/>
       <c r="E220" s="4"/>
-      <c r="F220" s="18"/>
+      <c r="F220" s="17"/>
     </row>
     <row r="221" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
       <c r="D221" s="4"/>
       <c r="E221" s="4"/>
-      <c r="F221" s="18" t="s">
-        <v>266</v>
+      <c r="F221" s="17" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="222" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3249,8 +3549,8 @@
       <c r="C222" s="4"/>
       <c r="D222" s="4"/>
       <c r="E222" s="4"/>
-      <c r="F222" s="18" t="s">
-        <v>267</v>
+      <c r="F222" s="17" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="223" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3258,8 +3558,8 @@
       <c r="C223" s="4"/>
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
-      <c r="F223" s="18" t="s">
-        <v>268</v>
+      <c r="F223" s="17" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="224" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3267,8 +3567,8 @@
       <c r="C224" s="4"/>
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
-      <c r="F224" s="18" t="s">
-        <v>269</v>
+      <c r="F224" s="17" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="225" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3276,8 +3576,8 @@
       <c r="C225" s="4"/>
       <c r="D225" s="4"/>
       <c r="E225" s="4"/>
-      <c r="F225" s="18" t="s">
-        <v>270</v>
+      <c r="F225" s="17" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="226" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3285,8 +3585,8 @@
       <c r="C226" s="4"/>
       <c r="D226" s="4"/>
       <c r="E226" s="4"/>
-      <c r="F226" s="18" t="s">
-        <v>271</v>
+      <c r="F226" s="17" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="227" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3294,8 +3594,8 @@
       <c r="C227" s="4"/>
       <c r="D227" s="4"/>
       <c r="E227" s="4"/>
-      <c r="F227" s="18" t="s">
-        <v>272</v>
+      <c r="F227" s="17" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="228" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3303,8 +3603,8 @@
       <c r="C228" s="4"/>
       <c r="D228" s="4"/>
       <c r="E228" s="4"/>
-      <c r="F228" s="18" t="s">
-        <v>273</v>
+      <c r="F228" s="17" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="229" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3312,8 +3612,8 @@
       <c r="C229" s="4"/>
       <c r="D229" s="4"/>
       <c r="E229" s="4"/>
-      <c r="F229" s="18" t="s">
-        <v>274</v>
+      <c r="F229" s="17" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="230" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3321,36 +3621,36 @@
       <c r="C230" s="4"/>
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
-      <c r="F230" s="18"/>
+      <c r="F230" s="17"/>
     </row>
     <row r="231" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
-      <c r="F231" s="18"/>
+      <c r="F231" s="17"/>
     </row>
     <row r="232" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
-      <c r="F232" s="18"/>
+      <c r="F232" s="17"/>
     </row>
     <row r="233" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
-      <c r="F233" s="18"/>
+      <c r="F233" s="17"/>
     </row>
     <row r="234" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
       <c r="D234" s="4"/>
       <c r="E234" s="4"/>
-      <c r="F234" s="18" t="s">
-        <v>275</v>
+      <c r="F234" s="17" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="235" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3358,8 +3658,8 @@
       <c r="C235" s="4"/>
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
-      <c r="F235" s="18" t="s">
-        <v>276</v>
+      <c r="F235" s="17" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="236" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3367,8 +3667,8 @@
       <c r="C236" s="4"/>
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
-      <c r="F236" s="18" t="s">
-        <v>277</v>
+      <c r="F236" s="17" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="237" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3376,8 +3676,8 @@
       <c r="C237" s="4"/>
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
-      <c r="F237" s="18" t="s">
-        <v>278</v>
+      <c r="F237" s="17" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="238" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3385,8 +3685,8 @@
       <c r="C238" s="4"/>
       <c r="D238" s="4"/>
       <c r="E238" s="4"/>
-      <c r="F238" s="18" t="s">
-        <v>279</v>
+      <c r="F238" s="17" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="239" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3394,8 +3694,8 @@
       <c r="C239" s="4"/>
       <c r="D239" s="4"/>
       <c r="E239" s="4"/>
-      <c r="F239" s="18" t="s">
-        <v>280</v>
+      <c r="F239" s="17" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="240" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3403,8 +3703,8 @@
       <c r="C240" s="4"/>
       <c r="D240" s="4"/>
       <c r="E240" s="4"/>
-      <c r="F240" s="18" t="s">
-        <v>281</v>
+      <c r="F240" s="17" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="241" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3412,8 +3712,8 @@
       <c r="C241" s="4"/>
       <c r="D241" s="4"/>
       <c r="E241" s="4"/>
-      <c r="F241" s="18" t="s">
-        <v>282</v>
+      <c r="F241" s="17" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="242" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3421,8 +3721,8 @@
       <c r="C242" s="4"/>
       <c r="D242" s="4"/>
       <c r="E242" s="4"/>
-      <c r="F242" s="18" t="s">
-        <v>283</v>
+      <c r="F242" s="17" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="243" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3430,29 +3730,29 @@
       <c r="C243" s="4"/>
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
-      <c r="F243" s="18"/>
+      <c r="F243" s="17"/>
     </row>
     <row r="244" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
       <c r="D244" s="4"/>
       <c r="E244" s="4"/>
-      <c r="F244" s="18"/>
+      <c r="F244" s="17"/>
     </row>
     <row r="245" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
       <c r="D245" s="4"/>
       <c r="E245" s="4"/>
-      <c r="F245" s="18"/>
+      <c r="F245" s="17"/>
     </row>
     <row r="246" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
       <c r="D246" s="4"/>
       <c r="E246" s="4"/>
-      <c r="F246" s="18" t="s">
-        <v>284</v>
+      <c r="F246" s="17" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="247" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3460,8 +3760,8 @@
       <c r="C247" s="4"/>
       <c r="D247" s="4"/>
       <c r="E247" s="4"/>
-      <c r="F247" s="18" t="s">
-        <v>285</v>
+      <c r="F247" s="17" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="248" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3469,8 +3769,8 @@
       <c r="C248" s="4"/>
       <c r="D248" s="4"/>
       <c r="E248" s="4"/>
-      <c r="F248" s="18" t="s">
-        <v>286</v>
+      <c r="F248" s="17" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="249" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3478,8 +3778,8 @@
       <c r="C249" s="4"/>
       <c r="D249" s="4"/>
       <c r="E249" s="4"/>
-      <c r="F249" s="18" t="s">
-        <v>287</v>
+      <c r="F249" s="17" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="250" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3487,8 +3787,8 @@
       <c r="C250" s="4"/>
       <c r="D250" s="4"/>
       <c r="E250" s="4"/>
-      <c r="F250" s="18" t="s">
-        <v>288</v>
+      <c r="F250" s="17" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="251" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3496,8 +3796,8 @@
       <c r="C251" s="4"/>
       <c r="D251" s="4"/>
       <c r="E251" s="4"/>
-      <c r="F251" s="18" t="s">
-        <v>289</v>
+      <c r="F251" s="17" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="252" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3505,8 +3805,8 @@
       <c r="C252" s="4"/>
       <c r="D252" s="4"/>
       <c r="E252" s="4"/>
-      <c r="F252" s="18" t="s">
-        <v>290</v>
+      <c r="F252" s="17" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="253" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3514,8 +3814,8 @@
       <c r="C253" s="4"/>
       <c r="D253" s="4"/>
       <c r="E253" s="4"/>
-      <c r="F253" s="18" t="s">
-        <v>291</v>
+      <c r="F253" s="17" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="254" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3523,8 +3823,8 @@
       <c r="C254" s="4"/>
       <c r="D254" s="4"/>
       <c r="E254" s="4"/>
-      <c r="F254" s="18" t="s">
-        <v>292</v>
+      <c r="F254" s="17" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="255" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3532,29 +3832,29 @@
       <c r="C255" s="4"/>
       <c r="D255" s="4"/>
       <c r="E255" s="4"/>
-      <c r="F255" s="18"/>
+      <c r="F255" s="17"/>
     </row>
     <row r="256" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
       <c r="D256" s="4"/>
       <c r="E256" s="4"/>
-      <c r="F256" s="18"/>
+      <c r="F256" s="17"/>
     </row>
     <row r="257" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
       <c r="D257" s="4"/>
       <c r="E257" s="4"/>
-      <c r="F257" s="18"/>
+      <c r="F257" s="17"/>
     </row>
     <row r="258" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
       <c r="D258" s="4"/>
       <c r="E258" s="4"/>
-      <c r="F258" s="18" t="s">
-        <v>294</v>
+      <c r="F258" s="17" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="259" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3562,22 +3862,22 @@
       <c r="C259" s="4"/>
       <c r="D259" s="4"/>
       <c r="E259" s="4"/>
-      <c r="F259" s="18"/>
+      <c r="F259" s="17"/>
     </row>
     <row r="260" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
       <c r="D260" s="4"/>
       <c r="E260" s="4"/>
-      <c r="F260" s="18"/>
+      <c r="F260" s="17"/>
     </row>
     <row r="261" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
       <c r="D261" s="4"/>
       <c r="E261" s="4"/>
-      <c r="F261" s="18" t="s">
-        <v>293</v>
+      <c r="F261" s="17" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="262" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3585,8 +3885,8 @@
       <c r="C262" s="4"/>
       <c r="D262" s="4"/>
       <c r="E262" s="4"/>
-      <c r="F262" s="18" t="s">
-        <v>295</v>
+      <c r="F262" s="17" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="263" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3594,8 +3894,8 @@
       <c r="C263" s="4"/>
       <c r="D263" s="4"/>
       <c r="E263" s="4"/>
-      <c r="F263" s="18" t="s">
-        <v>296</v>
+      <c r="F263" s="17" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="264" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3603,8 +3903,8 @@
       <c r="C264" s="4"/>
       <c r="D264" s="4"/>
       <c r="E264" s="4"/>
-      <c r="F264" s="18" t="s">
-        <v>297</v>
+      <c r="F264" s="17" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="265" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3612,8 +3912,8 @@
       <c r="C265" s="4"/>
       <c r="D265" s="4"/>
       <c r="E265" s="4"/>
-      <c r="F265" s="18" t="s">
-        <v>298</v>
+      <c r="F265" s="17" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="266" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3621,22 +3921,22 @@
       <c r="C266" s="4"/>
       <c r="D266" s="4"/>
       <c r="E266" s="4"/>
-      <c r="F266" s="18"/>
+      <c r="F266" s="17"/>
     </row>
     <row r="267" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
       <c r="D267" s="4"/>
       <c r="E267" s="4"/>
-      <c r="F267" s="18"/>
+      <c r="F267" s="17"/>
     </row>
     <row r="268" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
       <c r="D268" s="4"/>
       <c r="E268" s="4"/>
-      <c r="F268" s="18" t="s">
-        <v>299</v>
+      <c r="F268" s="17" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="269" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3644,8 +3944,8 @@
       <c r="C269" s="4"/>
       <c r="D269" s="4"/>
       <c r="E269" s="4"/>
-      <c r="F269" s="18" t="s">
-        <v>300</v>
+      <c r="F269" s="17" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="270" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3653,8 +3953,8 @@
       <c r="C270" s="4"/>
       <c r="D270" s="4"/>
       <c r="E270" s="4"/>
-      <c r="F270" s="18" t="s">
-        <v>301</v>
+      <c r="F270" s="17" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="271" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3662,29 +3962,29 @@
       <c r="C271" s="4"/>
       <c r="D271" s="4"/>
       <c r="E271" s="4"/>
-      <c r="F271" s="18"/>
+      <c r="F271" s="17"/>
     </row>
     <row r="272" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
       <c r="D272" s="4"/>
       <c r="E272" s="4"/>
-      <c r="F272" s="18"/>
+      <c r="F272" s="17"/>
     </row>
     <row r="273" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
       <c r="D273" s="4"/>
       <c r="E273" s="4"/>
-      <c r="F273" s="18"/>
+      <c r="F273" s="17"/>
     </row>
     <row r="274" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
       <c r="D274" s="4"/>
       <c r="E274" s="4"/>
-      <c r="F274" s="18" t="s">
-        <v>302</v>
+      <c r="F274" s="17" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="275" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
@@ -3692,226 +3992,226 @@
       <c r="C275" s="4"/>
       <c r="D275" s="4"/>
       <c r="E275" s="4"/>
-      <c r="F275" s="18" t="s">
-        <v>303</v>
+      <c r="F275" s="17" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="276" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F276" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="277" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F277" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="278" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F278" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="279" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F279" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="280" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F280" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="281" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F281" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="282" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F282" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="283" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F283" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="284" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F284" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="285" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F285" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="286" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F286" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G286" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="287" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F287" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="288" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F288" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="289" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F289" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="290" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F290" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="291" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F291" s="19" t="s">
-        <v>320</v>
+      <c r="F291" s="18" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="292" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F292" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="293" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F293" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="294" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F294" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="298" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F298" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="299" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F299" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="300" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F300" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="301" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F301" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="302" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F302" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="303" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F303" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="304" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F304" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="305" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F305" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="306" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F306" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="307" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F307" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="308" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F308" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="309" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F309" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="310" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F310" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="315" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F315" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="316" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F316" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="317" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F317" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="318" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F318" s="20" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="319" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F319" s="20" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="318" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F318" s="21" t="s">
+    <row r="320" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F320" s="20" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="319" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F319" s="21" t="s">
+    <row r="321" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F321" s="20" t="s">
         <v>341</v>
-      </c>
-    </row>
-    <row r="320" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F320" s="21" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="321" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F321" s="21" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="322" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F322" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="325" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F325" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="326" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F326" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="327" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F327" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="G327" t="s">
         <v>38</v>
@@ -3919,182 +4219,707 @@
     </row>
     <row r="328" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F328" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="329" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F329" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="330" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F330" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="331" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F331" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="332" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F332" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="333" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F333" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="334" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F334" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="335" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F335" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="336" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F336" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="339" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F339" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="342" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F342" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="343" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F343" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="344" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F344" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="345" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F345" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="346" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F346" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="347" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F347" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="348" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F348" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="349" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F349" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="350" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F350" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="355" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F355" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="356" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F356" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="357" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F357" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="358" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F358" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="359" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F359" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="360" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F360" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="361" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F361" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="362" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F362" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="363" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F363" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="364" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F364" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="365" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F365" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="366" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F366" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="367" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F367" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="368" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F368" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="371" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F371" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="373" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F373" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
+      </c>
+    </row>
+    <row r="377" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F377" s="2" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="380" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F380" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="382" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F382" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="383" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F383" s="2" t="s">
         <v>388</v>
+      </c>
+    </row>
+    <row r="384" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F384" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="385" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F385" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="386" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F386" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="387" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F387" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="390" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F390" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="391" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F391" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="392" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F392" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="393" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F393" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="394" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F394" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="395" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F395" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="398" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F398" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="399" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F399" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="400" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F400" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="401" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F401" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="402" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F402" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="403" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F403" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="408" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F408" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="410" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F410" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="411" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F411" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="412" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F412" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="413" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F413" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="414" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F414" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="415" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F415" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="416" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F416" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="417" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F417" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="418" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F418" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="419" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F419" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="420" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F420" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="421" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F421" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="422" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F422" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="423" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F423" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="424" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F424" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="427" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F427" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="428" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F428" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="429" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F429" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="430" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F430" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="431" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F431" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="432" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F432" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="433" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F433" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="434" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F434" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="435" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F435" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="436" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F436" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="437" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F437" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="438" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F438" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="439" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F439" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="440" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F440" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="441" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F441" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="442" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F442" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="443" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F443" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="444" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F444" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="445" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F445" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="446" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F446" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="447" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F447" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="448" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F448" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="449" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F449" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="450" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F450" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="453" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F453" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="454" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F454" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="455" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F455" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="456" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F456" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="457" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F457" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="458" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F458" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="459" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F459" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="460" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F460" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="461" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F461" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="462" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F462" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="463" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F463" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="464" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F464" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="465" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F465" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="466" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F466" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="467" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F467" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="468" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F468" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="469" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F469" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="470" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F470" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="473" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F473" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="474" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F474" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="475" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F475" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="476" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F476" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="477" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F477" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="478" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F478" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="479" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F479" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="480" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F480" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="481" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F481" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="482" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F482" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="483" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F483" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="484" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F484" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="485" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F485" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="486" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F486" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="487" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F487" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="488" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F488" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="491" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F491" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="492" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F492" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="493" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F493" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="494" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F494" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="495" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F495" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="496" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F496" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="497" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F497" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="498" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F498" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="499" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F499" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="500" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F500" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="501" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F501" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="502" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F502" s="2" t="s">
+        <v>488</v>
       </c>
     </row>
   </sheetData>
@@ -4110,226 +4935,226 @@
   <dimension ref="A1:C79"/>
   <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="98.1796875" style="16" customWidth="1"/>
-    <col min="2" max="2" width="22.36328125" style="16" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" style="16"/>
+    <col min="1" max="1" width="98.1796875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="22.36328125" style="15" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="15" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="15" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="16" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="16" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="16" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="16" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="15" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="16" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="15" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="16" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="15" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="16" t="s">
+      <c r="B22" s="15" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="16" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="16" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="16" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="16" t="s">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="15" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="16" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="15" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="16" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="15" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="16" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="15" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="16" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="15" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="16" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="15" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="16" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="15" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="16" t="s">
+      <c r="B37" s="15" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="16" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="C38" s="15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="B38" s="16" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C38" s="16" t="s">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="16" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="15" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="16" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="15" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="16" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="15" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="16" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="15" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="16" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C54" s="15" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="16" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="15" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C54" s="16" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="15" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="16" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="16" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="15" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="16" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="15" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="16" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="16" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="15" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="16" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="16" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="16" t="s">
-        <v>78</v>
-      </c>
-    </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="16" t="s">
-        <v>89</v>
+      <c r="A79" s="15" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -4339,7 +5164,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A35"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="98.7265625" style="4" customWidth="1"/>
@@ -4352,13 +5177,13 @@
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A5" s="14" t="s">
-        <v>83</v>
+      <c r="A5" s="13" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A7" s="14" t="s">
-        <v>84</v>
+      <c r="A7" s="13" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
@@ -4382,7 +5207,7 @@
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="14" t="s">
         <v>26</v>
       </c>
     </row>
@@ -4391,54 +5216,55 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A21" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A22" s="13" t="s">
-        <v>41</v>
+      <c r="A22" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A23" s="4" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A25" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A26" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A29" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A31" s="4" t="s">
-        <v>99</v>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="19" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A33" s="4" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" s="20" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="20" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A35" s="4" t="s">
-        <v>346</v>
+        <v>343</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A37" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A39" s="21" t="s">
+        <v>405</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A15" r:id="rId1" display="https://www.geeksforgeeks.org/dsa/print-all-permutations-of-a-string-in-java/" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A39" r:id="rId2" xr:uid="{49B8824C-64D5-47B7-BD9F-F3E73F317B6D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4454,55 +5280,55 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B10" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41FF54F-6BF5-4616-9D5C-89A286D7F307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{273FA4E0-560A-4949-AA74-D21CCE25E2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{273FA4E0-560A-4949-AA74-D21CCE25E2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0201BB3E-1850-450E-9979-C1FC1EDC195C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Stack" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="496">
   <si>
     <t>NextJS</t>
   </si>
@@ -1722,6 +1722,27 @@
   </si>
   <si>
     <t>ELB Terminology</t>
+  </si>
+  <si>
+    <t>Samba4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        v</t>
+  </si>
+  <si>
+    <t>Solutions Architect Associate (SAA-C03)</t>
+  </si>
+  <si>
+    <t>Solutions Architect Professional</t>
+  </si>
+  <si>
+    <t>Specialty Certifications</t>
+  </si>
+  <si>
+    <t>(Security / Networking / Data / ML)</t>
   </si>
 </sst>
 </file>
@@ -5164,7 +5185,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A39"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="98.7265625" style="4" customWidth="1"/>
@@ -5259,6 +5280,46 @@
     <row r="39" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A39" s="21" t="s">
         <v>405</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A46" s="4" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A47" s="4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A48" s="4" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A49" s="4" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A50" s="4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A51" s="4" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A52" s="4" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A53" s="4" t="s">
+        <v>495</v>
       </c>
     </row>
   </sheetData>
@@ -5272,7 +5333,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD312072-87FE-40B5-A445-1591614412BD}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="123.36328125" customWidth="1"/>
@@ -5331,6 +5392,11 @@
         <v>359</v>
       </c>
     </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>489</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0201BB3E-1850-450E-9979-C1FC1EDC195C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731D6759-7E23-4C95-B776-F849F9B399D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Stack" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="513">
   <si>
     <t>NextJS</t>
   </si>
@@ -1744,12 +1744,63 @@
   <si>
     <t>(Security / Networking / Data / ML)</t>
   </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Amazon EC2</t>
+  </si>
+  <si>
+    <t>Run individual virtual servers</t>
+  </si>
+  <si>
+    <t>Amazon EMR</t>
+  </si>
+  <si>
+    <t>Amazon Athena</t>
+  </si>
+  <si>
+    <t>Run SQL queries directly on S3</t>
+  </si>
+  <si>
+    <t>Data warehouse analytics</t>
+  </si>
+  <si>
+    <t>Process huge datasets using clusters (With Hadoop)</t>
+  </si>
+  <si>
+    <t>Amazon DynamoDB</t>
+  </si>
+  <si>
+    <t>AWS Glue</t>
+  </si>
+  <si>
+    <t> - AWS Glue is a fully managed extract, transform, and load (ETL) service </t>
+  </si>
+  <si>
+    <t>is a fully managed NoSQL database service provided by AWS that stores and retrieves data with very low latency (very fast response time) and can automatically scale.</t>
+  </si>
+  <si>
+    <t>throttled</t>
+  </si>
+  <si>
+    <t>Samba 4</t>
+  </si>
+  <si>
+    <t>Too many requests are coming, so AWS temporarily reduces or blocks extra requests to protect the service.</t>
+  </si>
+  <si>
+    <t>aws glue DataBrew</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1836,6 +1887,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1888,7 +1954,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1925,6 +1991,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2431,11 +2504,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD904FA-0FAD-46CD-8773-AE594AFC6DAB}">
-  <dimension ref="B10:G502"/>
+  <dimension ref="B10:G526"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="8.7265625" customWidth="1"/>
     <col min="6" max="6" width="130.1796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="32.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="10" spans="6:6" ht="409.5" x14ac:dyDescent="0.55000000000000004">
@@ -4941,6 +5015,72 @@
     <row r="502" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F502" s="2" t="s">
         <v>488</v>
+      </c>
+    </row>
+    <row r="513" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F513" s="22" t="s">
+        <v>496</v>
+      </c>
+      <c r="G513" s="22" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="514" spans="6:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="F514" s="23" t="s">
+        <v>498</v>
+      </c>
+      <c r="G514" s="23" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="515" spans="6:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="F515" s="23" t="s">
+        <v>500</v>
+      </c>
+      <c r="G515" s="23" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="516" spans="6:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="F516" s="23" t="s">
+        <v>501</v>
+      </c>
+      <c r="G516" s="23" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="517" spans="6:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="F517" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="G517" s="23" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="519" spans="6:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="F519" s="24" t="s">
+        <v>506</v>
+      </c>
+      <c r="G519" s="23" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="522" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F522" t="s">
+        <v>505</v>
+      </c>
+      <c r="G522" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="524" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F524" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="526" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F526" s="2" t="s">
+        <v>512</v>
       </c>
     </row>
   </sheetData>
@@ -5333,7 +5473,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD312072-87FE-40B5-A445-1591614412BD}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="123.36328125" customWidth="1"/>
@@ -5397,6 +5537,14 @@
         <v>489</v>
       </c>
     </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>509</v>
+      </c>
+      <c r="B12" t="s">
+        <v>511</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731D6759-7E23-4C95-B776-F849F9B399D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C74FCA-FA86-4C55-B804-93A914097129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="522">
   <si>
     <t>NextJS</t>
   </si>
@@ -1795,12 +1795,39 @@
   <si>
     <t>aws glue DataBrew</t>
   </si>
+  <si>
+    <t>PAN CARD Original</t>
+  </si>
+  <si>
+    <t>Ipsec</t>
+  </si>
+  <si>
+    <t>Internet Protocol security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightsail </t>
+  </si>
+  <si>
+    <t>UDAMY ON TV</t>
+  </si>
+  <si>
+    <t>Prepare for the best, forget about TEST.</t>
+  </si>
+  <si>
+    <t>Phani Kumar from Tag group</t>
+  </si>
+  <si>
+    <t>MPP</t>
+  </si>
+  <si>
+    <t>Masive Parallel Processing</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1902,8 +1929,15 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="3" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1940,6 +1974,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF00FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1954,7 +2000,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1998,6 +2044,8 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2007,6 +2055,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF00FF"/>
       <color rgb="FFFF0066"/>
       <color rgb="FFCC3300"/>
     </mruColors>
@@ -2309,7 +2358,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="91.81640625" style="1" customWidth="1"/>
@@ -2487,9 +2536,24 @@
         <v>84</v>
       </c>
     </row>
+    <row r="59" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="25" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A66" s="26" t="s">
+        <v>518</v>
       </c>
     </row>
   </sheetData>
@@ -2504,7 +2568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD904FA-0FAD-46CD-8773-AE594AFC6DAB}">
-  <dimension ref="B10:G526"/>
+  <dimension ref="B10:G534"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="8.7265625" customWidth="1"/>
@@ -5081,6 +5145,27 @@
     <row r="526" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F526" s="2" t="s">
         <v>512</v>
+      </c>
+    </row>
+    <row r="528" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F528" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="G528" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="531" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F531" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="534" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F534" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="G534" t="s">
+        <v>521</v>
       </c>
     </row>
   </sheetData>
@@ -5325,7 +5410,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A53"/>
+  <dimension ref="A1:A58"/>
   <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="98.7265625" style="4" customWidth="1"/>
@@ -5460,6 +5545,16 @@
     <row r="53" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
         <v>495</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A56" s="26" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A58" s="4" t="s">
+        <v>519</v>
       </c>
     </row>
   </sheetData>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C74FCA-FA86-4C55-B804-93A914097129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AA4E09-78CA-463F-A578-BBD650440095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,6 +13,7 @@
     <sheet name="DynPro" sheetId="5" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId4"/>
     <sheet name="Need to address" sheetId="6" r:id="rId5"/>
+    <sheet name="LYNUX COMMADS" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="580">
   <si>
     <t>NextJS</t>
   </si>
@@ -68,9 +69,6 @@
   </si>
   <si>
     <t>Preparing FAQ's on all topics</t>
-  </si>
-  <si>
-    <t>Pyton</t>
   </si>
   <si>
     <t>datastructure and algorithems</t>
@@ -1814,20 +1812,219 @@
     <t>Prepare for the best, forget about TEST.</t>
   </si>
   <si>
-    <t>Phani Kumar from Tag group</t>
-  </si>
-  <si>
     <t>MPP</t>
   </si>
   <si>
     <t>Masive Parallel Processing</t>
+  </si>
+  <si>
+    <t>VPN</t>
+  </si>
+  <si>
+    <t>Prepare for the best, forget about result/test</t>
+  </si>
+  <si>
+    <t>Chiropractor</t>
+  </si>
+  <si>
+    <t>Floor, 680, 13th Cross Rd, 1st Sector, HSR Layout, Bengaluru,  9606270303</t>
+  </si>
+  <si>
+    <t>JAW</t>
+  </si>
+  <si>
+    <t>Reserved insance</t>
+  </si>
+  <si>
+    <t>RI</t>
+  </si>
+  <si>
+    <t>Latency</t>
+  </si>
+  <si>
+    <t>is a time delay required for data request to travel across a network from request to destination and back</t>
+  </si>
+  <si>
+    <t>SAMBA</t>
+  </si>
+  <si>
+    <t>Is a measures the total amount of data successfully read or write per unit of time.</t>
+  </si>
+  <si>
+    <t>the amount of data transferred or processed in a given amount of time.</t>
+  </si>
+  <si>
+    <t>Linex commands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT </t>
+  </si>
+  <si>
+    <t>TO SEE FILE Content</t>
+  </si>
+  <si>
+    <t>CAT  /mnt/fsl/abc.txt</t>
+  </si>
+  <si>
+    <t>GWLB</t>
+  </si>
+  <si>
+    <t>Gateway Load Balancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCP </t>
+  </si>
+  <si>
+    <t>Layour 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP HTTPS </t>
+  </si>
+  <si>
+    <t>Layer 7</t>
+  </si>
+  <si>
+    <t>7. Application</t>
+  </si>
+  <si>
+    <t>6. Presentation</t>
+  </si>
+  <si>
+    <t>5. Session</t>
+  </si>
+  <si>
+    <t>4. Transport</t>
+  </si>
+  <si>
+    <t>3. Network</t>
+  </si>
+  <si>
+    <t>2. Data Link</t>
+  </si>
+  <si>
+    <t>1. Physical</t>
+  </si>
+  <si>
+    <t>ACM</t>
+  </si>
+  <si>
+    <t>AWS Certificate Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNI </t>
+  </si>
+  <si>
+    <t>ServerName Indicator</t>
+  </si>
+  <si>
+    <t>threshold</t>
+  </si>
+  <si>
+    <t>, a threshold is a predefined limit or value that, when reached or exceeded, triggers an action, alert, or change in behavi</t>
+  </si>
+  <si>
+    <t>AWS Security Groups control network traffic to AWS resources that have network interfaces ( ENIs)</t>
+  </si>
+  <si>
+    <t>EC2</t>
+  </si>
+  <si>
+    <t>RDS</t>
+  </si>
+  <si>
+    <t>ElasticCache</t>
+  </si>
+  <si>
+    <t>EFS</t>
+  </si>
+  <si>
+    <t>Lambda</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=UdB-vk8pe-Q</t>
+  </si>
+  <si>
+    <t>Delete or arrange photo in phone and computer</t>
+  </si>
+  <si>
+    <t>CRR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRR </t>
+  </si>
+  <si>
+    <t>Cross Region Replication</t>
+  </si>
+  <si>
+    <t>Same Region Replication</t>
+  </si>
+  <si>
+    <t>YAV3160637</t>
+  </si>
+  <si>
+    <t>ATHENA</t>
+  </si>
+  <si>
+    <t>DATA ANALYSIS TOOL</t>
+  </si>
+  <si>
+    <t>S3 LENCES</t>
+  </si>
+  <si>
+    <t>S3 GLACIER VALUT LOCK</t>
+  </si>
+  <si>
+    <t>Edge Locations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDN </t>
+  </si>
+  <si>
+    <t>CloudFront</t>
+  </si>
+  <si>
+    <t>AWS Global accelerator   Unicast IP VS AnyCast IP</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AWS Snowball  - for  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Deprecated</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">   (To Migrate data between edge location and client or edge location to aws)</t>
+    </r>
+  </si>
+  <si>
+    <t>Hybrid Cloud Storage</t>
+  </si>
+  <si>
+    <t>AWS Store gateway    Bridge Between on-premises data and cloud data</t>
+  </si>
+  <si>
+    <t>difference route 53 and aws cloudFront</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1936,8 +2133,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1947,12 +2158,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0066"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC3300"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1986,6 +2191,48 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2000,23 +2247,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -2044,8 +2290,33 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2358,11 +2629,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D66"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D80"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="91.81640625" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.7265625" style="1"/>
+    <col min="2" max="2" width="90.7265625" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -2382,7 +2654,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
@@ -2425,75 +2697,75 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="6" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
+      <c r="D23" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="10"/>
+    </row>
+    <row r="29" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="10"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="11"/>
-    </row>
-    <row r="30" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="11"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.35">
@@ -2501,1086 +2773,1115 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A42" s="1" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A45" s="12" t="s">
-        <v>25</v>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A53" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A55" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="25" t="s">
-        <v>513</v>
+    <row r="58" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="24" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" s="1" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A66" s="26" t="s">
-        <v>518</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A65" s="25" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" s="1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" s="28" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="28" t="s">
+        <v>522</v>
+      </c>
+      <c r="B70" s="28" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" s="1" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" s="1" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" s="20" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" s="1" t="s">
+        <v>567</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A45" r:id="rId2" display="https://www.flipkart.com/accutrust-smart-visual-ear-wax-cleaner-5mp-hd-camera-wifi-connectivity-electric/p/itm0315faef11f13?pid=EECHGXCWFRH6XZHA&amp;lid=LSTEECHGXCWFRH6XZHAISPLFA&amp;marketplace=FLIPKART&amp;cmpid=content_electric-ear-cleaner_8965229628_gmc&amp;affExtParam1=YT3-z2rvmWPrOgxlKmfc_aEoLuOMgI-j9wjho2LRdfrZUYxb7nMHeUixAxq1wdbLmpADGix8YWLsz2ErZwLHghUe8bs&amp;affid=ytflipkart" xr:uid="{43FE7E05-99E0-44FD-92C6-50DC9E76E9D2}"/>
+    <hyperlink ref="A25" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A44" r:id="rId2" display="https://www.flipkart.com/accutrust-smart-visual-ear-wax-cleaner-5mp-hd-camera-wifi-connectivity-electric/p/itm0315faef11f13?pid=EECHGXCWFRH6XZHA&amp;lid=LSTEECHGXCWFRH6XZHAISPLFA&amp;marketplace=FLIPKART&amp;cmpid=content_electric-ear-cleaner_8965229628_gmc&amp;affExtParam1=YT3-z2rvmWPrOgxlKmfc_aEoLuOMgI-j9wjho2LRdfrZUYxb7nMHeUixAxq1wdbLmpADGix8YWLsz2ErZwLHghUe8bs&amp;affid=ytflipkart" xr:uid="{43FE7E05-99E0-44FD-92C6-50DC9E76E9D2}"/>
+    <hyperlink ref="A77" r:id="rId3" xr:uid="{848F9BED-8591-4632-A158-BADB42AFF627}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD904FA-0FAD-46CD-8773-AE594AFC6DAB}">
-  <dimension ref="B10:G534"/>
+  <dimension ref="B10:G593"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="8.7265625" customWidth="1"/>
     <col min="6" max="6" width="130.1796875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="32.6328125" customWidth="1"/>
+    <col min="7" max="7" width="32.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="10" spans="6:6" ht="409.5" x14ac:dyDescent="0.55000000000000004">
       <c r="F10" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F32" s="15" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F32" s="16" t="s">
+    <row r="33" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F33" s="15" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F33" s="16" t="s">
+    <row r="34" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F34" s="15" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F34" s="16" t="s">
+    <row r="35" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F35" s="15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F35" s="16" t="s">
+    <row r="36" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F36" s="15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="37" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F37" s="15" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="36" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F36" s="16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="37" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F37" s="16" t="s">
+    <row r="38" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F38" s="15" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="38" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F38" s="16" t="s">
-        <v>94</v>
-      </c>
-    </row>
     <row r="39" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F39" s="16"/>
+      <c r="F39" s="15"/>
     </row>
     <row r="40" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F40" s="16"/>
+      <c r="F40" s="15"/>
     </row>
     <row r="41" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F41" s="16" t="s">
+      <c r="F41" s="15" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="42" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F42" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="42" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F42" s="16" t="s">
+    <row r="43" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F43" s="15" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="43" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F43" s="16" t="s">
+    <row r="44" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F44" s="15" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="44" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F44" s="16" t="s">
+    <row r="45" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F45" s="15" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F45" s="16" t="s">
+    <row r="46" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F46" s="15" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="46" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F46" s="16" t="s">
+    <row r="47" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F47" s="15" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="47" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F47" s="16" t="s">
+    <row r="48" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F48" s="15" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="48" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F48" s="16" t="s">
+    <row r="49" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E49" s="15"/>
+      <c r="F49" s="15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E50" s="15"/>
+      <c r="F50" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E51" s="15"/>
+      <c r="F51" s="15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E52" s="15"/>
+      <c r="F52" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E53" s="15"/>
+      <c r="F53" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E54" s="15"/>
+      <c r="F54" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="55" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E55" s="15"/>
+      <c r="F55" s="15" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="56" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E56" s="15"/>
+      <c r="F56" s="15" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="49" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E49" s="16"/>
-      <c r="F49" s="16" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="50" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E50" s="16"/>
-      <c r="F50" s="16" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="51" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E51" s="16"/>
-      <c r="F51" s="16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E52" s="16"/>
-      <c r="F52" s="16" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="53" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E53" s="16"/>
-      <c r="F53" s="16" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="54" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E54" s="16"/>
-      <c r="F54" s="16" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="55" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E55" s="16"/>
-      <c r="F55" s="16" t="s">
+    <row r="57" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E57" s="15"/>
+      <c r="F57" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="58" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E58" s="15"/>
+      <c r="F58" s="15" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="56" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E56" s="16"/>
-      <c r="F56" s="16" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="57" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E57" s="16"/>
-      <c r="F57" s="16" t="s">
+    <row r="59" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E59" s="15"/>
+      <c r="F59" s="15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="60" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E60" s="15"/>
+      <c r="F60" s="15" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="58" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E58" s="16"/>
-      <c r="F58" s="16" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="59" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E59" s="16"/>
-      <c r="F59" s="16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="60" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E60" s="16"/>
-      <c r="F60" s="16" t="s">
+    <row r="61" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E61" s="15"/>
+      <c r="F61" s="15"/>
+    </row>
+    <row r="62" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E62" s="15"/>
+      <c r="F62" s="15"/>
+    </row>
+    <row r="63" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E63" s="15"/>
+      <c r="F63" s="15"/>
+    </row>
+    <row r="64" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E64" s="15"/>
+      <c r="F64" s="15" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="61" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E61" s="16"/>
-      <c r="F61" s="16"/>
-    </row>
-    <row r="62" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
-    </row>
-    <row r="63" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E63" s="16"/>
-      <c r="F63" s="16"/>
-    </row>
-    <row r="64" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E64" s="16"/>
-      <c r="F64" s="16" t="s">
+    <row r="65" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E65" s="15"/>
+      <c r="F65" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="65" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E65" s="16"/>
-      <c r="F65" s="16" t="s">
+    <row r="66" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E66" s="15"/>
+      <c r="F66" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="66" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E66" s="16"/>
-      <c r="F66" s="16" t="s">
+    <row r="67" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E67" s="15"/>
+      <c r="F67" s="15" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="67" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E67" s="16"/>
-      <c r="F67" s="16" t="s">
+    <row r="68" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E68" s="15"/>
+      <c r="F68" s="15" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="68" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E68" s="16"/>
-      <c r="F68" s="16" t="s">
+    <row r="69" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E69" s="15"/>
+      <c r="F69" s="15" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="69" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E69" s="16"/>
-      <c r="F69" s="16" t="s">
+    <row r="70" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E70" s="15"/>
+      <c r="F70" s="15" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="70" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E70" s="16"/>
-      <c r="F70" s="16" t="s">
+    <row r="71" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E71" s="15"/>
+      <c r="F71" s="15" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="71" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E71" s="16"/>
-      <c r="F71" s="16" t="s">
+    <row r="72" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E72" s="15"/>
+      <c r="F72" s="15" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="72" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E72" s="16"/>
-      <c r="F72" s="16" t="s">
+    <row r="73" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E73" s="15"/>
+      <c r="F73" s="15" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="73" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E73" s="16"/>
-      <c r="F73" s="16" t="s">
+    <row r="74" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E74" s="15"/>
+      <c r="F74" s="15" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="74" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E74" s="16"/>
-      <c r="F74" s="16" t="s">
+    <row r="75" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E75" s="15"/>
+      <c r="F75" s="15" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="75" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E75" s="16"/>
-      <c r="F75" s="16" t="s">
+    <row r="76" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E76" s="15"/>
+      <c r="F76" s="15" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="76" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E76" s="16"/>
-      <c r="F76" s="16" t="s">
+    <row r="77" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E77" s="15"/>
+      <c r="F77" s="15" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="77" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E77" s="16"/>
-      <c r="F77" s="16" t="s">
+    <row r="78" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E78" s="15"/>
+      <c r="F78" s="15" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="78" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E78" s="16"/>
-      <c r="F78" s="16" t="s">
+    <row r="79" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E79" s="15"/>
+      <c r="F79" s="15" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="79" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E79" s="16"/>
-      <c r="F79" s="16" t="s">
+    <row r="80" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E80" s="15"/>
+      <c r="F80" s="15" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="80" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E80" s="16"/>
-      <c r="F80" s="16" t="s">
+    <row r="81" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E81" s="15"/>
+      <c r="F81" s="15" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="81" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E81" s="16"/>
-      <c r="F81" s="16" t="s">
+    <row r="82" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E82" s="15"/>
+      <c r="F82" s="15" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="82" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E82" s="16"/>
-      <c r="F82" s="16" t="s">
+    <row r="83" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E83" s="15"/>
+      <c r="F83" s="15" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="83" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E83" s="16"/>
-      <c r="F83" s="16" t="s">
+    <row r="84" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E84" s="15"/>
+      <c r="F84" s="15"/>
+    </row>
+    <row r="85" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E85" s="15"/>
+      <c r="F85" s="15"/>
+    </row>
+    <row r="86" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E86" s="15"/>
+      <c r="F86" s="15" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="84" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E84" s="16"/>
-      <c r="F84" s="16"/>
-    </row>
-    <row r="85" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E85" s="16"/>
-      <c r="F85" s="16"/>
-    </row>
-    <row r="86" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E86" s="16"/>
-      <c r="F86" s="16" t="s">
+    <row r="87" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E87" s="15"/>
+      <c r="F87" s="15" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="87" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E87" s="16"/>
-      <c r="F87" s="16" t="s">
+    <row r="88" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E88" s="15"/>
+      <c r="F88" s="15" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="88" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E88" s="16"/>
-      <c r="F88" s="16" t="s">
+    <row r="89" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E89" s="15"/>
+      <c r="F89" s="15"/>
+    </row>
+    <row r="90" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E90" s="15"/>
+      <c r="F90" s="15"/>
+    </row>
+    <row r="91" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E91" s="15"/>
+      <c r="F91" s="15" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="89" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E89" s="16"/>
-      <c r="F89" s="16"/>
-    </row>
-    <row r="90" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E90" s="16"/>
-      <c r="F90" s="16"/>
-    </row>
-    <row r="91" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E91" s="16"/>
-      <c r="F91" s="16" t="s">
+    <row r="92" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E92" s="15"/>
+      <c r="F92" s="15" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="92" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E92" s="16"/>
-      <c r="F92" s="16" t="s">
+    <row r="93" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E93" s="15"/>
+      <c r="F93" s="15" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="93" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E93" s="16"/>
-      <c r="F93" s="16" t="s">
+    <row r="94" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E94" s="15"/>
+      <c r="F94" s="15" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="94" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E94" s="16"/>
-      <c r="F94" s="16" t="s">
+    <row r="95" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E95" s="15"/>
+      <c r="F95" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="95" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E95" s="16"/>
-      <c r="F95" s="16" t="s">
+    <row r="96" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E96" s="15"/>
+      <c r="F96" s="15" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="96" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E96" s="16"/>
-      <c r="F96" s="16" t="s">
+    <row r="97" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E97" s="15"/>
+      <c r="F97" s="15" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="97" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E97" s="16"/>
-      <c r="F97" s="16" t="s">
+    <row r="98" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E98" s="15"/>
+      <c r="F98" s="15" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="98" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E98" s="16"/>
-      <c r="F98" s="16" t="s">
+    <row r="99" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E99" s="15"/>
+      <c r="F99" s="15" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="99" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E99" s="16"/>
-      <c r="F99" s="16" t="s">
+    <row r="100" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E100" s="15"/>
+      <c r="F100" s="15" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="100" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E100" s="16"/>
-      <c r="F100" s="16" t="s">
+    <row r="101" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E101" s="15"/>
+      <c r="F101" s="15" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="101" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E101" s="16"/>
-      <c r="F101" s="16" t="s">
+    <row r="102" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E102" s="15"/>
+      <c r="F102" s="15" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="102" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E102" s="16"/>
-      <c r="F102" s="16" t="s">
+    <row r="103" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E103" s="15"/>
+      <c r="F103" s="15" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="103" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E103" s="16"/>
-      <c r="F103" s="16" t="s">
+    <row r="104" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E104" s="15"/>
+      <c r="F104" s="15" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="104" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E104" s="16"/>
-      <c r="F104" s="16" t="s">
+    <row r="105" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E105" s="15"/>
+      <c r="F105" s="15" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="105" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E105" s="16"/>
-      <c r="F105" s="16" t="s">
+      <c r="G105" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="106" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E106" s="15"/>
+      <c r="F106" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="G105" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="106" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E106" s="16"/>
-      <c r="F106" s="16" t="s">
+    </row>
+    <row r="107" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E107" s="15"/>
+      <c r="F107" s="15"/>
+    </row>
+    <row r="108" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E108" s="15"/>
+      <c r="F108" s="15"/>
+    </row>
+    <row r="109" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E109" s="15"/>
+      <c r="F109" s="15" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="107" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E107" s="16"/>
-      <c r="F107" s="16"/>
-    </row>
-    <row r="108" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E108" s="16"/>
-      <c r="F108" s="16"/>
-    </row>
-    <row r="109" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E109" s="16"/>
-      <c r="F109" s="16" t="s">
+    <row r="110" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E110" s="15"/>
+      <c r="F110" s="15" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="110" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E110" s="16"/>
-      <c r="F110" s="16" t="s">
+    <row r="111" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E111" s="15"/>
+      <c r="F111" s="15" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="111" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E111" s="16"/>
-      <c r="F111" s="16" t="s">
+    <row r="112" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E112" s="15"/>
+      <c r="F112" s="15" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="112" spans="5:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E112" s="16"/>
-      <c r="F112" s="16" t="s">
+    <row r="113" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E113" s="15"/>
+      <c r="F113" s="15" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="113" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E113" s="16"/>
-      <c r="F113" s="16" t="s">
+    <row r="114" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E114" s="15"/>
+      <c r="F114" s="15" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="114" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E114" s="16"/>
-      <c r="F114" s="16" t="s">
+    <row r="115" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E115" s="15"/>
+      <c r="F115" s="15" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="115" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E115" s="16"/>
-      <c r="F115" s="16" t="s">
+    <row r="116" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E116" s="15"/>
+      <c r="F116" s="15" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="116" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E116" s="16"/>
-      <c r="F116" s="16" t="s">
+    <row r="117" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E117" s="15"/>
+      <c r="F117" s="15" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="117" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E117" s="16"/>
-      <c r="F117" s="16" t="s">
+    <row r="118" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E118" s="15"/>
+      <c r="F118" s="15" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="118" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E118" s="16"/>
-      <c r="F118" s="16" t="s">
+    <row r="119" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E119" s="15"/>
+      <c r="F119" s="15" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="119" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E119" s="16"/>
-      <c r="F119" s="16" t="s">
+    <row r="120" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E120" s="15"/>
+      <c r="F120" s="15" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="120" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E120" s="16"/>
-      <c r="F120" s="16" t="s">
+    <row r="121" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E121" s="15"/>
+      <c r="F121" s="15"/>
+    </row>
+    <row r="122" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E122" s="15"/>
+      <c r="F122" s="15"/>
+    </row>
+    <row r="123" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E123" s="15"/>
+      <c r="F123" s="15"/>
+    </row>
+    <row r="124" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E124" s="15"/>
+      <c r="F124" s="15" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="121" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E121" s="16"/>
-      <c r="F121" s="16"/>
-    </row>
-    <row r="122" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E122" s="16"/>
-      <c r="F122" s="16"/>
-    </row>
-    <row r="123" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E123" s="16"/>
-      <c r="F123" s="16"/>
-    </row>
-    <row r="124" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E124" s="16"/>
-      <c r="F124" s="16" t="s">
+    <row r="125" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E125" s="15"/>
+      <c r="F125" s="15" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="125" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E125" s="16"/>
-      <c r="F125" s="16" t="s">
+    <row r="126" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E126" s="15"/>
+      <c r="F126" s="15" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="126" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E126" s="16"/>
-      <c r="F126" s="16" t="s">
+    <row r="127" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E127" s="15"/>
+      <c r="F127" s="15" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="127" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E127" s="16"/>
-      <c r="F127" s="16" t="s">
+    <row r="128" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E128" s="15"/>
+      <c r="F128" s="15" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="128" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E128" s="16"/>
-      <c r="F128" s="16" t="s">
+    <row r="129" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E129" s="15"/>
+      <c r="F129" s="15" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="129" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E129" s="16"/>
-      <c r="F129" s="16" t="s">
+    <row r="130" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E130" s="15"/>
+      <c r="F130" s="15" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="130" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E130" s="16"/>
-      <c r="F130" s="16" t="s">
+    <row r="131" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E131" s="15"/>
+      <c r="F131" s="15" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="131" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E131" s="16"/>
-      <c r="F131" s="16" t="s">
+    <row r="132" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E132" s="15"/>
+      <c r="F132" s="15" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="132" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E132" s="16"/>
-      <c r="F132" s="16" t="s">
+    <row r="133" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E133" s="15"/>
+      <c r="F133" s="15" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="133" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E133" s="16"/>
-      <c r="F133" s="16" t="s">
+    <row r="134" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E134" s="15"/>
+      <c r="F134" s="15" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="134" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E134" s="16"/>
-      <c r="F134" s="16" t="s">
+    <row r="135" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E135" s="15"/>
+      <c r="F135" s="15" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="135" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E135" s="16"/>
-      <c r="F135" s="16" t="s">
+    <row r="136" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E136" s="15"/>
+      <c r="F136" s="15" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="136" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E136" s="16"/>
-      <c r="F136" s="16" t="s">
+    <row r="137" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E137" s="15"/>
+      <c r="F137" s="15" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="137" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E137" s="16"/>
-      <c r="F137" s="16" t="s">
+    <row r="138" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E138" s="15"/>
+      <c r="F138" s="15" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="138" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E138" s="16"/>
-      <c r="F138" s="16" t="s">
+    <row r="139" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E139" s="15"/>
+      <c r="F139" s="15" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="139" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E139" s="16"/>
-      <c r="F139" s="16" t="s">
+    <row r="140" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E140" s="15"/>
+      <c r="F140" s="15" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="140" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E140" s="16"/>
-      <c r="F140" s="16" t="s">
+    <row r="141" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E141" s="15"/>
+      <c r="F141" s="15" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="141" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E141" s="16"/>
-      <c r="F141" s="16" t="s">
+    <row r="142" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E142" s="15"/>
+      <c r="F142" s="15" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="142" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E142" s="16"/>
-      <c r="F142" s="16" t="s">
+    <row r="143" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E143" s="15"/>
+      <c r="F143" s="15" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="143" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E143" s="16"/>
-      <c r="F143" s="16" t="s">
+    <row r="144" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E144" s="15"/>
+      <c r="F144" s="15" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="144" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E144" s="16"/>
-      <c r="F144" s="16" t="s">
+    <row r="145" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E145" s="15"/>
+      <c r="F145" s="15" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="145" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E145" s="16"/>
-      <c r="F145" s="16" t="s">
+    <row r="146" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E146" s="15"/>
+      <c r="F146" s="15" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="146" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E146" s="16"/>
-      <c r="F146" s="16" t="s">
+    <row r="147" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E147" s="15"/>
+      <c r="F147" s="15" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="147" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E147" s="16"/>
-      <c r="F147" s="16" t="s">
+    <row r="148" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E148" s="15"/>
+      <c r="F148" s="15" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="148" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E148" s="16"/>
-      <c r="F148" s="16" t="s">
+    <row r="149" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E149" s="15"/>
+      <c r="F149" s="15" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="149" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E149" s="16"/>
-      <c r="F149" s="16" t="s">
+    <row r="150" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E150" s="15"/>
+      <c r="F150" s="15" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="150" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E150" s="16"/>
-      <c r="F150" s="16" t="s">
+    <row r="151" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E151" s="15"/>
+      <c r="F151" s="15"/>
+    </row>
+    <row r="152" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E152" s="15"/>
+      <c r="F152" s="15"/>
+    </row>
+    <row r="153" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E153" s="15"/>
+      <c r="F153" s="15" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="151" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E151" s="16"/>
-      <c r="F151" s="16"/>
-    </row>
-    <row r="152" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E152" s="16"/>
-      <c r="F152" s="16"/>
-    </row>
-    <row r="153" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E153" s="16"/>
-      <c r="F153" s="16" t="s">
-        <v>197</v>
-      </c>
-    </row>
     <row r="154" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E154" s="16"/>
-      <c r="F154" s="16" t="s">
+      <c r="E154" s="15"/>
+      <c r="F154" s="15" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="155" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E155" s="15"/>
+      <c r="F155" s="15" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="155" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E155" s="16"/>
-      <c r="F155" s="16" t="s">
+    <row r="156" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E156" s="15"/>
+      <c r="F156" s="15" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="156" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E156" s="16"/>
-      <c r="F156" s="16" t="s">
+    <row r="157" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E157" s="15"/>
+      <c r="F157" s="15" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="157" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E157" s="16"/>
-      <c r="F157" s="16" t="s">
-        <v>205</v>
-      </c>
-    </row>
     <row r="158" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E158" s="16"/>
-      <c r="F158" s="16" t="s">
+      <c r="E158" s="15"/>
+      <c r="F158" s="15" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="159" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E159" s="15"/>
+      <c r="F159" s="15" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="159" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E159" s="16"/>
-      <c r="F159" s="16" t="s">
+    <row r="160" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E160" s="15"/>
+      <c r="F160" s="15" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="160" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E160" s="16"/>
-      <c r="F160" s="16" t="s">
+    <row r="161" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E161" s="15"/>
+      <c r="F161" s="15" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="161" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E161" s="16"/>
-      <c r="F161" s="16" t="s">
+    <row r="162" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E162" s="15"/>
+      <c r="F162" s="15" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="162" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E162" s="16"/>
-      <c r="F162" s="16" t="s">
+    <row r="163" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E163" s="15"/>
+      <c r="F163" s="15" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="163" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E163" s="16"/>
-      <c r="F163" s="16" t="s">
+    <row r="164" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E164" s="15"/>
+      <c r="F164" s="15" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="164" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E164" s="16"/>
-      <c r="F164" s="16" t="s">
+    <row r="165" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E165" s="15"/>
+      <c r="F165" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="166" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E166" s="15"/>
+      <c r="F166" s="15" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="165" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E165" s="16"/>
-      <c r="F165" s="16" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="166" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E166" s="16"/>
-      <c r="F166" s="16" t="s">
+    <row r="167" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E167" s="15"/>
+      <c r="F167" s="15" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="167" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E167" s="16"/>
-      <c r="F167" s="16" t="s">
+    <row r="168" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E168" s="15"/>
+      <c r="F168" s="15" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="168" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E168" s="16"/>
-      <c r="F168" s="16" t="s">
+    <row r="169" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E169" s="15"/>
+      <c r="F169" s="15" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="169" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E169" s="16"/>
-      <c r="F169" s="16" t="s">
+    <row r="170" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E170" s="15"/>
+      <c r="F170" s="15" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="170" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E170" s="16"/>
-      <c r="F170" s="16" t="s">
+    <row r="171" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E171" s="15"/>
+      <c r="F171" s="15" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="171" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E171" s="16"/>
-      <c r="F171" s="16" t="s">
+    <row r="172" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E172" s="15"/>
+      <c r="F172" s="15" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="172" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E172" s="16"/>
-      <c r="F172" s="16" t="s">
+    <row r="173" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E173" s="15"/>
+      <c r="F173" s="15" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="173" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E173" s="16"/>
-      <c r="F173" s="16" t="s">
+    <row r="174" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E174" s="15"/>
+      <c r="F174" s="15" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="174" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E174" s="16"/>
-      <c r="F174" s="16" t="s">
+    <row r="175" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E175" s="15"/>
+      <c r="F175" s="15" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="175" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E175" s="16"/>
-      <c r="F175" s="16" t="s">
+    <row r="176" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E176" s="15"/>
+      <c r="F176" s="15" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="176" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E176" s="16"/>
-      <c r="F176" s="16" t="s">
+    <row r="177" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E177" s="15"/>
+      <c r="F177" s="15" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="177" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E177" s="16"/>
-      <c r="F177" s="16" t="s">
+    <row r="178" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E178" s="15"/>
+      <c r="F178" s="15" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="178" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E178" s="16"/>
-      <c r="F178" s="16" t="s">
+    <row r="179" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E179" s="15"/>
+      <c r="F179" s="15" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="179" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E179" s="16"/>
-      <c r="F179" s="16" t="s">
+    <row r="180" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E180" s="15"/>
+      <c r="F180" s="15" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="180" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E180" s="16"/>
-      <c r="F180" s="16" t="s">
+    <row r="181" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E181" s="15"/>
+      <c r="F181" s="15" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="181" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E181" s="16"/>
-      <c r="F181" s="16" t="s">
+    <row r="182" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E182" s="15"/>
+      <c r="F182" s="15" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="182" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E182" s="16"/>
-      <c r="F182" s="16" t="s">
+    <row r="183" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E183" s="15"/>
+      <c r="F183" s="15" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="183" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E183" s="16"/>
-      <c r="F183" s="16" t="s">
+    <row r="184" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E184" s="15"/>
+      <c r="F184" s="15" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="184" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E184" s="16"/>
-      <c r="F184" s="16" t="s">
+    <row r="185" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E185" s="15"/>
+      <c r="F185" s="15" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="185" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E185" s="16"/>
-      <c r="F185" s="16" t="s">
+    <row r="186" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E186" s="15"/>
+      <c r="F186" s="15" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="186" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E186" s="16"/>
-      <c r="F186" s="16" t="s">
+    <row r="187" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E187" s="15"/>
+      <c r="F187" s="15" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="187" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E187" s="16"/>
-      <c r="F187" s="16" t="s">
+    <row r="188" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E188" s="15"/>
+      <c r="F188" s="15"/>
+    </row>
+    <row r="189" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E189" s="15"/>
+      <c r="F189" s="15"/>
+    </row>
+    <row r="190" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E190" s="15"/>
+      <c r="F190" s="15"/>
+    </row>
+    <row r="191" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E191" s="15"/>
+      <c r="F191" s="15" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="188" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E188" s="16"/>
-      <c r="F188" s="16"/>
-    </row>
-    <row r="189" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E189" s="16"/>
-      <c r="F189" s="16"/>
-    </row>
-    <row r="190" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E190" s="16"/>
-      <c r="F190" s="16"/>
-    </row>
-    <row r="191" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E191" s="16"/>
-      <c r="F191" s="16" t="s">
+    <row r="192" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="E192" s="15"/>
+      <c r="F192" s="15" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="192" spans="5:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="E192" s="16"/>
-      <c r="F192" s="16" t="s">
+    <row r="193" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E193" s="15"/>
+      <c r="F193" s="15" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="193" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E193" s="16"/>
-      <c r="F193" s="16" t="s">
+    <row r="194" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E194" s="15"/>
+      <c r="F194" s="15" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="194" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E194" s="16"/>
-      <c r="F194" s="16" t="s">
+    <row r="195" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E195" s="15"/>
+      <c r="F195" s="15" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="195" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E195" s="16"/>
-      <c r="F195" s="16" t="s">
+    <row r="196" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E196" s="15"/>
+      <c r="F196" s="15" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="196" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E196" s="16"/>
-      <c r="F196" s="16" t="s">
+    <row r="197" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E197" s="15"/>
+      <c r="F197" s="15" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="197" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E197" s="16"/>
-      <c r="F197" s="16" t="s">
+    <row r="198" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E198" s="15"/>
+      <c r="F198" s="15" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="198" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E198" s="16"/>
-      <c r="F198" s="16" t="s">
+    <row r="199" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E199" s="15"/>
+      <c r="F199" s="15" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="199" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E199" s="16"/>
-      <c r="F199" s="16" t="s">
+    <row r="200" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E200" s="15"/>
+      <c r="F200" s="15" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="200" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E200" s="16"/>
-      <c r="F200" s="16" t="s">
+    <row r="201" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E201" s="15"/>
+      <c r="F201" s="15"/>
+    </row>
+    <row r="202" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E202" s="15"/>
+      <c r="F202" s="15"/>
+    </row>
+    <row r="203" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E203" s="15"/>
+      <c r="F203" s="15" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="201" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E201" s="16"/>
-      <c r="F201" s="16"/>
-    </row>
-    <row r="202" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E202" s="16"/>
-      <c r="F202" s="16"/>
-    </row>
-    <row r="203" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E203" s="16"/>
-      <c r="F203" s="16" t="s">
+    <row r="204" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E204" s="15"/>
+      <c r="F204" s="15" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="204" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E204" s="16"/>
-      <c r="F204" s="16" t="s">
+      <c r="G204" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="205" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E205" s="15"/>
+      <c r="F205" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="G204" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="205" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E205" s="16"/>
-      <c r="F205" s="16" t="s">
+    </row>
+    <row r="206" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="E206" s="15"/>
+      <c r="F206" s="15" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="206" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="E206" s="16"/>
-      <c r="F206" s="16" t="s">
+    <row r="207" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+      <c r="F207" s="15" t="s">
         <v>249</v>
-      </c>
-    </row>
-    <row r="207" spans="2:7" ht="21" x14ac:dyDescent="0.5">
-      <c r="F207" s="16" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="208" spans="2:7" ht="21" x14ac:dyDescent="0.5">
@@ -3588,8 +3889,8 @@
       <c r="C208" s="4"/>
       <c r="D208" s="4"/>
       <c r="E208" s="4"/>
-      <c r="F208" s="16" t="s">
-        <v>253</v>
+      <c r="F208" s="15" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="209" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3597,8 +3898,8 @@
       <c r="C209" s="4"/>
       <c r="D209" s="4"/>
       <c r="E209" s="4"/>
-      <c r="F209" s="17" t="s">
-        <v>254</v>
+      <c r="F209" s="16" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="210" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3606,8 +3907,8 @@
       <c r="C210" s="4"/>
       <c r="D210" s="4"/>
       <c r="E210" s="4"/>
-      <c r="F210" s="17" t="s">
-        <v>255</v>
+      <c r="F210" s="16" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="211" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3615,8 +3916,8 @@
       <c r="C211" s="4"/>
       <c r="D211" s="4"/>
       <c r="E211" s="4"/>
-      <c r="F211" s="17" t="s">
-        <v>257</v>
+      <c r="F211" s="16" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="212" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3624,8 +3925,8 @@
       <c r="C212" s="4"/>
       <c r="D212" s="4"/>
       <c r="E212" s="4"/>
-      <c r="F212" s="17" t="s">
-        <v>258</v>
+      <c r="F212" s="16" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="213" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3633,8 +3934,8 @@
       <c r="C213" s="4"/>
       <c r="D213" s="4"/>
       <c r="E213" s="4"/>
-      <c r="F213" s="17" t="s">
-        <v>259</v>
+      <c r="F213" s="16" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="214" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3642,8 +3943,8 @@
       <c r="C214" s="4"/>
       <c r="D214" s="4"/>
       <c r="E214" s="4"/>
-      <c r="F214" s="17" t="s">
-        <v>260</v>
+      <c r="F214" s="16" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="215" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3651,8 +3952,8 @@
       <c r="C215" s="4"/>
       <c r="D215" s="4"/>
       <c r="E215" s="4"/>
-      <c r="F215" s="17" t="s">
-        <v>261</v>
+      <c r="F215" s="16" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="216" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3660,8 +3961,8 @@
       <c r="C216" s="4"/>
       <c r="D216" s="4"/>
       <c r="E216" s="4"/>
-      <c r="F216" s="17" t="s">
-        <v>262</v>
+      <c r="F216" s="16" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="217" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3669,8 +3970,8 @@
       <c r="C217" s="4"/>
       <c r="D217" s="4"/>
       <c r="E217" s="4"/>
-      <c r="F217" s="17" t="s">
-        <v>263</v>
+      <c r="F217" s="16" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="218" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3678,29 +3979,29 @@
       <c r="C218" s="4"/>
       <c r="D218" s="4"/>
       <c r="E218" s="4"/>
-      <c r="F218" s="17"/>
+      <c r="F218" s="16"/>
     </row>
     <row r="219" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
-      <c r="F219" s="17"/>
+      <c r="F219" s="16"/>
     </row>
     <row r="220" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
       <c r="D220" s="4"/>
       <c r="E220" s="4"/>
-      <c r="F220" s="17"/>
+      <c r="F220" s="16"/>
     </row>
     <row r="221" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
       <c r="D221" s="4"/>
       <c r="E221" s="4"/>
-      <c r="F221" s="17" t="s">
-        <v>264</v>
+      <c r="F221" s="16" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="222" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3708,8 +4009,8 @@
       <c r="C222" s="4"/>
       <c r="D222" s="4"/>
       <c r="E222" s="4"/>
-      <c r="F222" s="17" t="s">
-        <v>265</v>
+      <c r="F222" s="16" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="223" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3717,8 +4018,8 @@
       <c r="C223" s="4"/>
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
-      <c r="F223" s="17" t="s">
-        <v>266</v>
+      <c r="F223" s="16" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="224" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3726,8 +4027,8 @@
       <c r="C224" s="4"/>
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
-      <c r="F224" s="17" t="s">
-        <v>267</v>
+      <c r="F224" s="16" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="225" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3735,8 +4036,8 @@
       <c r="C225" s="4"/>
       <c r="D225" s="4"/>
       <c r="E225" s="4"/>
-      <c r="F225" s="17" t="s">
-        <v>268</v>
+      <c r="F225" s="16" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="226" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3744,8 +4045,8 @@
       <c r="C226" s="4"/>
       <c r="D226" s="4"/>
       <c r="E226" s="4"/>
-      <c r="F226" s="17" t="s">
-        <v>269</v>
+      <c r="F226" s="16" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="227" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3753,8 +4054,8 @@
       <c r="C227" s="4"/>
       <c r="D227" s="4"/>
       <c r="E227" s="4"/>
-      <c r="F227" s="17" t="s">
-        <v>270</v>
+      <c r="F227" s="16" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="228" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3762,8 +4063,8 @@
       <c r="C228" s="4"/>
       <c r="D228" s="4"/>
       <c r="E228" s="4"/>
-      <c r="F228" s="17" t="s">
-        <v>271</v>
+      <c r="F228" s="16" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="229" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3771,8 +4072,8 @@
       <c r="C229" s="4"/>
       <c r="D229" s="4"/>
       <c r="E229" s="4"/>
-      <c r="F229" s="17" t="s">
-        <v>272</v>
+      <c r="F229" s="16" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="230" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3780,36 +4081,36 @@
       <c r="C230" s="4"/>
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
-      <c r="F230" s="17"/>
+      <c r="F230" s="16"/>
     </row>
     <row r="231" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
-      <c r="F231" s="17"/>
+      <c r="F231" s="16"/>
     </row>
     <row r="232" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
-      <c r="F232" s="17"/>
+      <c r="F232" s="16"/>
     </row>
     <row r="233" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
-      <c r="F233" s="17"/>
+      <c r="F233" s="16"/>
     </row>
     <row r="234" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
       <c r="D234" s="4"/>
       <c r="E234" s="4"/>
-      <c r="F234" s="17" t="s">
-        <v>273</v>
+      <c r="F234" s="16" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="235" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3817,8 +4118,8 @@
       <c r="C235" s="4"/>
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
-      <c r="F235" s="17" t="s">
-        <v>274</v>
+      <c r="F235" s="16" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="236" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3826,8 +4127,8 @@
       <c r="C236" s="4"/>
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
-      <c r="F236" s="17" t="s">
-        <v>275</v>
+      <c r="F236" s="16" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="237" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3835,8 +4136,8 @@
       <c r="C237" s="4"/>
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
-      <c r="F237" s="17" t="s">
-        <v>276</v>
+      <c r="F237" s="16" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="238" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3844,8 +4145,8 @@
       <c r="C238" s="4"/>
       <c r="D238" s="4"/>
       <c r="E238" s="4"/>
-      <c r="F238" s="17" t="s">
-        <v>277</v>
+      <c r="F238" s="16" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="239" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3853,8 +4154,8 @@
       <c r="C239" s="4"/>
       <c r="D239" s="4"/>
       <c r="E239" s="4"/>
-      <c r="F239" s="17" t="s">
-        <v>278</v>
+      <c r="F239" s="16" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="240" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3862,8 +4163,8 @@
       <c r="C240" s="4"/>
       <c r="D240" s="4"/>
       <c r="E240" s="4"/>
-      <c r="F240" s="17" t="s">
-        <v>279</v>
+      <c r="F240" s="16" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="241" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3871,8 +4172,8 @@
       <c r="C241" s="4"/>
       <c r="D241" s="4"/>
       <c r="E241" s="4"/>
-      <c r="F241" s="17" t="s">
-        <v>280</v>
+      <c r="F241" s="16" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="242" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3880,8 +4181,8 @@
       <c r="C242" s="4"/>
       <c r="D242" s="4"/>
       <c r="E242" s="4"/>
-      <c r="F242" s="17" t="s">
-        <v>281</v>
+      <c r="F242" s="16" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="243" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3889,29 +4190,29 @@
       <c r="C243" s="4"/>
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
-      <c r="F243" s="17"/>
+      <c r="F243" s="16"/>
     </row>
     <row r="244" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
       <c r="D244" s="4"/>
       <c r="E244" s="4"/>
-      <c r="F244" s="17"/>
+      <c r="F244" s="16"/>
     </row>
     <row r="245" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
       <c r="D245" s="4"/>
       <c r="E245" s="4"/>
-      <c r="F245" s="17"/>
+      <c r="F245" s="16"/>
     </row>
     <row r="246" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
       <c r="D246" s="4"/>
       <c r="E246" s="4"/>
-      <c r="F246" s="17" t="s">
-        <v>282</v>
+      <c r="F246" s="16" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="247" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3919,8 +4220,8 @@
       <c r="C247" s="4"/>
       <c r="D247" s="4"/>
       <c r="E247" s="4"/>
-      <c r="F247" s="17" t="s">
-        <v>283</v>
+      <c r="F247" s="16" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="248" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3928,8 +4229,8 @@
       <c r="C248" s="4"/>
       <c r="D248" s="4"/>
       <c r="E248" s="4"/>
-      <c r="F248" s="17" t="s">
-        <v>284</v>
+      <c r="F248" s="16" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="249" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3937,8 +4238,8 @@
       <c r="C249" s="4"/>
       <c r="D249" s="4"/>
       <c r="E249" s="4"/>
-      <c r="F249" s="17" t="s">
-        <v>285</v>
+      <c r="F249" s="16" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="250" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3946,8 +4247,8 @@
       <c r="C250" s="4"/>
       <c r="D250" s="4"/>
       <c r="E250" s="4"/>
-      <c r="F250" s="17" t="s">
-        <v>286</v>
+      <c r="F250" s="16" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="251" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3955,8 +4256,8 @@
       <c r="C251" s="4"/>
       <c r="D251" s="4"/>
       <c r="E251" s="4"/>
-      <c r="F251" s="17" t="s">
-        <v>287</v>
+      <c r="F251" s="16" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="252" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3964,8 +4265,8 @@
       <c r="C252" s="4"/>
       <c r="D252" s="4"/>
       <c r="E252" s="4"/>
-      <c r="F252" s="17" t="s">
-        <v>288</v>
+      <c r="F252" s="16" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="253" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3973,8 +4274,8 @@
       <c r="C253" s="4"/>
       <c r="D253" s="4"/>
       <c r="E253" s="4"/>
-      <c r="F253" s="17" t="s">
-        <v>289</v>
+      <c r="F253" s="16" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="254" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3982,8 +4283,8 @@
       <c r="C254" s="4"/>
       <c r="D254" s="4"/>
       <c r="E254" s="4"/>
-      <c r="F254" s="17" t="s">
-        <v>290</v>
+      <c r="F254" s="16" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="255" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -3991,29 +4292,29 @@
       <c r="C255" s="4"/>
       <c r="D255" s="4"/>
       <c r="E255" s="4"/>
-      <c r="F255" s="17"/>
+      <c r="F255" s="16"/>
     </row>
     <row r="256" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
       <c r="D256" s="4"/>
       <c r="E256" s="4"/>
-      <c r="F256" s="17"/>
+      <c r="F256" s="16"/>
     </row>
     <row r="257" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
       <c r="D257" s="4"/>
       <c r="E257" s="4"/>
-      <c r="F257" s="17"/>
+      <c r="F257" s="16"/>
     </row>
     <row r="258" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
       <c r="D258" s="4"/>
       <c r="E258" s="4"/>
-      <c r="F258" s="17" t="s">
-        <v>292</v>
+      <c r="F258" s="16" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="259" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -4021,22 +4322,22 @@
       <c r="C259" s="4"/>
       <c r="D259" s="4"/>
       <c r="E259" s="4"/>
-      <c r="F259" s="17"/>
+      <c r="F259" s="16"/>
     </row>
     <row r="260" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
       <c r="D260" s="4"/>
       <c r="E260" s="4"/>
-      <c r="F260" s="17"/>
+      <c r="F260" s="16"/>
     </row>
     <row r="261" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
       <c r="D261" s="4"/>
       <c r="E261" s="4"/>
-      <c r="F261" s="17" t="s">
-        <v>291</v>
+      <c r="F261" s="16" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="262" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -4044,8 +4345,8 @@
       <c r="C262" s="4"/>
       <c r="D262" s="4"/>
       <c r="E262" s="4"/>
-      <c r="F262" s="17" t="s">
-        <v>293</v>
+      <c r="F262" s="16" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="263" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -4053,8 +4354,8 @@
       <c r="C263" s="4"/>
       <c r="D263" s="4"/>
       <c r="E263" s="4"/>
-      <c r="F263" s="17" t="s">
-        <v>294</v>
+      <c r="F263" s="16" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="264" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -4062,8 +4363,8 @@
       <c r="C264" s="4"/>
       <c r="D264" s="4"/>
       <c r="E264" s="4"/>
-      <c r="F264" s="17" t="s">
-        <v>295</v>
+      <c r="F264" s="16" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="265" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -4071,8 +4372,8 @@
       <c r="C265" s="4"/>
       <c r="D265" s="4"/>
       <c r="E265" s="4"/>
-      <c r="F265" s="17" t="s">
-        <v>296</v>
+      <c r="F265" s="16" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="266" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -4080,22 +4381,22 @@
       <c r="C266" s="4"/>
       <c r="D266" s="4"/>
       <c r="E266" s="4"/>
-      <c r="F266" s="17"/>
+      <c r="F266" s="16"/>
     </row>
     <row r="267" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
       <c r="D267" s="4"/>
       <c r="E267" s="4"/>
-      <c r="F267" s="17"/>
+      <c r="F267" s="16"/>
     </row>
     <row r="268" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
       <c r="D268" s="4"/>
       <c r="E268" s="4"/>
-      <c r="F268" s="17" t="s">
-        <v>297</v>
+      <c r="F268" s="16" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="269" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -4103,8 +4404,8 @@
       <c r="C269" s="4"/>
       <c r="D269" s="4"/>
       <c r="E269" s="4"/>
-      <c r="F269" s="17" t="s">
-        <v>298</v>
+      <c r="F269" s="16" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="270" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -4112,8 +4413,8 @@
       <c r="C270" s="4"/>
       <c r="D270" s="4"/>
       <c r="E270" s="4"/>
-      <c r="F270" s="17" t="s">
-        <v>299</v>
+      <c r="F270" s="16" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="271" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -4121,29 +4422,29 @@
       <c r="C271" s="4"/>
       <c r="D271" s="4"/>
       <c r="E271" s="4"/>
-      <c r="F271" s="17"/>
+      <c r="F271" s="16"/>
     </row>
     <row r="272" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
       <c r="D272" s="4"/>
       <c r="E272" s="4"/>
-      <c r="F272" s="17"/>
+      <c r="F272" s="16"/>
     </row>
     <row r="273" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
       <c r="D273" s="4"/>
       <c r="E273" s="4"/>
-      <c r="F273" s="17"/>
+      <c r="F273" s="16"/>
     </row>
     <row r="274" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
       <c r="D274" s="4"/>
       <c r="E274" s="4"/>
-      <c r="F274" s="17" t="s">
-        <v>300</v>
+      <c r="F274" s="16" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="275" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
@@ -4151,1021 +4452,1216 @@
       <c r="C275" s="4"/>
       <c r="D275" s="4"/>
       <c r="E275" s="4"/>
-      <c r="F275" s="17" t="s">
-        <v>301</v>
+      <c r="F275" s="16" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="276" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F276" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="277" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F277" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="278" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F278" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="279" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F279" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="280" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F280" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="281" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F281" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="282" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F282" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="283" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F283" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="284" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F284" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="285" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F285" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="286" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F286" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G286" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="287" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F287" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="288" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F288" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="289" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F289" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="290" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F290" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="291" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F291" s="17" t="s">
         <v>317</v>
-      </c>
-    </row>
-    <row r="291" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F291" s="18" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="292" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F292" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="293" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F293" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="294" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F294" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="298" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F298" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="299" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F299" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="300" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F300" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="301" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F301" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="302" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F302" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="303" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F303" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="304" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F304" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="305" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F305" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="306" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F306" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="307" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F307" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="308" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F308" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="309" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F309" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="310" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F310" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="315" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F315" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="316" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F316" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="317" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F317" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="318" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F318" s="19" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="318" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F318" s="20" t="s">
+    <row r="319" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F319" s="19" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="319" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F319" s="20" t="s">
+    <row r="320" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F320" s="19" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="320" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F320" s="20" t="s">
+    <row r="321" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F321" s="19" t="s">
         <v>340</v>
-      </c>
-    </row>
-    <row r="321" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F321" s="20" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="322" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F322" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="325" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F325" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="326" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F326" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="327" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F327" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G327" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="328" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F328" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="329" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F329" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="330" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F330" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="331" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F331" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="332" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F332" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="333" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F333" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="334" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F334" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="335" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F335" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="336" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F336" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="339" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F339" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="342" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F342" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="343" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F343" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="344" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F344" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="345" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F345" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="346" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F346" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="347" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F347" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="348" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F348" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="349" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F349" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="350" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F350" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="355" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F355" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="356" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F356" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="357" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F357" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="358" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F358" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="359" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F359" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="360" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F360" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="361" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F361" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="362" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F362" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="363" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F363" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="364" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F364" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="365" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F365" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="366" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F366" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="367" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F367" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="368" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F368" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="371" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F371" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="373" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F373" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="377" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F377" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="380" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F380" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="382" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F382" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="383" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F383" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="384" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F384" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="385" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F385" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="386" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F386" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="387" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F387" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="390" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F390" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="391" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F391" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="392" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F392" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="393" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F393" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="394" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F394" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="395" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F395" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="398" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F398" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="399" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F399" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="400" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F400" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="401" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F401" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="402" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F402" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="403" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F403" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="408" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F408" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="410" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F410" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="411" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F411" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="412" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F412" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="413" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F413" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="414" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F414" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="415" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F415" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="416" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F416" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="417" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F417" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="418" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F418" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="419" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F419" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="420" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F420" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="421" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F421" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="422" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F422" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="423" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F423" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="424" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F424" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="427" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F427" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="428" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F428" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="429" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F429" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="430" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F430" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="431" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F431" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="432" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F432" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="433" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F433" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="434" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F434" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="435" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F435" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="436" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F436" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="437" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F437" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="438" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F438" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="439" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F439" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="440" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F440" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="441" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F441" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="442" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F442" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="443" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F443" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="444" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F444" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="445" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F445" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="446" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F446" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="447" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F447" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="448" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F448" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="449" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F449" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="450" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F450" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="453" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F453" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="454" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F454" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="455" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F455" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="456" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F456" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="457" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F457" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="458" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F458" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="459" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F459" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="460" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F460" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="461" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F461" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="462" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F462" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="463" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F463" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="464" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F464" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="465" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F465" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="466" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F466" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="467" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F467" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="468" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F468" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="469" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F469" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="470" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F470" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="473" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F473" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="474" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F474" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="475" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F475" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="476" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F476" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="477" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F477" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="478" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F478" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="479" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F479" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="480" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F480" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="481" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F481" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="482" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F482" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="483" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F483" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="484" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F484" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="485" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F485" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="486" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F486" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="487" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F487" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="488" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F488" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="491" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F491" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="492" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F492" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="493" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F493" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="494" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F494" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="495" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F495" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="496" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F496" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="497" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F497" s="2" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="497" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F497" s="2" t="s">
+    <row r="498" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F498" s="2" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="498" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F498" s="2" t="s">
+    <row r="499" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F499" s="2" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="499" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F499" s="2" t="s">
+    <row r="500" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F500" s="2" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="500" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F500" s="2" t="s">
+    <row r="501" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F501" s="2" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="501" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F501" s="2" t="s">
+    <row r="502" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F502" s="2" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="502" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F502" s="2" t="s">
-        <v>488</v>
+    <row r="503" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F503" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="G503" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="504" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F504" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="G504" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="513" spans="6:7" x14ac:dyDescent="0.35">
-      <c r="F513" s="22" t="s">
+      <c r="F513" s="21" t="s">
+        <v>495</v>
+      </c>
+      <c r="G513" s="21" t="s">
         <v>496</v>
       </c>
-      <c r="G513" s="22" t="s">
+    </row>
+    <row r="514" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F514" s="22" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="514" spans="6:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="F514" s="23" t="s">
+      <c r="G514" s="22" t="s">
         <v>498</v>
       </c>
-      <c r="G514" s="23" t="s">
+    </row>
+    <row r="515" spans="6:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="F515" s="22" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="515" spans="6:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="F515" s="23" t="s">
+      <c r="G515" s="22" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="516" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F516" s="22" t="s">
         <v>500</v>
       </c>
-      <c r="G515" s="23" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="516" spans="6:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="F516" s="23" t="s">
+      <c r="G516" s="22" t="s">
         <v>501</v>
       </c>
-      <c r="G516" s="23" t="s">
+    </row>
+    <row r="517" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F517" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="G517" s="22" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="517" spans="6:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="F517" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="G517" s="23" t="s">
-        <v>503</v>
-      </c>
-    </row>
     <row r="519" spans="6:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="F519" s="24" t="s">
+      <c r="F519" s="23" t="s">
+        <v>505</v>
+      </c>
+      <c r="G519" s="22" t="s">
         <v>506</v>
-      </c>
-      <c r="G519" s="23" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="522" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F522" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G522" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="524" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F524" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="526" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F526" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="528" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F528" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="G528" t="s">
         <v>514</v>
-      </c>
-      <c r="G528" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="531" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F531" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="534" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F534" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G534" t="s">
-        <v>521</v>
+        <v>519</v>
+      </c>
+    </row>
+    <row r="537" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F537" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="G537" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="539" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F539" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="541" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F541" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="G541" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="544" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F544" s="31" t="s">
+        <v>538</v>
+      </c>
+      <c r="G544" s="32" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="545" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F545" s="31" t="s">
+        <v>540</v>
+      </c>
+      <c r="G545" s="32" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="547" spans="6:7" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F547" s="29" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="548" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F548" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="549" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F549" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="550" spans="6:7" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F550" s="29" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="551" spans="6:7" s="30" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F551" s="29" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="552" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F552" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="553" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F553" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="557" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F557" s="35" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="558" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F558" s="35" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="559" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F559" s="35" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="560" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F560" s="35" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="561" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F561" s="35" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="562" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F562" s="35" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="565" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F565" s="34"/>
+    </row>
+    <row r="567" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F567" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="G567" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="568" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F568" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="G568" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="570" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F570" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="G570" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="574" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F574" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="575" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F575" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="581" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F581" s="40" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="582" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F582" s="40" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="583" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F583" s="40" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="584" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F584" s="40" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="585" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F585" s="40" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="589" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F589" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="590" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F590" s="2" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="593" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F593" s="2" t="s">
+        <v>579</v>
       </c>
     </row>
   </sheetData>
@@ -5179,228 +5675,228 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97581F73-ACDD-44F9-985C-0540C21B38C5}">
   <dimension ref="A1:C79"/>
-  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="21" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="98.1796875" style="15" customWidth="1"/>
-    <col min="2" max="2" width="22.36328125" style="15" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" style="15"/>
+    <col min="1" max="1" width="98.1796875" style="14" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" style="14" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="15" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="15" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="15" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="15" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="14" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="15" t="s">
+      <c r="B22" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="15" t="s">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="14" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="15" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="15" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="15" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="15" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="14" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="15" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="15" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="14" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="15" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="14" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="15" t="s">
+      <c r="B37" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="B37" s="15" t="s">
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="14" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="B38" s="15" t="s">
+      <c r="C38" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C38" s="15" t="s">
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="14" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="15" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="14" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="15" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="15" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="14" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="15" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="15" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="14" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="15" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C54" s="14" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C54" s="15" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="14" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="15" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="14" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="15" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="14" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="15" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="14" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="15" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="14" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="15" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="15" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="15" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="15" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="15" t="s">
-        <v>76</v>
-      </c>
-    </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="15" t="s">
-        <v>87</v>
+      <c r="A79" s="14" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -5410,8 +5906,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A58"/>
-  <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:A56"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="98.7265625" style="4" customWidth="1"/>
     <col min="2" max="16384" width="8.7265625" style="4"/>
@@ -5419,142 +5915,137 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A7" s="12" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A7" s="13" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A15" s="14" t="s">
-        <v>26</v>
+      <c r="A15" s="13" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A29" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="26" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="27" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A33" s="18" t="s">
         <v>342</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" s="19" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="19" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A33" s="4" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A37" s="4" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A39" s="20" t="s">
         <v>404</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A39" s="21" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A46" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A47" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A48" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A49" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A50" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A51" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A56" s="26" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A58" s="4" t="s">
-        <v>519</v>
+      <c r="A56" s="25" t="s">
+        <v>517</v>
       </c>
     </row>
   </sheetData>
@@ -5568,76 +6059,136 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD312072-87FE-40B5-A445-1591614412BD}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="23.5" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="159.81640625" style="33" customWidth="1"/>
+    <col min="2" max="2" width="76.81640625" style="33" customWidth="1"/>
+    <col min="3" max="16384" width="9.1796875" style="33"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="33" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="37" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="37" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="38" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="38" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="39" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="39" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="33" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="33" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="33" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="33" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>530</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="33" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="33" t="s">
+        <v>508</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="36" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="36" t="s">
+        <v>527</v>
+      </c>
+      <c r="B13" s="36" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="33" t="s">
+        <v>553</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>554</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82BFCEE3-ED03-49F6-AF6F-9D257DBB8787}">
+  <dimension ref="A3:E5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="123.36328125" customWidth="1"/>
+    <col min="1" max="1" width="30.54296875" customWidth="1"/>
+    <col min="2" max="2" width="46.54296875" customWidth="1"/>
+    <col min="3" max="3" width="0.453125" customWidth="1"/>
+    <col min="4" max="4" width="0.54296875" customWidth="1"/>
+    <col min="5" max="5" width="58.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>357</v>
-      </c>
-      <c r="B10" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>509</v>
-      </c>
-      <c r="B12" t="s">
-        <v>511</v>
+        <v>533</v>
+      </c>
+      <c r="B5" t="s">
+        <v>534</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>535</v>
       </c>
     </row>
   </sheetData>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AA4E09-78CA-463F-A578-BBD650440095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE5824F-C49C-43CD-A8AA-54289F633277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Stack" sheetId="1" r:id="rId1"/>
@@ -35,8 +35,57 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="H612" authorId="0" shapeId="0" xr:uid="{2906E36E-FDA9-47D0-BFBB-7EA647B55CDA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Need to check where it will fit
+{
+  "Version": "2012-10-17",
+  "Statement": [
+    {
+      "Effect": "Allow",
+      "Action": "ec2:StopInstances",
+      "Resource": "*",
+      "Condition": {
+        "StringEquals": {
+          "aws:ResourceTag/Environment": "Development"
+        }
+      }
+    }
+  ]
+}</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="635">
   <si>
     <t>NextJS</t>
   </si>
@@ -1959,9 +2008,6 @@
     <t>Same Region Replication</t>
   </si>
   <si>
-    <t>YAV3160637</t>
-  </si>
-  <si>
     <t>ATHENA</t>
   </si>
   <si>
@@ -2019,12 +2065,238 @@
   <si>
     <t>difference route 53 and aws cloudFront</t>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=gbQGMEBCZ3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Blury vision</t>
+  </si>
+  <si>
+    <t>HP OmniBook 7 Laptop 16-ayOxxx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS CloudFront  </t>
+  </si>
+  <si>
+    <t>Is Content Delivery Network</t>
+  </si>
+  <si>
+    <t>AWS CloudFormation</t>
+  </si>
+  <si>
+    <t>is Creating and managing AWS resources ( Create an entire VPC, ECS cluster, and RDS database using a template )</t>
+  </si>
+  <si>
+    <t>unpredictable</t>
+  </si>
+  <si>
+    <t>steep sudden spikes</t>
+  </si>
+  <si>
+    <t>Apache Cassandra</t>
+  </si>
+  <si>
+    <t>open-source NoSQL distributed database</t>
+  </si>
+  <si>
+    <t>Dynamo db</t>
+  </si>
+  <si>
+    <t>aws nosql database</t>
+  </si>
+  <si>
+    <t>Amazon Neptune</t>
+  </si>
+  <si>
+    <t>Graph database</t>
+  </si>
+  <si>
+    <t>Document DB</t>
+  </si>
+  <si>
+    <t>No sql database</t>
+  </si>
+  <si>
+    <t>Document DB (mongo DB)</t>
+  </si>
+  <si>
+    <t>DynamoDB</t>
+  </si>
+  <si>
+    <t>AWS RedShift</t>
+  </si>
+  <si>
+    <t>Its based on PostgreSQL , and it  a OLAp. It is analtic and dataware house</t>
+  </si>
+  <si>
+    <t>AWS QuickSight or Tableau</t>
+  </si>
+  <si>
+    <t>EMR - Elastic Map Reducer</t>
+  </si>
+  <si>
+    <t>Analyses big data  EMR Comes with Apache sparck , Hbase, Presto, Flink</t>
+  </si>
+  <si>
+    <t>BI Tool to create interactive dash boards</t>
+  </si>
+  <si>
+    <t>Glue</t>
+  </si>
+  <si>
+    <t>Is a Manaaged Extract, transform, and load ETL Service.</t>
+  </si>
+  <si>
+    <t>flink apachr</t>
+  </si>
+  <si>
+    <t>real time data processing ;mApache Flink is an open-source distributed data processing framework designed primarily for real-time stream processing, though it also supports batch processing. It enables processing of unbounded (streaming) and bounded (batch) datasets with high throughput and low latency</t>
+  </si>
+  <si>
+    <t>Provides governce , complience and audit for ur AWS Account</t>
+  </si>
+  <si>
+    <t>https://024052294111-iep5wnwx.us-east-1.console.aws.amazon.com/billing/home?region=ap-south-1#/account/customer-verification</t>
+  </si>
+  <si>
+    <t>YAV3160637    Voter Id Reference</t>
+  </si>
+  <si>
+    <t>SCPs do not grant permissions. They define the maximum permissions that member accounts in an AWS Organization can use.</t>
+  </si>
+  <si>
+    <r>
+      <t>IAM policies grant permissions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to users, groups, and roles within an AWS account.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Therefore, an AWS request succeeds </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>only if the IAM policy allows it and no applicable SCP blocks it</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Resource-Based Policies</t>
+  </si>
+  <si>
+    <t>AWS IAM Roles  (Identity-Based Policy)</t>
+  </si>
+  <si>
+    <t>Resource = An object created inside that product.       EC2 Instance (i-1234567890abcdef0) → Resource               S3 Bucket, Object</t>
+  </si>
+  <si>
+    <t>Rule</t>
+  </si>
+  <si>
+    <t>IAM Permisssion</t>
+  </si>
+  <si>
+    <t>IAM Role</t>
+  </si>
+  <si>
+    <t>IAM User</t>
+  </si>
+  <si>
+    <t>User Request │ ▼ IAM Policy │ ▼ Account SCP │ ▼ OU SCP │ ▼ Root SCP │ ▼ AWS Service</t>
+  </si>
+  <si>
+    <r>
+      <t>Service</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = The AWS product.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                                               Amazon EC2 → Service                                                              Amazon S3</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> • Identity-based Policies</t>
+  </si>
+  <si>
+    <t>• Resource-based Policies</t>
+  </si>
+  <si>
+    <t>• Session Policies</t>
+  </si>
+  <si>
+    <t>• Permissions Boundaries</t>
+  </si>
+  <si>
+    <t>• SCPs (AWS Organizations)</t>
+  </si>
+  <si>
+    <t>• RCPs (if applicable)</t>
+  </si>
+  <si>
+    <t>An SCP cannot grant permissions, It only limits what IAM policies can grant.</t>
+  </si>
+  <si>
+    <t>ui Policy Number  0718032826p103254361   0718032826P103254361</t>
+  </si>
+  <si>
+    <t>AWS Organizations Tag Policies</t>
+  </si>
+  <si>
+    <t>Parameter Policies   SSM  - is only for advanced parameters</t>
+  </si>
+  <si>
+    <t>VPN Gateway</t>
+  </si>
+  <si>
+    <t>NAT Gateway</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2147,8 +2419,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2233,6 +2526,36 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2247,7 +2570,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2317,6 +2640,26 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2629,10 +2972,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="91.81640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="123.6328125" style="1" customWidth="1"/>
     <col min="2" max="2" width="90.7265625" style="1" customWidth="1"/>
     <col min="3" max="16384" width="8.7265625" style="1"/>
   </cols>
@@ -2853,7 +3196,35 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
-        <v>567</v>
+        <v>610</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" s="1" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91" s="1" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92" s="1" t="s">
+        <v>630</v>
       </c>
     </row>
   </sheetData>
@@ -2868,13 +3239,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD904FA-0FAD-46CD-8773-AE594AFC6DAB}">
-  <dimension ref="B10:G593"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD904FA-0FAD-46CD-8773-AE594AFC6DAB}">
+  <dimension ref="B10:H652"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="8.7265625" customWidth="1"/>
-    <col min="6" max="6" width="130.1796875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="32.54296875" customWidth="1"/>
+    <col min="6" max="6" width="162.81640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="58.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="10" spans="6:6" ht="409.5" x14ac:dyDescent="0.55000000000000004">
@@ -5414,7 +5785,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="515" spans="6:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="515" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F515" s="22" t="s">
         <v>499</v>
       </c>
@@ -5438,7 +5809,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="519" spans="6:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="519" spans="6:7" ht="29" x14ac:dyDescent="0.35">
       <c r="F519" s="23" t="s">
         <v>505</v>
       </c>
@@ -5608,60 +5979,289 @@
     </row>
     <row r="570" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F570" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="G570" t="s">
         <v>568</v>
-      </c>
-      <c r="G570" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="574" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F574" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="575" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F575" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="581" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F581" s="40" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="582" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F582" s="40" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="583" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F583" s="40" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="584" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F584" s="40" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="585" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F585" s="40" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="589" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F589" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="590" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F590" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="593" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F593" s="2" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="593" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F593" s="2" t="s">
-        <v>579</v>
+    <row r="596" spans="6:7" s="44" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F596" s="43" t="s">
+        <v>582</v>
+      </c>
+      <c r="G596" s="44" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="597" spans="6:7" s="42" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="F597" s="41" t="s">
+        <v>584</v>
+      </c>
+      <c r="G597" s="42" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="600" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F600" t="s">
+        <v>588</v>
+      </c>
+      <c r="G600" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="601" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F601" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G601" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="602" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F602" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="G602" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="603" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F603" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="G603" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="604" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F604" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="G604" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="605" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F605" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="G605" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="606" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F606" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="G606" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="607" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F607" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="G607" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="608" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F608" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="G608" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="609" spans="6:8" x14ac:dyDescent="0.35">
+      <c r="F609" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="G609" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="611" spans="6:8" x14ac:dyDescent="0.35">
+      <c r="F611" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G611" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="612" spans="6:8" x14ac:dyDescent="0.35">
+      <c r="H612" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="616" spans="6:8" ht="21" x14ac:dyDescent="0.5">
+      <c r="F616" s="45" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="617" spans="6:8" ht="21" x14ac:dyDescent="0.5">
+      <c r="F617" s="46" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="618" spans="6:8" ht="21" x14ac:dyDescent="0.5">
+      <c r="F618" s="46" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="619" spans="6:8" ht="21" x14ac:dyDescent="0.5">
+      <c r="F619" s="46" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="624" spans="6:8" x14ac:dyDescent="0.35">
+      <c r="F624" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="625" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F625" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="626" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F626" s="2" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="628" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F628" s="47" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="629" spans="6:6" ht="42" x14ac:dyDescent="0.5">
+      <c r="F629" s="48" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="631" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F631" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="634" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F634" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="635" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F635" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="636" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F636" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="637" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F637" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="640" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F640" s="49" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="641" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F641" s="49" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="642" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F642" s="49" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="643" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F643" s="50" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="644" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F644" s="50" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="645" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F645" s="50" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="649" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F649" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="650" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F650" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="651" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F651" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="652" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F652" s="2" t="s">
+        <v>634</v>
       </c>
     </row>
   </sheetData>
@@ -5669,6 +6269,7 @@
     <hyperlink ref="F291" r:id="rId1" xr:uid="{5B4939E1-0F97-4A79-B4A5-1D09873EBA1F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -6059,7 +6660,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD312072-87FE-40B5-A445-1591614412BD}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="23.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="159.81640625" style="33" customWidth="1"/>
@@ -6153,6 +6754,16 @@
       </c>
       <c r="B14" s="33" t="s">
         <v>554</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>587</v>
       </c>
     </row>
   </sheetData>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE5824F-C49C-43CD-A8AA-54289F633277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B373254-FFBB-4232-A24A-1B00FEFAF001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2760" windowWidth="28785" windowHeight="12825" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Stack" sheetId="1" r:id="rId1"/>
@@ -80,12 +80,118 @@
         </r>
       </text>
     </comment>
+    <comment ref="F651" authorId="0" shapeId="0" xr:uid="{58882077-26BC-43F0-914E-01F9877CB536}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+IGW</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F653" authorId="0" shapeId="0" xr:uid="{CB4594E8-88F5-4954-8748-DF82948354B8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+NATGW</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F659" authorId="0" shapeId="0" xr:uid="{8E4A042E-B3F7-497C-A745-BC9E3059EEC6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+You must update the Route Tables</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F664" authorId="0" shapeId="0" xr:uid="{2AF2031F-1762-4C77-8A56-B6D73C610C3A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+| AWS Accelerator                   | Purpose                                                        | Typical Use Case                                  |
+| --------------------------------- | -------------------------------------------------------------- | ------------------------------------------------- |
+| Amazon S3 Transfer Acceleration   | Speeds up uploads/downloads to S3 using AWS edge locations     | Large file transfers from global users            |
+| AWS Global Accelerator            | Improves performance and availability for TCP/UDP applications | Global web applications, APIs, gaming             |
+| Amazon CloudFront                 | Caches and delivers content from edge locations                | Websites, videos, APIs, static assets             |
+| Amazon DynamoDB Accelerator (DAX) | In-memory cache for DynamoDB                                   | Microsecond read latency for read-heavy workloads |
+| Amazon ElastiCache                | In-memory caching using Redis or Memcached                     | Accelerating database and application performance |
+| AWS DataSync                      | Accelerates online data migration between on-premises and AWS  | Large-scale data migration                        |
+| AWS Snowball Edge                 | Physical appliance for transferring large datasets             | PB-scale offline data transfer                    |
+| AWS Direct Connect                | Dedicated private network connection to AWS                    | Low-latency, high-bandwidth connectivity          |
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="645">
   <si>
     <t>NextJS</t>
   </si>
@@ -2277,9 +2383,6 @@
     <t>An SCP cannot grant permissions, It only limits what IAM policies can grant.</t>
   </si>
   <si>
-    <t>ui Policy Number  0718032826p103254361   0718032826P103254361</t>
-  </si>
-  <si>
     <t>AWS Organizations Tag Policies</t>
   </si>
   <si>
@@ -2290,6 +2393,39 @@
   </si>
   <si>
     <t>NAT Gateway</t>
+  </si>
+  <si>
+    <t>Transfer acceleration</t>
+  </si>
+  <si>
+    <t>Global Accelerator</t>
+  </si>
+  <si>
+    <t>United Insurance Policy Number  0718032826P103254361</t>
+  </si>
+  <si>
+    <t>S3 Transfer Acceleration</t>
+  </si>
+  <si>
+    <t>DAX Amazon DyamoDB Accelerator DAX</t>
+  </si>
+  <si>
+    <t>VPW Virtual Private Gateway.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CGW Customer Gateway </t>
+  </si>
+  <si>
+    <t>Transit Gateway (TGW)</t>
+  </si>
+  <si>
+    <t>AWS Storage Gateway</t>
+  </si>
+  <si>
+    <t>DirectConnect gateway</t>
+  </si>
+  <si>
+    <t>Egress only Internet Gateway</t>
   </si>
 </sst>
 </file>
@@ -2973,89 +3109,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D92"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="123.6328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="90.7265625" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="123.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="90.7109375" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>12</v>
       </c>
@@ -3063,8 +3199,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>13</v>
       </c>
@@ -3072,7 +3208,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>15</v>
       </c>
@@ -3080,98 +3216,98 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10"/>
     </row>
-    <row r="29" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="58" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="24" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A65" s="25" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="70" spans="1:2" s="28" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="28" t="s">
         <v>522</v>
       </c>
@@ -3179,27 +3315,27 @@
         <v>523</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="20" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>579</v>
       </c>
@@ -3207,24 +3343,24 @@
         <v>580</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A91" s="1" t="s">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="20" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
     </row>
   </sheetData>
@@ -3232,431 +3368,432 @@
     <hyperlink ref="A25" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="A44" r:id="rId2" display="https://www.flipkart.com/accutrust-smart-visual-ear-wax-cleaner-5mp-hd-camera-wifi-connectivity-electric/p/itm0315faef11f13?pid=EECHGXCWFRH6XZHA&amp;lid=LSTEECHGXCWFRH6XZHAISPLFA&amp;marketplace=FLIPKART&amp;cmpid=content_electric-ear-cleaner_8965229628_gmc&amp;affExtParam1=YT3-z2rvmWPrOgxlKmfc_aEoLuOMgI-j9wjho2LRdfrZUYxb7nMHeUixAxq1wdbLmpADGix8YWLsz2ErZwLHghUe8bs&amp;affid=ytflipkart" xr:uid="{43FE7E05-99E0-44FD-92C6-50DC9E76E9D2}"/>
     <hyperlink ref="A77" r:id="rId3" xr:uid="{848F9BED-8591-4632-A158-BADB42AFF627}"/>
+    <hyperlink ref="A91" r:id="rId4" location="/account/customer-verification" xr:uid="{8ABF94D8-AF01-4018-862E-FF9302717FBE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD904FA-0FAD-46CD-8773-AE594AFC6DAB}">
-  <dimension ref="B10:H652"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B10:H667"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="8.7265625" customWidth="1"/>
-    <col min="6" max="6" width="162.81640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="58.7265625" customWidth="1"/>
+    <col min="1" max="2" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="162.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="58.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="10" spans="6:6" ht="409.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="6:6" ht="409.5" x14ac:dyDescent="0.35">
       <c r="F10" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="32" spans="6:6" ht="21" x14ac:dyDescent="0.35">
       <c r="F32" s="15" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="33" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="33" spans="6:6" ht="21" x14ac:dyDescent="0.35">
       <c r="F33" s="15" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="34" spans="6:6" ht="21" x14ac:dyDescent="0.35">
       <c r="F34" s="15" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="35" spans="6:6" ht="21" x14ac:dyDescent="0.35">
       <c r="F35" s="15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="36" spans="6:6" ht="21" x14ac:dyDescent="0.35">
       <c r="F36" s="15" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="37" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="37" spans="6:6" ht="21" x14ac:dyDescent="0.35">
       <c r="F37" s="15" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="38" spans="6:6" ht="21" x14ac:dyDescent="0.35">
       <c r="F38" s="15" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="39" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="39" spans="6:6" ht="21" x14ac:dyDescent="0.35">
       <c r="F39" s="15"/>
     </row>
-    <row r="40" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="40" spans="6:6" ht="21" x14ac:dyDescent="0.35">
       <c r="F40" s="15"/>
     </row>
-    <row r="41" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="41" spans="6:6" ht="21" x14ac:dyDescent="0.35">
       <c r="F41" s="15" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="42" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="42" spans="6:6" ht="21" x14ac:dyDescent="0.35">
       <c r="F42" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="43" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="43" spans="6:6" ht="21" x14ac:dyDescent="0.35">
       <c r="F43" s="15" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="44" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="44" spans="6:6" ht="21" x14ac:dyDescent="0.35">
       <c r="F44" s="15" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="45" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="45" spans="6:6" ht="21" x14ac:dyDescent="0.35">
       <c r="F45" s="15" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="46" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="46" spans="6:6" ht="21" x14ac:dyDescent="0.35">
       <c r="F46" s="15" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="47" spans="6:6" ht="21" x14ac:dyDescent="0.35">
       <c r="F47" s="15" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="48" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="48" spans="6:6" ht="21" x14ac:dyDescent="0.35">
       <c r="F48" s="15" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="49" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="49" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E49" s="15"/>
       <c r="F49" s="15" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="50" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E50" s="15"/>
       <c r="F50" s="15" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="51" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="51" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E51" s="15"/>
       <c r="F51" s="15" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="52" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="52" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E52" s="15"/>
       <c r="F52" s="15" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="53" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E53" s="15"/>
       <c r="F53" s="15" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="54" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="54" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E54" s="15"/>
       <c r="F54" s="15" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="55" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="55" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E55" s="15"/>
       <c r="F55" s="15" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="56" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="56" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E56" s="15"/>
       <c r="F56" s="15" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="57" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="57" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E57" s="15"/>
       <c r="F57" s="15" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="58" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="58" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E58" s="15"/>
       <c r="F58" s="15" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="59" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="59" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E59" s="15"/>
       <c r="F59" s="15" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="60" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="60" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E60" s="15"/>
       <c r="F60" s="15" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="61" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="61" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E61" s="15"/>
       <c r="F61" s="15"/>
     </row>
-    <row r="62" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="62" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E62" s="15"/>
       <c r="F62" s="15"/>
     </row>
-    <row r="63" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="63" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E63" s="15"/>
       <c r="F63" s="15"/>
     </row>
-    <row r="64" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="64" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E64" s="15"/>
       <c r="F64" s="15" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="65" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="65" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E65" s="15"/>
       <c r="F65" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="66" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="66" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E66" s="15"/>
       <c r="F66" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="67" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="67" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E67" s="15"/>
       <c r="F67" s="15" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="68" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="68" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E68" s="15"/>
       <c r="F68" s="15" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="69" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="69" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E69" s="15"/>
       <c r="F69" s="15" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="70" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="70" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E70" s="15"/>
       <c r="F70" s="15" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="71" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="71" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E71" s="15"/>
       <c r="F71" s="15" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="72" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="72" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E72" s="15"/>
       <c r="F72" s="15" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="73" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="73" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E73" s="15"/>
       <c r="F73" s="15" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="74" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="74" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E74" s="15"/>
       <c r="F74" s="15" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="75" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="75" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E75" s="15"/>
       <c r="F75" s="15" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="76" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="76" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E76" s="15"/>
       <c r="F76" s="15" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="77" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="77" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E77" s="15"/>
       <c r="F77" s="15" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="78" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="78" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E78" s="15"/>
       <c r="F78" s="15" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="79" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="79" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E79" s="15"/>
       <c r="F79" s="15" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="80" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="80" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E80" s="15"/>
       <c r="F80" s="15" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="81" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="81" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E81" s="15"/>
       <c r="F81" s="15" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="82" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="82" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E82" s="15"/>
       <c r="F82" s="15" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="83" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="83" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E83" s="15"/>
       <c r="F83" s="15" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="84" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="84" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E84" s="15"/>
       <c r="F84" s="15"/>
     </row>
-    <row r="85" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="85" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E85" s="15"/>
       <c r="F85" s="15"/>
     </row>
-    <row r="86" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="86" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E86" s="15"/>
       <c r="F86" s="15" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="87" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="87" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E87" s="15"/>
       <c r="F87" s="15" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="88" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="88" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E88" s="15"/>
       <c r="F88" s="15" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="89" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="89" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E89" s="15"/>
       <c r="F89" s="15"/>
     </row>
-    <row r="90" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="90" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E90" s="15"/>
       <c r="F90" s="15"/>
     </row>
-    <row r="91" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="91" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E91" s="15"/>
       <c r="F91" s="15" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="92" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="92" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E92" s="15"/>
       <c r="F92" s="15" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="93" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="93" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E93" s="15"/>
       <c r="F93" s="15" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="94" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E94" s="15"/>
       <c r="F94" s="15" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="95" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="95" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E95" s="15"/>
       <c r="F95" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="96" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="96" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E96" s="15"/>
       <c r="F96" s="15" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="97" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="97" spans="5:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E97" s="15"/>
       <c r="F97" s="15" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="98" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="98" spans="5:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E98" s="15"/>
       <c r="F98" s="15" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="99" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="99" spans="5:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E99" s="15"/>
       <c r="F99" s="15" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="100" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="100" spans="5:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E100" s="15"/>
       <c r="F100" s="15" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="101" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="101" spans="5:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E101" s="15"/>
       <c r="F101" s="15" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="102" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="102" spans="5:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E102" s="15"/>
       <c r="F102" s="15" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="103" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="103" spans="5:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E103" s="15"/>
       <c r="F103" s="15" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="104" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="104" spans="5:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E104" s="15"/>
       <c r="F104" s="15" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="105" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="105" spans="5:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E105" s="15"/>
       <c r="F105" s="15" t="s">
         <v>155</v>
@@ -3665,571 +3802,571 @@
         <v>37</v>
       </c>
     </row>
-    <row r="106" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="106" spans="5:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E106" s="15"/>
       <c r="F106" s="15" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="107" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="107" spans="5:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E107" s="15"/>
       <c r="F107" s="15"/>
     </row>
-    <row r="108" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="108" spans="5:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E108" s="15"/>
       <c r="F108" s="15"/>
     </row>
-    <row r="109" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="109" spans="5:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E109" s="15"/>
       <c r="F109" s="15" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="110" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="110" spans="5:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E110" s="15"/>
       <c r="F110" s="15" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="111" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="111" spans="5:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E111" s="15"/>
       <c r="F111" s="15" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="112" spans="5:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="112" spans="5:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E112" s="15"/>
       <c r="F112" s="15" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="113" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="113" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E113" s="15"/>
       <c r="F113" s="15" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="114" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="114" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E114" s="15"/>
       <c r="F114" s="15" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="115" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="115" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E115" s="15"/>
       <c r="F115" s="15" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="116" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="116" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E116" s="15"/>
       <c r="F116" s="15" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="117" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="117" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E117" s="15"/>
       <c r="F117" s="15" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="118" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="118" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E118" s="15"/>
       <c r="F118" s="15" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="119" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="119" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E119" s="15"/>
       <c r="F119" s="15" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="120" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="120" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E120" s="15"/>
       <c r="F120" s="15" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="121" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="121" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E121" s="15"/>
       <c r="F121" s="15"/>
     </row>
-    <row r="122" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="122" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E122" s="15"/>
       <c r="F122" s="15"/>
     </row>
-    <row r="123" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="123" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E123" s="15"/>
       <c r="F123" s="15"/>
     </row>
-    <row r="124" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="124" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E124" s="15"/>
       <c r="F124" s="15" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="125" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="125" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E125" s="15"/>
       <c r="F125" s="15" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="126" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="126" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E126" s="15"/>
       <c r="F126" s="15" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="127" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="127" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E127" s="15"/>
       <c r="F127" s="15" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="128" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="128" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E128" s="15"/>
       <c r="F128" s="15" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="129" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="129" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E129" s="15"/>
       <c r="F129" s="15" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="130" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="130" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E130" s="15"/>
       <c r="F130" s="15" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="131" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="131" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E131" s="15"/>
       <c r="F131" s="15" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="132" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="132" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E132" s="15"/>
       <c r="F132" s="15" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="133" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="133" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E133" s="15"/>
       <c r="F133" s="15" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="134" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="134" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E134" s="15"/>
       <c r="F134" s="15" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="135" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="135" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E135" s="15"/>
       <c r="F135" s="15" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="136" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="136" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E136" s="15"/>
       <c r="F136" s="15" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="137" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="137" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E137" s="15"/>
       <c r="F137" s="15" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="138" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="138" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E138" s="15"/>
       <c r="F138" s="15" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="139" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="139" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E139" s="15"/>
       <c r="F139" s="15" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="140" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="140" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E140" s="15"/>
       <c r="F140" s="15" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="141" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="141" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E141" s="15"/>
       <c r="F141" s="15" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="142" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="142" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E142" s="15"/>
       <c r="F142" s="15" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="143" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="143" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E143" s="15"/>
       <c r="F143" s="15" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="144" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="144" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E144" s="15"/>
       <c r="F144" s="15" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="145" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="145" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E145" s="15"/>
       <c r="F145" s="15" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="146" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="146" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E146" s="15"/>
       <c r="F146" s="15" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="147" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="147" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E147" s="15"/>
       <c r="F147" s="15" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="148" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="148" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E148" s="15"/>
       <c r="F148" s="15" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="149" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="149" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E149" s="15"/>
       <c r="F149" s="15" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="150" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="150" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E150" s="15"/>
       <c r="F150" s="15" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="151" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="151" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E151" s="15"/>
       <c r="F151" s="15"/>
     </row>
-    <row r="152" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="152" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E152" s="15"/>
       <c r="F152" s="15"/>
     </row>
-    <row r="153" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="153" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E153" s="15"/>
       <c r="F153" s="15" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="154" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="154" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E154" s="15"/>
       <c r="F154" s="15" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="155" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="155" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E155" s="15"/>
       <c r="F155" s="15" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="156" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="156" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E156" s="15"/>
       <c r="F156" s="15" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="157" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="157" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E157" s="15"/>
       <c r="F157" s="15" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="158" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="158" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E158" s="15"/>
       <c r="F158" s="15" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="159" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="159" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E159" s="15"/>
       <c r="F159" s="15" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="160" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="160" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E160" s="15"/>
       <c r="F160" s="15" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="161" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="161" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E161" s="15"/>
       <c r="F161" s="15" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="162" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="162" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E162" s="15"/>
       <c r="F162" s="15" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="163" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="163" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E163" s="15"/>
       <c r="F163" s="15" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="164" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="164" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E164" s="15"/>
       <c r="F164" s="15" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="165" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="165" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E165" s="15"/>
       <c r="F165" s="15" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="166" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="166" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E166" s="15"/>
       <c r="F166" s="15" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="167" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="167" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E167" s="15"/>
       <c r="F167" s="15" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="168" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="168" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E168" s="15"/>
       <c r="F168" s="15" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="169" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="169" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E169" s="15"/>
       <c r="F169" s="15" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="170" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="170" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E170" s="15"/>
       <c r="F170" s="15" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="171" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="171" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E171" s="15"/>
       <c r="F171" s="15" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="172" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="172" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E172" s="15"/>
       <c r="F172" s="15" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="173" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="173" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E173" s="15"/>
       <c r="F173" s="15" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="174" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="174" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E174" s="15"/>
       <c r="F174" s="15" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="175" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="175" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E175" s="15"/>
       <c r="F175" s="15" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="176" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="176" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E176" s="15"/>
       <c r="F176" s="15" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="177" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="177" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E177" s="15"/>
       <c r="F177" s="15" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="178" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="178" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E178" s="15"/>
       <c r="F178" s="15" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="179" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="179" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E179" s="15"/>
       <c r="F179" s="15" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="180" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="180" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E180" s="15"/>
       <c r="F180" s="15" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="181" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="181" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E181" s="15"/>
       <c r="F181" s="15" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="182" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="182" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E182" s="15"/>
       <c r="F182" s="15" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="183" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="183" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E183" s="15"/>
       <c r="F183" s="15" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="184" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="184" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E184" s="15"/>
       <c r="F184" s="15" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="185" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="185" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E185" s="15"/>
       <c r="F185" s="15" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="186" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="186" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E186" s="15"/>
       <c r="F186" s="15" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="187" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="187" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E187" s="15"/>
       <c r="F187" s="15" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="188" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="188" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E188" s="15"/>
       <c r="F188" s="15"/>
     </row>
-    <row r="189" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="189" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E189" s="15"/>
       <c r="F189" s="15"/>
     </row>
-    <row r="190" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="190" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E190" s="15"/>
       <c r="F190" s="15"/>
     </row>
-    <row r="191" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="191" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E191" s="15"/>
       <c r="F191" s="15" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="192" spans="5:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="192" spans="5:6" ht="21" x14ac:dyDescent="0.35">
       <c r="E192" s="15"/>
       <c r="F192" s="15" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="193" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="193" spans="2:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E193" s="15"/>
       <c r="F193" s="15" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="194" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="194" spans="2:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E194" s="15"/>
       <c r="F194" s="15" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="195" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="195" spans="2:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E195" s="15"/>
       <c r="F195" s="15" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="196" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="196" spans="2:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E196" s="15"/>
       <c r="F196" s="15" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="197" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="197" spans="2:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E197" s="15"/>
       <c r="F197" s="15" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="198" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="198" spans="2:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E198" s="15"/>
       <c r="F198" s="15" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="199" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="199" spans="2:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E199" s="15"/>
       <c r="F199" s="15" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="200" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="200" spans="2:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E200" s="15"/>
       <c r="F200" s="15" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="201" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="201" spans="2:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E201" s="15"/>
       <c r="F201" s="15"/>
     </row>
-    <row r="202" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="202" spans="2:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E202" s="15"/>
       <c r="F202" s="15"/>
     </row>
-    <row r="203" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="203" spans="2:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E203" s="15"/>
       <c r="F203" s="15" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="204" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="204" spans="2:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E204" s="15"/>
       <c r="F204" s="15" t="s">
         <v>246</v>
@@ -4238,24 +4375,24 @@
         <v>37</v>
       </c>
     </row>
-    <row r="205" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="205" spans="2:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E205" s="15"/>
       <c r="F205" s="15" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="206" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="206" spans="2:7" ht="21" x14ac:dyDescent="0.35">
       <c r="E206" s="15"/>
       <c r="F206" s="15" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="207" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="207" spans="2:7" ht="21" x14ac:dyDescent="0.35">
       <c r="F207" s="15" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="208" spans="2:7" ht="21" x14ac:dyDescent="0.5">
+    <row r="208" spans="2:7" ht="21" x14ac:dyDescent="0.35">
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
       <c r="D208" s="4"/>
@@ -4264,7 +4401,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="209" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="209" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
       <c r="D209" s="4"/>
@@ -4273,7 +4410,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="210" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="210" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
       <c r="D210" s="4"/>
@@ -4282,7 +4419,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="211" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="211" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
       <c r="D211" s="4"/>
@@ -4291,7 +4428,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="212" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="212" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
       <c r="D212" s="4"/>
@@ -4300,7 +4437,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="213" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="213" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
       <c r="D213" s="4"/>
@@ -4309,7 +4446,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="214" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="214" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
       <c r="D214" s="4"/>
@@ -4318,7 +4455,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="215" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="215" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
       <c r="D215" s="4"/>
@@ -4327,7 +4464,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="216" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="216" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
       <c r="D216" s="4"/>
@@ -4336,7 +4473,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="217" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="217" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
       <c r="D217" s="4"/>
@@ -4345,28 +4482,28 @@
         <v>262</v>
       </c>
     </row>
-    <row r="218" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="218" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
       <c r="D218" s="4"/>
       <c r="E218" s="4"/>
       <c r="F218" s="16"/>
     </row>
-    <row r="219" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="219" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
       <c r="F219" s="16"/>
     </row>
-    <row r="220" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="220" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
       <c r="D220" s="4"/>
       <c r="E220" s="4"/>
       <c r="F220" s="16"/>
     </row>
-    <row r="221" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="221" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
       <c r="D221" s="4"/>
@@ -4375,7 +4512,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="222" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="222" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
       <c r="D222" s="4"/>
@@ -4384,7 +4521,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="223" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="223" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
       <c r="D223" s="4"/>
@@ -4393,7 +4530,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="224" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="224" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
       <c r="D224" s="4"/>
@@ -4402,7 +4539,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="225" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="225" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
       <c r="D225" s="4"/>
@@ -4411,7 +4548,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="226" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="226" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
       <c r="D226" s="4"/>
@@ -4420,7 +4557,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="227" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="227" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
       <c r="D227" s="4"/>
@@ -4429,7 +4566,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="228" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="228" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
       <c r="D228" s="4"/>
@@ -4438,7 +4575,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="229" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="229" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
       <c r="D229" s="4"/>
@@ -4447,35 +4584,35 @@
         <v>271</v>
       </c>
     </row>
-    <row r="230" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="230" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
       <c r="F230" s="16"/>
     </row>
-    <row r="231" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="231" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
       <c r="F231" s="16"/>
     </row>
-    <row r="232" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="232" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
       <c r="F232" s="16"/>
     </row>
-    <row r="233" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="233" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
       <c r="F233" s="16"/>
     </row>
-    <row r="234" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="234" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
       <c r="D234" s="4"/>
@@ -4484,7 +4621,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="235" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="235" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
       <c r="D235" s="4"/>
@@ -4493,7 +4630,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="236" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="236" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
       <c r="D236" s="4"/>
@@ -4502,7 +4639,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="237" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="237" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
       <c r="D237" s="4"/>
@@ -4511,7 +4648,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="238" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="238" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
       <c r="D238" s="4"/>
@@ -4520,7 +4657,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="239" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="239" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
       <c r="D239" s="4"/>
@@ -4529,7 +4666,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="240" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="240" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
       <c r="D240" s="4"/>
@@ -4538,7 +4675,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="241" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="241" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
       <c r="D241" s="4"/>
@@ -4547,7 +4684,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="242" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="242" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
       <c r="D242" s="4"/>
@@ -4556,28 +4693,28 @@
         <v>280</v>
       </c>
     </row>
-    <row r="243" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="243" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
       <c r="F243" s="16"/>
     </row>
-    <row r="244" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="244" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
       <c r="D244" s="4"/>
       <c r="E244" s="4"/>
       <c r="F244" s="16"/>
     </row>
-    <row r="245" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="245" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
       <c r="D245" s="4"/>
       <c r="E245" s="4"/>
       <c r="F245" s="16"/>
     </row>
-    <row r="246" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="246" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
       <c r="D246" s="4"/>
@@ -4586,7 +4723,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="247" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="247" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
       <c r="D247" s="4"/>
@@ -4595,7 +4732,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="248" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="248" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
       <c r="D248" s="4"/>
@@ -4604,7 +4741,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="249" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="249" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
       <c r="D249" s="4"/>
@@ -4613,7 +4750,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="250" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="250" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
       <c r="D250" s="4"/>
@@ -4622,7 +4759,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="251" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="251" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
       <c r="D251" s="4"/>
@@ -4631,7 +4768,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="252" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="252" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
       <c r="D252" s="4"/>
@@ -4640,7 +4777,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="253" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="253" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
       <c r="D253" s="4"/>
@@ -4649,7 +4786,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="254" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="254" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
       <c r="D254" s="4"/>
@@ -4658,28 +4795,28 @@
         <v>289</v>
       </c>
     </row>
-    <row r="255" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="255" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
       <c r="D255" s="4"/>
       <c r="E255" s="4"/>
       <c r="F255" s="16"/>
     </row>
-    <row r="256" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="256" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
       <c r="D256" s="4"/>
       <c r="E256" s="4"/>
       <c r="F256" s="16"/>
     </row>
-    <row r="257" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="257" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
       <c r="D257" s="4"/>
       <c r="E257" s="4"/>
       <c r="F257" s="16"/>
     </row>
-    <row r="258" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="258" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
       <c r="D258" s="4"/>
@@ -4688,21 +4825,21 @@
         <v>291</v>
       </c>
     </row>
-    <row r="259" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="259" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B259" s="4"/>
       <c r="C259" s="4"/>
       <c r="D259" s="4"/>
       <c r="E259" s="4"/>
       <c r="F259" s="16"/>
     </row>
-    <row r="260" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="260" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
       <c r="D260" s="4"/>
       <c r="E260" s="4"/>
       <c r="F260" s="16"/>
     </row>
-    <row r="261" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="261" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
       <c r="D261" s="4"/>
@@ -4711,7 +4848,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="262" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="262" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B262" s="4"/>
       <c r="C262" s="4"/>
       <c r="D262" s="4"/>
@@ -4720,7 +4857,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="263" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="263" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B263" s="4"/>
       <c r="C263" s="4"/>
       <c r="D263" s="4"/>
@@ -4729,7 +4866,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="264" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="264" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
       <c r="D264" s="4"/>
@@ -4738,7 +4875,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="265" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="265" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B265" s="4"/>
       <c r="C265" s="4"/>
       <c r="D265" s="4"/>
@@ -4747,21 +4884,21 @@
         <v>295</v>
       </c>
     </row>
-    <row r="266" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="266" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B266" s="4"/>
       <c r="C266" s="4"/>
       <c r="D266" s="4"/>
       <c r="E266" s="4"/>
       <c r="F266" s="16"/>
     </row>
-    <row r="267" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="267" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
       <c r="D267" s="4"/>
       <c r="E267" s="4"/>
       <c r="F267" s="16"/>
     </row>
-    <row r="268" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="268" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
       <c r="D268" s="4"/>
@@ -4770,7 +4907,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="269" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="269" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
       <c r="D269" s="4"/>
@@ -4779,7 +4916,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="270" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="270" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
       <c r="D270" s="4"/>
@@ -4788,28 +4925,28 @@
         <v>298</v>
       </c>
     </row>
-    <row r="271" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="271" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
       <c r="D271" s="4"/>
       <c r="E271" s="4"/>
       <c r="F271" s="16"/>
     </row>
-    <row r="272" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="272" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
       <c r="D272" s="4"/>
       <c r="E272" s="4"/>
       <c r="F272" s="16"/>
     </row>
-    <row r="273" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="273" spans="2:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
       <c r="D273" s="4"/>
       <c r="E273" s="4"/>
       <c r="F273" s="16"/>
     </row>
-    <row r="274" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="274" spans="2:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
       <c r="D274" s="4"/>
@@ -4818,7 +4955,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="275" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="275" spans="2:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
       <c r="D275" s="4"/>
@@ -4827,57 +4964,57 @@
         <v>300</v>
       </c>
     </row>
-    <row r="276" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="276" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F276" s="2" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="277" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="277" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F277" s="2" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="278" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="278" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F278" s="2" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="279" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="279" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F279" s="2" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="280" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="280" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F280" s="2" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="281" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="281" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F281" s="2" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="282" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="282" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F282" s="2" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="283" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="283" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F283" s="2" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="284" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="284" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F284" s="2" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="285" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="285" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F285" s="2" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="286" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="286" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F286" s="2" t="s">
         <v>312</v>
       </c>
@@ -4885,162 +5022,162 @@
         <v>311</v>
       </c>
     </row>
-    <row r="287" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="287" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F287" s="2" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="288" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="288" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F288" s="2" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="289" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="289" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F289" s="2" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="290" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="290" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F290" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="291" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="291" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F291" s="17" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="292" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="292" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F292" s="2" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="293" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="293" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F293" s="2" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="294" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="294" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F294" s="2" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="298" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="298" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F298" s="2" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="299" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="299" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F299" s="2" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="300" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="300" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F300" s="2" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="301" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="301" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F301" s="2" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="302" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="302" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F302" s="2" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="303" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="303" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F303" s="2" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="304" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="304" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F304" s="2" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="305" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="305" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F305" s="2" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="306" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="306" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F306" s="2" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="307" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="307" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F307" s="2" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="308" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="308" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F308" s="2" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="309" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="309" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F309" s="2" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="310" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="310" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F310" s="2" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="315" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="315" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F315" s="2" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="316" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="316" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F316" s="2" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="317" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="317" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F317" s="2" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="318" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="318" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F318" s="19" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="319" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="319" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F319" s="19" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="320" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="320" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F320" s="19" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="321" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="321" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F321" s="19" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="322" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="322" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F322" s="2" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="325" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="325" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F325" s="2" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="326" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="326" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F326" s="2" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="327" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="327" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F327" s="2" t="s">
         <v>346</v>
       </c>
@@ -5048,712 +5185,712 @@
         <v>37</v>
       </c>
     </row>
-    <row r="328" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="328" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F328" s="2" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="329" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="329" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F329" s="2" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="330" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="330" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F330" s="2" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="331" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="331" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F331" s="2" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="332" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="332" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F332" s="2" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="333" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="333" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F333" s="2" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="334" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="334" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F334" s="2" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="335" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="335" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F335" s="2" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="336" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="336" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F336" s="2" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="339" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="339" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F339" s="2" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="342" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="342" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F342" s="2" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="343" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="343" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F343" s="2" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="344" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="344" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F344" s="2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="345" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="345" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F345" s="2" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="346" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="346" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F346" s="2" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="347" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="347" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F347" s="2" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="348" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="348" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F348" s="2" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="349" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="349" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F349" s="2" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="350" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="350" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F350" s="2" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="355" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="355" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F355" s="2" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="356" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="356" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F356" s="2" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="357" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="357" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F357" s="2" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="358" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="358" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F358" s="2" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="359" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="359" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F359" s="2" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="360" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="360" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F360" s="2" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="361" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="361" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F361" s="2" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="362" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="362" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F362" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="363" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="363" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F363" s="2" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="364" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="364" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F364" s="2" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="365" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="365" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F365" s="2" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="366" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="366" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F366" s="2" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="367" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="367" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F367" s="2" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="368" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="368" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F368" s="2" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="371" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="371" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F371" s="2" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="373" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="373" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F373" s="2" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="377" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="377" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F377" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="380" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="380" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F380" s="2" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="382" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="382" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F382" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="383" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="383" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F383" s="2" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="384" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="384" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F384" s="2" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="385" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="385" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F385" s="2" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="386" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="386" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F386" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="387" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="387" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F387" s="2" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="390" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="390" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F390" s="2" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="391" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="391" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F391" s="2" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="392" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="392" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F392" s="2" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="393" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="393" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F393" s="2" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="394" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="394" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F394" s="2" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="395" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="395" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F395" s="2" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="398" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="398" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F398" s="2" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="399" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="399" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F399" s="2" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="400" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="400" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F400" s="2" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="401" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="401" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F401" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="402" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="402" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F402" s="2" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="403" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="403" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F403" s="2" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="408" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="408" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F408" s="2" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="410" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="410" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F410" s="2" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="411" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="411" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F411" s="2" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="412" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="412" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F412" s="2" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="413" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="413" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F413" s="2" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="414" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="414" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F414" s="2" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="415" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="415" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F415" s="2" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="416" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="416" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F416" s="2" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="417" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="417" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F417" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="418" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="418" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F418" s="2" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="419" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="419" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F419" s="2" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="420" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="420" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F420" s="2" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="421" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="421" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F421" s="2" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="422" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="422" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F422" s="2" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="423" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="423" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F423" s="2" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="424" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="424" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F424" s="2" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="427" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="427" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F427" s="2" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="428" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="428" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F428" s="2" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="429" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="429" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F429" s="2" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="430" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="430" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F430" s="2" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="431" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="431" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F431" s="2" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="432" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="432" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F432" s="2" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="433" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="433" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F433" s="2" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="434" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="434" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F434" s="2" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="435" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="435" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F435" s="2" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="436" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="436" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F436" s="2" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="437" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="437" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F437" s="2" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="438" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="438" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F438" s="2" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="439" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="439" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F439" s="2" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="440" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="440" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F440" s="2" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="441" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="441" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F441" s="2" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="442" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="442" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F442" s="2" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="443" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="443" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F443" s="2" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="444" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="444" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F444" s="2" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="445" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="445" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F445" s="2" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="446" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="446" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F446" s="2" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="447" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="447" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F447" s="2" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="448" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="448" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F448" s="2" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="449" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="449" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F449" s="2" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="450" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="450" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F450" s="2" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="453" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="453" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F453" s="2" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="454" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="454" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F454" s="2" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="455" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="455" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F455" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="456" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="456" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F456" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="457" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="457" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F457" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="458" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="458" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F458" s="2" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="459" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="459" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F459" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="460" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="460" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F460" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="461" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="461" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F461" s="2" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="462" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="462" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F462" s="2" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="463" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="463" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F463" s="2" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="464" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="464" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F464" s="2" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="465" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="465" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F465" s="2" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="466" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="466" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F466" s="2" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="467" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="467" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F467" s="2" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="468" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="468" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F468" s="2" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="469" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="469" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F469" s="2" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="470" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="470" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F470" s="2" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="473" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="473" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F473" s="2" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="474" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="474" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F474" s="2" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="475" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="475" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F475" s="2" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="476" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="476" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F476" s="2" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="477" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="477" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F477" s="2" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="478" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="478" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F478" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="479" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="479" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F479" s="2" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="480" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="480" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F480" s="2" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="481" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="481" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F481" s="2" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="482" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="482" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F482" s="2" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="483" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="483" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F483" s="2" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="484" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="484" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F484" s="2" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="485" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="485" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F485" s="2" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="486" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="486" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F486" s="2" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="487" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="487" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F487" s="2" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="488" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="488" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F488" s="2" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="491" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="491" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F491" s="2" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="492" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="492" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F492" s="2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="493" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="493" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F493" s="2" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="494" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="494" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F494" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="495" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="495" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F495" s="2" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="496" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="496" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F496" s="2" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="497" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="497" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F497" s="2" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="498" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="498" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F498" s="2" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="499" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="499" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F499" s="2" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="500" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="500" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F500" s="2" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="501" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="501" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F501" s="2" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="502" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="502" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F502" s="2" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="503" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="503" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F503" s="2" t="s">
         <v>549</v>
       </c>
@@ -5761,7 +5898,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="504" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="504" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F504" s="2" t="s">
         <v>551</v>
       </c>
@@ -5769,7 +5906,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="513" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="513" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F513" s="21" t="s">
         <v>495</v>
       </c>
@@ -5777,7 +5914,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="514" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="514" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F514" s="22" t="s">
         <v>497</v>
       </c>
@@ -5785,7 +5922,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="515" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="515" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F515" s="22" t="s">
         <v>499</v>
       </c>
@@ -5793,7 +5930,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="516" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="516" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F516" s="22" t="s">
         <v>500</v>
       </c>
@@ -5801,7 +5938,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="517" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="517" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F517" s="22" t="s">
         <v>282</v>
       </c>
@@ -5809,7 +5946,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="519" spans="6:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="519" spans="6:7" ht="30" x14ac:dyDescent="0.25">
       <c r="F519" s="23" t="s">
         <v>505</v>
       </c>
@@ -5817,7 +5954,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="522" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="522" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F522" t="s">
         <v>504</v>
       </c>
@@ -5825,17 +5962,17 @@
         <v>507</v>
       </c>
     </row>
-    <row r="524" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="524" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F524" s="2" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="526" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="526" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F526" s="2" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="528" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="528" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F528" s="2" t="s">
         <v>513</v>
       </c>
@@ -5843,12 +5980,12 @@
         <v>514</v>
       </c>
     </row>
-    <row r="531" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="531" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F531" s="2" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="534" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="534" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F534" s="2" t="s">
         <v>518</v>
       </c>
@@ -5856,7 +5993,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="537" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="537" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F537" s="2" t="s">
         <v>525</v>
       </c>
@@ -5864,12 +6001,12 @@
         <v>526</v>
       </c>
     </row>
-    <row r="539" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="539" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F539" s="2" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="541" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="541" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F541" s="2" t="s">
         <v>536</v>
       </c>
@@ -5877,7 +6014,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="544" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="544" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F544" s="31" t="s">
         <v>538</v>
       </c>
@@ -5885,7 +6022,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="545" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="545" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F545" s="31" t="s">
         <v>540</v>
       </c>
@@ -5893,75 +6030,75 @@
         <v>541</v>
       </c>
     </row>
-    <row r="547" spans="6:7" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="6:7" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F547" s="29" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="548" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="548" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F548" s="2" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="549" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="549" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F549" s="2" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="550" spans="6:7" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="6:7" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F550" s="29" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="551" spans="6:7" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="6:7" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F551" s="29" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="552" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="552" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F552" s="2" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="553" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="553" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F553" s="2" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="557" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="557" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F557" s="35" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="558" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="558" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F558" s="35" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="559" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="559" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F559" s="35" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="560" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="560" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F560" s="35" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="561" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="561" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F561" s="35" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="562" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="562" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F562" s="35" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="565" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="565" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F565" s="34"/>
     </row>
-    <row r="567" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="567" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F567" s="2" t="s">
         <v>563</v>
       </c>
@@ -5969,7 +6106,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="568" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="568" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F568" s="2" t="s">
         <v>564</v>
       </c>
@@ -5977,7 +6114,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="570" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="570" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F570" s="2" t="s">
         <v>567</v>
       </c>
@@ -5985,57 +6122,57 @@
         <v>568</v>
       </c>
     </row>
-    <row r="574" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="574" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F574" s="2" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="575" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="575" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F575" s="2" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="581" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="581" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F581" s="40" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="582" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="582" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F582" s="40" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="583" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="583" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F583" s="40" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="584" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="584" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F584" s="40" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="585" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="585" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F585" s="40" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="589" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="589" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F589" s="2" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="590" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="590" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F590" s="2" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="593" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="593" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F593" s="2" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="596" spans="6:7" s="44" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="6:7" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F596" s="43" t="s">
         <v>582</v>
       </c>
@@ -6043,7 +6180,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="597" spans="6:7" s="42" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="6:7" s="42" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F597" s="41" t="s">
         <v>584</v>
       </c>
@@ -6051,7 +6188,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="600" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="600" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F600" t="s">
         <v>588</v>
       </c>
@@ -6059,7 +6196,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="601" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="601" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F601" s="2" t="s">
         <v>590</v>
       </c>
@@ -6067,7 +6204,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="602" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="602" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F602" s="2" t="s">
         <v>592</v>
       </c>
@@ -6075,7 +6212,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="603" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="603" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F603" s="2" t="s">
         <v>596</v>
       </c>
@@ -6083,7 +6220,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="604" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="604" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F604" s="2" t="s">
         <v>597</v>
       </c>
@@ -6091,7 +6228,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="605" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="605" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F605" s="2" t="s">
         <v>598</v>
       </c>
@@ -6099,7 +6236,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="606" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="606" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F606" s="2" t="s">
         <v>600</v>
       </c>
@@ -6107,7 +6244,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="607" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="607" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F607" s="2" t="s">
         <v>601</v>
       </c>
@@ -6115,7 +6252,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="608" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="608" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F608" s="2" t="s">
         <v>604</v>
       </c>
@@ -6123,7 +6260,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="609" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="609" spans="6:8" x14ac:dyDescent="0.25">
       <c r="F609" s="2" t="s">
         <v>606</v>
       </c>
@@ -6131,7 +6268,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="611" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="611" spans="6:8" x14ac:dyDescent="0.25">
       <c r="F611" s="2" t="s">
         <v>236</v>
       </c>
@@ -6139,129 +6276,179 @@
         <v>608</v>
       </c>
     </row>
-    <row r="612" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="612" spans="6:8" x14ac:dyDescent="0.25">
       <c r="H612" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="616" spans="6:8" ht="21" x14ac:dyDescent="0.5">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="616" spans="6:8" ht="21" x14ac:dyDescent="0.35">
       <c r="F616" s="45" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="617" spans="6:8" ht="21" x14ac:dyDescent="0.5">
+    <row r="617" spans="6:8" ht="21" x14ac:dyDescent="0.35">
       <c r="F617" s="46" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="618" spans="6:8" ht="21" x14ac:dyDescent="0.5">
+    <row r="618" spans="6:8" ht="21" x14ac:dyDescent="0.35">
       <c r="F618" s="46" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="619" spans="6:8" ht="21" x14ac:dyDescent="0.5">
+    <row r="619" spans="6:8" ht="21" x14ac:dyDescent="0.35">
       <c r="F619" s="46" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="624" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="624" spans="6:8" x14ac:dyDescent="0.25">
       <c r="F624" s="2" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="625" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="625" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F625" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="626" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="626" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F626" s="2" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="628" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="628" spans="6:6" ht="21" x14ac:dyDescent="0.35">
       <c r="F628" s="47" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="629" spans="6:6" ht="42" x14ac:dyDescent="0.5">
+    <row r="629" spans="6:6" ht="42" x14ac:dyDescent="0.35">
       <c r="F629" s="48" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="631" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="631" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F631" s="2" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="634" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="634" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F634" s="2" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="635" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="635" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F635" s="2" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="636" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="636" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F636" s="2" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="637" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="637" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F637" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="640" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="640" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F640" s="49" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="641" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="641" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F641" s="49" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="642" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="642" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F642" s="49" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="643" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="643" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F643" s="50" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="644" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="644" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F644" s="50" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="645" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="645" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F645" s="50" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="649" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F649" s="2" t="s">
+    <row r="650" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F650" s="2" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="650" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F650" s="2" t="s">
+    <row r="651" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F651" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="651" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F651" s="2" t="s">
+    <row r="652" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F652" s="2" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="653" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F653" s="2" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="652" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F652" s="2" t="s">
+    <row r="654" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F654" s="2" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="655" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F655" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="656" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F656" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="657" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F657" s="2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="658" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F658" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="659" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F659" s="2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="664" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F664" t="s">
         <v>634</v>
+      </c>
+    </row>
+    <row r="665" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F665" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="666" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F666" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="667" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F667" s="2" t="s">
+        <v>638</v>
       </c>
     </row>
   </sheetData>
@@ -6276,84 +6463,84 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97581F73-ACDD-44F9-985C-0540C21B38C5}">
   <dimension ref="A1:C79"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="21" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="20.25" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="98.1796875" style="14" customWidth="1"/>
-    <col min="2" max="2" width="22.453125" style="14" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" style="14"/>
+    <col min="1" max="1" width="98.140625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" style="14" customWidth="1"/>
+    <col min="3" max="16384" width="8.7109375" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B21" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="14" t="s">
         <v>47</v>
       </c>
@@ -6361,42 +6548,42 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="14" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="14" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="14" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="14" t="s">
         <v>56</v>
       </c>
@@ -6404,7 +6591,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="14" t="s">
         <v>56</v>
       </c>
@@ -6415,87 +6602,87 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="14" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="14" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="14" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="14" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C54" s="14" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="14" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="14" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="14" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="14" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" s="14" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" s="14" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" s="14" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" s="14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" s="14" t="s">
         <v>86</v>
       </c>
@@ -6508,143 +6695,143 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A56"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="98.7265625" style="4" customWidth="1"/>
-    <col min="2" max="16384" width="8.7265625" style="4"/>
+    <col min="1" max="1" width="98.7109375" style="4" customWidth="1"/>
+    <col min="2" max="16384" width="8.7109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="26" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="32" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="27" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="18" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="20" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="25" t="s">
         <v>517</v>
       </c>
@@ -6661,54 +6848,54 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD312072-87FE-40B5-A445-1591614412BD}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="23.5" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="159.81640625" style="33" customWidth="1"/>
-    <col min="2" max="2" width="76.81640625" style="33" customWidth="1"/>
-    <col min="3" max="16384" width="9.1796875" style="33"/>
+    <col min="1" max="1" width="159.85546875" style="33" customWidth="1"/>
+    <col min="2" max="2" width="76.85546875" style="33" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="33" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="37" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:3" s="37" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="37" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="38" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:3" s="38" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="38" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="39" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:3" s="39" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="39" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="33" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="33" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="33" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="33" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="33" t="s">
         <v>255</v>
       </c>
@@ -6719,7 +6906,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="33" t="s">
         <v>356</v>
       </c>
@@ -6727,12 +6914,12 @@
         <v>358</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="33" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="33" t="s">
         <v>508</v>
       </c>
@@ -6740,7 +6927,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="36" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:3" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="36" t="s">
         <v>527</v>
       </c>
@@ -6748,7 +6935,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="33" t="s">
         <v>553</v>
       </c>
@@ -6756,12 +6943,12 @@
         <v>554</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>587</v>
       </c>
@@ -6774,21 +6961,21 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82BFCEE3-ED03-49F6-AF6F-9D257DBB8787}">
   <dimension ref="A3:E5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.54296875" customWidth="1"/>
-    <col min="2" max="2" width="46.54296875" customWidth="1"/>
-    <col min="3" max="3" width="0.453125" customWidth="1"/>
-    <col min="4" max="4" width="0.54296875" customWidth="1"/>
-    <col min="5" max="5" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="30.5703125" customWidth="1"/>
+    <col min="2" max="2" width="46.5703125" customWidth="1"/>
+    <col min="3" max="3" width="0.42578125" customWidth="1"/>
+    <col min="4" max="4" width="0.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>533</v>
       </c>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B373254-FFBB-4232-A24A-1B00FEFAF001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905E7D07-9229-4A92-9E37-0E7AA8CF6CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2760" windowWidth="28785" windowHeight="12825" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Stack" sheetId="1" r:id="rId1"/>
@@ -191,7 +191,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="658">
   <si>
     <t>NextJS</t>
   </si>
@@ -2426,6 +2426,45 @@
   </si>
   <si>
     <t>Egress only Internet Gateway</t>
+  </si>
+  <si>
+    <t>4126358  BESCOM</t>
+  </si>
+  <si>
+    <t>Amazon Redshift   based on postgreSQL Database based on OLAP  - High performance - scale to PBs of data</t>
+  </si>
+  <si>
+    <t>Glue Streaming</t>
+  </si>
+  <si>
+    <t>Dynamodb stream</t>
+  </si>
+  <si>
+    <t>aws neptune steam</t>
+  </si>
+  <si>
+    <t>apache Flink</t>
+  </si>
+  <si>
+    <t>apache spark</t>
+  </si>
+  <si>
+    <t>apacher casandra</t>
+  </si>
+  <si>
+    <t>SageMaker AI = A managed platform for developing and deploying machine-learning models.</t>
+  </si>
+  <si>
+    <t>A company wants to build, train, and deploy its own machine-learning models.</t>
+  </si>
+  <si>
+    <t>Cloud watch Matrics stream</t>
+  </si>
+  <si>
+    <t>Quicksight</t>
+  </si>
+  <si>
+    <t>Cloud Watch Application Insight</t>
   </si>
 </sst>
 </file>
@@ -3108,90 +3147,90 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D92"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D94"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="123.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="90.7109375" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="123.54296875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="90.7265625" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
         <v>12</v>
       </c>
@@ -3199,8 +3238,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>13</v>
       </c>
@@ -3208,7 +3247,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
         <v>15</v>
       </c>
@@ -3216,98 +3255,98 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
     </row>
-    <row r="29" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="10"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="58" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="24" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A65" s="25" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="70" spans="1:2" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" s="28" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A70" s="28" t="s">
         <v>522</v>
       </c>
@@ -3315,27 +3354,27 @@
         <v>523</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="20" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>579</v>
       </c>
@@ -3343,24 +3382,29 @@
         <v>580</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="20" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>636</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94" s="1" t="s">
+        <v>645</v>
       </c>
     </row>
   </sheetData>
@@ -3377,423 +3421,423 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD904FA-0FAD-46CD-8773-AE594AFC6DAB}">
-  <dimension ref="B10:H667"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B10:H702"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="8.7109375" customWidth="1"/>
-    <col min="6" max="6" width="162.85546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="58.7109375" customWidth="1"/>
+    <col min="1" max="2" width="8.7265625" customWidth="1"/>
+    <col min="6" max="6" width="162.81640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="58.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="10" spans="6:6" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="6:6" ht="409.5" x14ac:dyDescent="0.55000000000000004">
       <c r="F10" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="6:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="32" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F32" s="15" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="33" spans="6:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="33" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F33" s="15" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="6:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="34" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F34" s="15" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="6:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="35" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F35" s="15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="6:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="36" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F36" s="15" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="37" spans="6:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="37" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F37" s="15" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="6:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="38" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F38" s="15" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="39" spans="6:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="39" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F39" s="15"/>
     </row>
-    <row r="40" spans="6:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="40" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F40" s="15"/>
     </row>
-    <row r="41" spans="6:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="41" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F41" s="15" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="42" spans="6:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="42" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F42" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="43" spans="6:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="43" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F43" s="15" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="44" spans="6:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="44" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F44" s="15" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="45" spans="6:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="45" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F45" s="15" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="46" spans="6:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="46" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F46" s="15" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="6:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="47" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F47" s="15" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="48" spans="6:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="48" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F48" s="15" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="49" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="49" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E49" s="15"/>
       <c r="F49" s="15" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="50" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E50" s="15"/>
       <c r="F50" s="15" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="51" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="51" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E51" s="15"/>
       <c r="F51" s="15" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="52" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="52" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E52" s="15"/>
       <c r="F52" s="15" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="53" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E53" s="15"/>
       <c r="F53" s="15" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="54" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="54" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E54" s="15"/>
       <c r="F54" s="15" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="55" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="55" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E55" s="15"/>
       <c r="F55" s="15" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="56" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="56" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E56" s="15"/>
       <c r="F56" s="15" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="57" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="57" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E57" s="15"/>
       <c r="F57" s="15" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="58" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="58" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E58" s="15"/>
       <c r="F58" s="15" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="59" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="59" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E59" s="15"/>
       <c r="F59" s="15" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="60" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="60" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E60" s="15"/>
       <c r="F60" s="15" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="61" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="61" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E61" s="15"/>
       <c r="F61" s="15"/>
     </row>
-    <row r="62" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="62" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E62" s="15"/>
       <c r="F62" s="15"/>
     </row>
-    <row r="63" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="63" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E63" s="15"/>
       <c r="F63" s="15"/>
     </row>
-    <row r="64" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="64" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E64" s="15"/>
       <c r="F64" s="15" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="65" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="65" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E65" s="15"/>
       <c r="F65" s="15" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="66" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="66" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E66" s="15"/>
       <c r="F66" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="67" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="67" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E67" s="15"/>
       <c r="F67" s="15" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="68" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="68" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E68" s="15"/>
       <c r="F68" s="15" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="69" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="69" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E69" s="15"/>
       <c r="F69" s="15" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="70" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="70" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E70" s="15"/>
       <c r="F70" s="15" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="71" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="71" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E71" s="15"/>
       <c r="F71" s="15" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="72" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="72" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E72" s="15"/>
       <c r="F72" s="15" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="73" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="73" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E73" s="15"/>
       <c r="F73" s="15" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="74" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="74" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E74" s="15"/>
       <c r="F74" s="15" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="75" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="75" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E75" s="15"/>
       <c r="F75" s="15" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="76" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="76" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E76" s="15"/>
       <c r="F76" s="15" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="77" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="77" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E77" s="15"/>
       <c r="F77" s="15" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="78" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="78" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E78" s="15"/>
       <c r="F78" s="15" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="79" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="79" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E79" s="15"/>
       <c r="F79" s="15" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="80" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="80" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E80" s="15"/>
       <c r="F80" s="15" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="81" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="81" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E81" s="15"/>
       <c r="F81" s="15" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="82" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="82" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E82" s="15"/>
       <c r="F82" s="15" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="83" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="83" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E83" s="15"/>
       <c r="F83" s="15" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="84" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="84" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E84" s="15"/>
       <c r="F84" s="15"/>
     </row>
-    <row r="85" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="85" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E85" s="15"/>
       <c r="F85" s="15"/>
     </row>
-    <row r="86" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="86" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E86" s="15"/>
       <c r="F86" s="15" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="87" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="87" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E87" s="15"/>
       <c r="F87" s="15" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="88" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="88" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E88" s="15"/>
       <c r="F88" s="15" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="89" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="89" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E89" s="15"/>
       <c r="F89" s="15"/>
     </row>
-    <row r="90" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="90" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E90" s="15"/>
       <c r="F90" s="15"/>
     </row>
-    <row r="91" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="91" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E91" s="15"/>
       <c r="F91" s="15" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="92" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="92" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E92" s="15"/>
       <c r="F92" s="15" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="93" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="93" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E93" s="15"/>
       <c r="F93" s="15" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="94" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E94" s="15"/>
       <c r="F94" s="15" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="95" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="95" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E95" s="15"/>
       <c r="F95" s="15" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="96" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="96" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E96" s="15"/>
       <c r="F96" s="15" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="97" spans="5:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="97" spans="5:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E97" s="15"/>
       <c r="F97" s="15" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="98" spans="5:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="98" spans="5:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E98" s="15"/>
       <c r="F98" s="15" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="99" spans="5:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="99" spans="5:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E99" s="15"/>
       <c r="F99" s="15" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="100" spans="5:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="100" spans="5:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E100" s="15"/>
       <c r="F100" s="15" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="101" spans="5:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="101" spans="5:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E101" s="15"/>
       <c r="F101" s="15" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="102" spans="5:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="102" spans="5:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E102" s="15"/>
       <c r="F102" s="15" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="103" spans="5:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="103" spans="5:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E103" s="15"/>
       <c r="F103" s="15" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="104" spans="5:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="104" spans="5:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E104" s="15"/>
       <c r="F104" s="15" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="105" spans="5:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="105" spans="5:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E105" s="15"/>
       <c r="F105" s="15" t="s">
         <v>155</v>
@@ -3802,571 +3846,571 @@
         <v>37</v>
       </c>
     </row>
-    <row r="106" spans="5:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="106" spans="5:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E106" s="15"/>
       <c r="F106" s="15" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="107" spans="5:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="107" spans="5:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E107" s="15"/>
       <c r="F107" s="15"/>
     </row>
-    <row r="108" spans="5:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="108" spans="5:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E108" s="15"/>
       <c r="F108" s="15"/>
     </row>
-    <row r="109" spans="5:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="109" spans="5:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E109" s="15"/>
       <c r="F109" s="15" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="110" spans="5:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="110" spans="5:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E110" s="15"/>
       <c r="F110" s="15" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="111" spans="5:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="111" spans="5:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E111" s="15"/>
       <c r="F111" s="15" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="112" spans="5:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="112" spans="5:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E112" s="15"/>
       <c r="F112" s="15" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="113" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="113" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E113" s="15"/>
       <c r="F113" s="15" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="114" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="114" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E114" s="15"/>
       <c r="F114" s="15" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="115" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="115" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E115" s="15"/>
       <c r="F115" s="15" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="116" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="116" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E116" s="15"/>
       <c r="F116" s="15" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="117" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="117" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E117" s="15"/>
       <c r="F117" s="15" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="118" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="118" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E118" s="15"/>
       <c r="F118" s="15" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="119" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="119" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E119" s="15"/>
       <c r="F119" s="15" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="120" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="120" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E120" s="15"/>
       <c r="F120" s="15" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="121" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="121" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E121" s="15"/>
       <c r="F121" s="15"/>
     </row>
-    <row r="122" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="122" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E122" s="15"/>
       <c r="F122" s="15"/>
     </row>
-    <row r="123" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="123" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E123" s="15"/>
       <c r="F123" s="15"/>
     </row>
-    <row r="124" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="124" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E124" s="15"/>
       <c r="F124" s="15" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="125" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="125" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E125" s="15"/>
       <c r="F125" s="15" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="126" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="126" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E126" s="15"/>
       <c r="F126" s="15" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="127" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="127" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E127" s="15"/>
       <c r="F127" s="15" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="128" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="128" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E128" s="15"/>
       <c r="F128" s="15" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="129" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="129" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E129" s="15"/>
       <c r="F129" s="15" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="130" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="130" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E130" s="15"/>
       <c r="F130" s="15" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="131" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="131" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E131" s="15"/>
       <c r="F131" s="15" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="132" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="132" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E132" s="15"/>
       <c r="F132" s="15" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="133" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="133" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E133" s="15"/>
       <c r="F133" s="15" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="134" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="134" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E134" s="15"/>
       <c r="F134" s="15" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="135" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="135" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E135" s="15"/>
       <c r="F135" s="15" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="136" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="136" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E136" s="15"/>
       <c r="F136" s="15" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="137" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="137" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E137" s="15"/>
       <c r="F137" s="15" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="138" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="138" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E138" s="15"/>
       <c r="F138" s="15" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="139" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="139" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E139" s="15"/>
       <c r="F139" s="15" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="140" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="140" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E140" s="15"/>
       <c r="F140" s="15" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="141" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="141" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E141" s="15"/>
       <c r="F141" s="15" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="142" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="142" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E142" s="15"/>
       <c r="F142" s="15" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="143" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="143" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E143" s="15"/>
       <c r="F143" s="15" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="144" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="144" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E144" s="15"/>
       <c r="F144" s="15" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="145" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="145" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E145" s="15"/>
       <c r="F145" s="15" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="146" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="146" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E146" s="15"/>
       <c r="F146" s="15" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="147" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="147" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E147" s="15"/>
       <c r="F147" s="15" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="148" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="148" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E148" s="15"/>
       <c r="F148" s="15" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="149" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="149" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E149" s="15"/>
       <c r="F149" s="15" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="150" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="150" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E150" s="15"/>
       <c r="F150" s="15" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="151" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="151" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E151" s="15"/>
       <c r="F151" s="15"/>
     </row>
-    <row r="152" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="152" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E152" s="15"/>
       <c r="F152" s="15"/>
     </row>
-    <row r="153" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="153" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E153" s="15"/>
       <c r="F153" s="15" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="154" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="154" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E154" s="15"/>
       <c r="F154" s="15" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="155" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="155" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E155" s="15"/>
       <c r="F155" s="15" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="156" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="156" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E156" s="15"/>
       <c r="F156" s="15" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="157" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="157" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E157" s="15"/>
       <c r="F157" s="15" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="158" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="158" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E158" s="15"/>
       <c r="F158" s="15" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="159" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="159" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E159" s="15"/>
       <c r="F159" s="15" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="160" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="160" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E160" s="15"/>
       <c r="F160" s="15" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="161" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="161" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E161" s="15"/>
       <c r="F161" s="15" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="162" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="162" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E162" s="15"/>
       <c r="F162" s="15" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="163" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="163" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E163" s="15"/>
       <c r="F163" s="15" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="164" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="164" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E164" s="15"/>
       <c r="F164" s="15" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="165" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="165" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E165" s="15"/>
       <c r="F165" s="15" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="166" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="166" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E166" s="15"/>
       <c r="F166" s="15" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="167" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="167" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E167" s="15"/>
       <c r="F167" s="15" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="168" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="168" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E168" s="15"/>
       <c r="F168" s="15" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="169" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="169" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E169" s="15"/>
       <c r="F169" s="15" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="170" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="170" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E170" s="15"/>
       <c r="F170" s="15" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="171" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="171" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E171" s="15"/>
       <c r="F171" s="15" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="172" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="172" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E172" s="15"/>
       <c r="F172" s="15" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="173" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="173" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E173" s="15"/>
       <c r="F173" s="15" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="174" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="174" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E174" s="15"/>
       <c r="F174" s="15" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="175" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="175" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E175" s="15"/>
       <c r="F175" s="15" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="176" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="176" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E176" s="15"/>
       <c r="F176" s="15" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="177" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="177" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E177" s="15"/>
       <c r="F177" s="15" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="178" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="178" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E178" s="15"/>
       <c r="F178" s="15" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="179" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="179" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E179" s="15"/>
       <c r="F179" s="15" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="180" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="180" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E180" s="15"/>
       <c r="F180" s="15" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="181" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="181" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E181" s="15"/>
       <c r="F181" s="15" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="182" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="182" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E182" s="15"/>
       <c r="F182" s="15" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="183" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="183" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E183" s="15"/>
       <c r="F183" s="15" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="184" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="184" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E184" s="15"/>
       <c r="F184" s="15" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="185" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="185" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E185" s="15"/>
       <c r="F185" s="15" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="186" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="186" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E186" s="15"/>
       <c r="F186" s="15" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="187" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="187" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E187" s="15"/>
       <c r="F187" s="15" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="188" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="188" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E188" s="15"/>
       <c r="F188" s="15"/>
     </row>
-    <row r="189" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="189" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E189" s="15"/>
       <c r="F189" s="15"/>
     </row>
-    <row r="190" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="190" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E190" s="15"/>
       <c r="F190" s="15"/>
     </row>
-    <row r="191" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="191" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E191" s="15"/>
       <c r="F191" s="15" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="192" spans="5:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="192" spans="5:6" ht="21" x14ac:dyDescent="0.5">
       <c r="E192" s="15"/>
       <c r="F192" s="15" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="193" spans="2:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="193" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E193" s="15"/>
       <c r="F193" s="15" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="194" spans="2:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="194" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E194" s="15"/>
       <c r="F194" s="15" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="195" spans="2:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="195" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E195" s="15"/>
       <c r="F195" s="15" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="196" spans="2:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="196" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E196" s="15"/>
       <c r="F196" s="15" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="197" spans="2:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="197" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E197" s="15"/>
       <c r="F197" s="15" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="198" spans="2:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="198" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E198" s="15"/>
       <c r="F198" s="15" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="199" spans="2:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="199" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E199" s="15"/>
       <c r="F199" s="15" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="200" spans="2:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="200" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E200" s="15"/>
       <c r="F200" s="15" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="201" spans="2:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="201" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E201" s="15"/>
       <c r="F201" s="15"/>
     </row>
-    <row r="202" spans="2:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="202" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E202" s="15"/>
       <c r="F202" s="15"/>
     </row>
-    <row r="203" spans="2:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="203" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E203" s="15"/>
       <c r="F203" s="15" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="204" spans="2:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="204" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E204" s="15"/>
       <c r="F204" s="15" t="s">
         <v>246</v>
@@ -4375,24 +4419,24 @@
         <v>37</v>
       </c>
     </row>
-    <row r="205" spans="2:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="205" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E205" s="15"/>
       <c r="F205" s="15" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="206" spans="2:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="206" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="E206" s="15"/>
       <c r="F206" s="15" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="207" spans="2:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="207" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="F207" s="15" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="208" spans="2:7" ht="21" x14ac:dyDescent="0.35">
+    <row r="208" spans="2:7" ht="21" x14ac:dyDescent="0.5">
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
       <c r="D208" s="4"/>
@@ -4401,7 +4445,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="209" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
       <c r="D209" s="4"/>
@@ -4410,7 +4454,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="210" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
       <c r="D210" s="4"/>
@@ -4419,7 +4463,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="211" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
       <c r="D211" s="4"/>
@@ -4428,7 +4472,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="212" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
       <c r="D212" s="4"/>
@@ -4437,7 +4481,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="213" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
       <c r="D213" s="4"/>
@@ -4446,7 +4490,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="214" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
       <c r="D214" s="4"/>
@@ -4455,7 +4499,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="215" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
       <c r="D215" s="4"/>
@@ -4464,7 +4508,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="216" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
       <c r="D216" s="4"/>
@@ -4473,7 +4517,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="217" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
       <c r="D217" s="4"/>
@@ -4482,28 +4526,28 @@
         <v>262</v>
       </c>
     </row>
-    <row r="218" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
       <c r="D218" s="4"/>
       <c r="E218" s="4"/>
       <c r="F218" s="16"/>
     </row>
-    <row r="219" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
       <c r="F219" s="16"/>
     </row>
-    <row r="220" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
       <c r="D220" s="4"/>
       <c r="E220" s="4"/>
       <c r="F220" s="16"/>
     </row>
-    <row r="221" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
       <c r="D221" s="4"/>
@@ -4512,7 +4556,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="222" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
       <c r="D222" s="4"/>
@@ -4521,7 +4565,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="223" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
       <c r="D223" s="4"/>
@@ -4530,7 +4574,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="224" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
       <c r="D224" s="4"/>
@@ -4539,7 +4583,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="225" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
       <c r="D225" s="4"/>
@@ -4548,7 +4592,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="226" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
       <c r="D226" s="4"/>
@@ -4557,7 +4601,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="227" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
       <c r="D227" s="4"/>
@@ -4566,7 +4610,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="228" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
       <c r="D228" s="4"/>
@@ -4575,7 +4619,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="229" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
       <c r="D229" s="4"/>
@@ -4584,35 +4628,35 @@
         <v>271</v>
       </c>
     </row>
-    <row r="230" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
       <c r="F230" s="16"/>
     </row>
-    <row r="231" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
       <c r="F231" s="16"/>
     </row>
-    <row r="232" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
       <c r="F232" s="16"/>
     </row>
-    <row r="233" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
       <c r="F233" s="16"/>
     </row>
-    <row r="234" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
       <c r="D234" s="4"/>
@@ -4621,7 +4665,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="235" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
       <c r="D235" s="4"/>
@@ -4630,7 +4674,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="236" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
       <c r="D236" s="4"/>
@@ -4639,7 +4683,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="237" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
       <c r="D237" s="4"/>
@@ -4648,7 +4692,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="238" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
       <c r="D238" s="4"/>
@@ -4657,7 +4701,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="239" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
       <c r="D239" s="4"/>
@@ -4666,7 +4710,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="240" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
       <c r="D240" s="4"/>
@@ -4675,7 +4719,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="241" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
       <c r="D241" s="4"/>
@@ -4684,7 +4728,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="242" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
       <c r="D242" s="4"/>
@@ -4693,28 +4737,28 @@
         <v>280</v>
       </c>
     </row>
-    <row r="243" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
       <c r="F243" s="16"/>
     </row>
-    <row r="244" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
       <c r="D244" s="4"/>
       <c r="E244" s="4"/>
       <c r="F244" s="16"/>
     </row>
-    <row r="245" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
       <c r="D245" s="4"/>
       <c r="E245" s="4"/>
       <c r="F245" s="16"/>
     </row>
-    <row r="246" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
       <c r="D246" s="4"/>
@@ -4723,7 +4767,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="247" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
       <c r="D247" s="4"/>
@@ -4732,7 +4776,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="248" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
       <c r="D248" s="4"/>
@@ -4741,7 +4785,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="249" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
       <c r="D249" s="4"/>
@@ -4750,7 +4794,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="250" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
       <c r="D250" s="4"/>
@@ -4759,7 +4803,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="251" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
       <c r="D251" s="4"/>
@@ -4768,7 +4812,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="252" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
       <c r="D252" s="4"/>
@@ -4777,7 +4821,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="253" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
       <c r="D253" s="4"/>
@@ -4786,7 +4830,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="254" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
       <c r="D254" s="4"/>
@@ -4795,28 +4839,28 @@
         <v>289</v>
       </c>
     </row>
-    <row r="255" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
       <c r="D255" s="4"/>
       <c r="E255" s="4"/>
       <c r="F255" s="16"/>
     </row>
-    <row r="256" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
       <c r="D256" s="4"/>
       <c r="E256" s="4"/>
       <c r="F256" s="16"/>
     </row>
-    <row r="257" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
       <c r="D257" s="4"/>
       <c r="E257" s="4"/>
       <c r="F257" s="16"/>
     </row>
-    <row r="258" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
       <c r="D258" s="4"/>
@@ -4825,21 +4869,21 @@
         <v>291</v>
       </c>
     </row>
-    <row r="259" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B259" s="4"/>
       <c r="C259" s="4"/>
       <c r="D259" s="4"/>
       <c r="E259" s="4"/>
       <c r="F259" s="16"/>
     </row>
-    <row r="260" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
       <c r="D260" s="4"/>
       <c r="E260" s="4"/>
       <c r="F260" s="16"/>
     </row>
-    <row r="261" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
       <c r="D261" s="4"/>
@@ -4848,7 +4892,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="262" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B262" s="4"/>
       <c r="C262" s="4"/>
       <c r="D262" s="4"/>
@@ -4857,7 +4901,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="263" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B263" s="4"/>
       <c r="C263" s="4"/>
       <c r="D263" s="4"/>
@@ -4866,7 +4910,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="264" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
       <c r="D264" s="4"/>
@@ -4875,7 +4919,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="265" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B265" s="4"/>
       <c r="C265" s="4"/>
       <c r="D265" s="4"/>
@@ -4884,21 +4928,21 @@
         <v>295</v>
       </c>
     </row>
-    <row r="266" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B266" s="4"/>
       <c r="C266" s="4"/>
       <c r="D266" s="4"/>
       <c r="E266" s="4"/>
       <c r="F266" s="16"/>
     </row>
-    <row r="267" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
       <c r="D267" s="4"/>
       <c r="E267" s="4"/>
       <c r="F267" s="16"/>
     </row>
-    <row r="268" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
       <c r="D268" s="4"/>
@@ -4907,7 +4951,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="269" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
       <c r="D269" s="4"/>
@@ -4916,7 +4960,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="270" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
       <c r="D270" s="4"/>
@@ -4925,28 +4969,28 @@
         <v>298</v>
       </c>
     </row>
-    <row r="271" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
       <c r="D271" s="4"/>
       <c r="E271" s="4"/>
       <c r="F271" s="16"/>
     </row>
-    <row r="272" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
       <c r="D272" s="4"/>
       <c r="E272" s="4"/>
       <c r="F272" s="16"/>
     </row>
-    <row r="273" spans="2:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
       <c r="D273" s="4"/>
       <c r="E273" s="4"/>
       <c r="F273" s="16"/>
     </row>
-    <row r="274" spans="2:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
       <c r="D274" s="4"/>
@@ -4955,7 +4999,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="275" spans="2:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
       <c r="D275" s="4"/>
@@ -4964,57 +5008,57 @@
         <v>300</v>
       </c>
     </row>
-    <row r="276" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F276" s="2" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="277" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F277" s="2" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="278" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F278" s="2" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="279" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F279" s="2" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="280" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F280" s="2" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="281" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F281" s="2" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="282" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F282" s="2" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="283" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F283" s="2" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="284" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F284" s="2" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="285" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F285" s="2" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="286" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F286" s="2" t="s">
         <v>312</v>
       </c>
@@ -5022,162 +5066,162 @@
         <v>311</v>
       </c>
     </row>
-    <row r="287" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F287" s="2" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="288" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F288" s="2" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="289" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F289" s="2" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="290" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F290" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="291" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F291" s="17" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="292" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F292" s="2" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="293" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F293" s="2" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="294" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F294" s="2" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="298" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F298" s="2" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="299" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F299" s="2" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="300" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F300" s="2" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="301" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F301" s="2" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="302" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F302" s="2" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="303" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F303" s="2" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="304" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F304" s="2" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="305" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F305" s="2" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="306" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F306" s="2" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="307" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F307" s="2" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="308" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F308" s="2" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="309" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F309" s="2" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="310" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F310" s="2" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="315" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F315" s="2" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="316" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F316" s="2" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="317" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F317" s="2" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="318" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F318" s="19" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="319" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F319" s="19" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="320" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F320" s="19" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="321" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F321" s="19" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="322" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F322" s="2" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="325" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F325" s="2" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="326" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F326" s="2" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="327" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F327" s="2" t="s">
         <v>346</v>
       </c>
@@ -5185,712 +5229,712 @@
         <v>37</v>
       </c>
     </row>
-    <row r="328" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F328" s="2" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="329" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F329" s="2" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="330" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F330" s="2" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="331" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F331" s="2" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="332" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F332" s="2" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="333" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F333" s="2" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="334" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F334" s="2" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="335" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F335" s="2" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="336" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F336" s="2" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="339" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F339" s="2" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="342" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F342" s="2" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="343" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F343" s="2" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="344" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F344" s="2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="345" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F345" s="2" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="346" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F346" s="2" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="347" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F347" s="2" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="348" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F348" s="2" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="349" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F349" s="2" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="350" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F350" s="2" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="355" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F355" s="2" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="356" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F356" s="2" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="357" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F357" s="2" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="358" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F358" s="2" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="359" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F359" s="2" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="360" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F360" s="2" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="361" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F361" s="2" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="362" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F362" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="363" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F363" s="2" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="364" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="364" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F364" s="2" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="365" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F365" s="2" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="366" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F366" s="2" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="367" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="367" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F367" s="2" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="368" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F368" s="2" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="371" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F371" s="2" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="373" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F373" s="2" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="377" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F377" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="380" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F380" s="2" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="382" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F382" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="383" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F383" s="2" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="384" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F384" s="2" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="385" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F385" s="2" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="386" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F386" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="387" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F387" s="2" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="390" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F390" s="2" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="391" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F391" s="2" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="392" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F392" s="2" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="393" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F393" s="2" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="394" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F394" s="2" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="395" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F395" s="2" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="398" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F398" s="2" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="399" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F399" s="2" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="400" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F400" s="2" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="401" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F401" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="402" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F402" s="2" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="403" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F403" s="2" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="408" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F408" s="2" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="410" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F410" s="2" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="411" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F411" s="2" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="412" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F412" s="2" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="413" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F413" s="2" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="414" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F414" s="2" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="415" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F415" s="2" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="416" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F416" s="2" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="417" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F417" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="418" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F418" s="2" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="419" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F419" s="2" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="420" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F420" s="2" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="421" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="421" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F421" s="2" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="422" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F422" s="2" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="423" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F423" s="2" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="424" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F424" s="2" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="427" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F427" s="2" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="428" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F428" s="2" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="429" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F429" s="2" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="430" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F430" s="2" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="431" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F431" s="2" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="432" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F432" s="2" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="433" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F433" s="2" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="434" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F434" s="2" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="435" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F435" s="2" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="436" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F436" s="2" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="437" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F437" s="2" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="438" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F438" s="2" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="439" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F439" s="2" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="440" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F440" s="2" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="441" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F441" s="2" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="442" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F442" s="2" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="443" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F443" s="2" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="444" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F444" s="2" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="445" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F445" s="2" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="446" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F446" s="2" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="447" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F447" s="2" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="448" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F448" s="2" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="449" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F449" s="2" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="450" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F450" s="2" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="453" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F453" s="2" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="454" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F454" s="2" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="455" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F455" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="456" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F456" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="457" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F457" s="2" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="458" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F458" s="2" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="459" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F459" s="2" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="460" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F460" s="2" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="461" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F461" s="2" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="462" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="462" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F462" s="2" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="463" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="463" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F463" s="2" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="464" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F464" s="2" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="465" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="465" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F465" s="2" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="466" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="466" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F466" s="2" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="467" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="467" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F467" s="2" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="468" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="468" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F468" s="2" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="469" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="469" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F469" s="2" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="470" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="470" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F470" s="2" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="473" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="473" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F473" s="2" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="474" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="474" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F474" s="2" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="475" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="475" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F475" s="2" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="476" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="476" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F476" s="2" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="477" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="477" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F477" s="2" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="478" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="478" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F478" s="2" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="479" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="479" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F479" s="2" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="480" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="480" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F480" s="2" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="481" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="481" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F481" s="2" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="482" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="482" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F482" s="2" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="483" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="483" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F483" s="2" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="484" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="484" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F484" s="2" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="485" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="485" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F485" s="2" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="486" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="486" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F486" s="2" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="487" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="487" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F487" s="2" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="488" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="488" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F488" s="2" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="491" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="491" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F491" s="2" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="492" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="492" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F492" s="2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="493" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="493" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F493" s="2" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="494" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="494" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F494" s="2" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="495" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="495" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F495" s="2" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="496" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="496" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F496" s="2" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="497" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="497" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F497" s="2" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="498" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="498" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F498" s="2" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="499" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="499" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F499" s="2" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="500" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="500" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F500" s="2" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="501" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="501" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F501" s="2" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="502" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="502" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F502" s="2" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="503" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="503" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F503" s="2" t="s">
         <v>549</v>
       </c>
@@ -5898,7 +5942,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="504" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="504" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F504" s="2" t="s">
         <v>551</v>
       </c>
@@ -5906,7 +5950,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="513" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="513" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F513" s="21" t="s">
         <v>495</v>
       </c>
@@ -5914,7 +5958,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="514" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="514" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F514" s="22" t="s">
         <v>497</v>
       </c>
@@ -5922,7 +5966,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="515" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="515" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F515" s="22" t="s">
         <v>499</v>
       </c>
@@ -5930,7 +5974,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="516" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="516" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F516" s="22" t="s">
         <v>500</v>
       </c>
@@ -5938,15 +5982,15 @@
         <v>501</v>
       </c>
     </row>
-    <row r="517" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="517" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F517" s="22" t="s">
-        <v>282</v>
+        <v>646</v>
       </c>
       <c r="G517" s="22" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="519" spans="6:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="519" spans="6:7" ht="29" x14ac:dyDescent="0.35">
       <c r="F519" s="23" t="s">
         <v>505</v>
       </c>
@@ -5954,7 +5998,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="522" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="522" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F522" t="s">
         <v>504</v>
       </c>
@@ -5962,17 +6006,17 @@
         <v>507</v>
       </c>
     </row>
-    <row r="524" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="524" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F524" s="2" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="526" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="526" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F526" s="2" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="528" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="528" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F528" s="2" t="s">
         <v>513</v>
       </c>
@@ -5980,12 +6024,12 @@
         <v>514</v>
       </c>
     </row>
-    <row r="531" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="531" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F531" s="2" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="534" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="534" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F534" s="2" t="s">
         <v>518</v>
       </c>
@@ -5993,7 +6037,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="537" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="537" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F537" s="2" t="s">
         <v>525</v>
       </c>
@@ -6001,12 +6045,12 @@
         <v>526</v>
       </c>
     </row>
-    <row r="539" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="539" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F539" s="2" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="541" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="541" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F541" s="2" t="s">
         <v>536</v>
       </c>
@@ -6014,7 +6058,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="544" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="544" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F544" s="31" t="s">
         <v>538</v>
       </c>
@@ -6022,7 +6066,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="545" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="545" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F545" s="31" t="s">
         <v>540</v>
       </c>
@@ -6030,75 +6074,75 @@
         <v>541</v>
       </c>
     </row>
-    <row r="547" spans="6:7" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="6:7" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="F547" s="29" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="548" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="548" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F548" s="2" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="549" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="549" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F549" s="2" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="550" spans="6:7" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="6:7" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="F550" s="29" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="551" spans="6:7" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="6:7" s="30" customFormat="1" x14ac:dyDescent="0.35">
       <c r="F551" s="29" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="552" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="552" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F552" s="2" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="553" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="553" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F553" s="2" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="557" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="557" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F557" s="35" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="558" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="558" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F558" s="35" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="559" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="559" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F559" s="35" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="560" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="560" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F560" s="35" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="561" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="561" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F561" s="35" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="562" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="562" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F562" s="35" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="565" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="565" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F565" s="34"/>
     </row>
-    <row r="567" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="567" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F567" s="2" t="s">
         <v>563</v>
       </c>
@@ -6106,7 +6150,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="568" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="568" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F568" s="2" t="s">
         <v>564</v>
       </c>
@@ -6114,7 +6158,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="570" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="570" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F570" s="2" t="s">
         <v>567</v>
       </c>
@@ -6122,57 +6166,57 @@
         <v>568</v>
       </c>
     </row>
-    <row r="574" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="574" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F574" s="2" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="575" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="575" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F575" s="2" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="581" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="581" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F581" s="40" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="582" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="582" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F582" s="40" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="583" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="583" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F583" s="40" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="584" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="584" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F584" s="40" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="585" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="585" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F585" s="40" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="589" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="589" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F589" s="2" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="590" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="590" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F590" s="2" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="593" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="593" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F593" s="2" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="596" spans="6:7" s="44" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="6:7" s="44" customFormat="1" x14ac:dyDescent="0.35">
       <c r="F596" s="43" t="s">
         <v>582</v>
       </c>
@@ -6180,7 +6224,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="597" spans="6:7" s="42" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="6:7" s="42" customFormat="1" x14ac:dyDescent="0.35">
       <c r="F597" s="41" t="s">
         <v>584</v>
       </c>
@@ -6188,7 +6232,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="600" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="600" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F600" t="s">
         <v>588</v>
       </c>
@@ -6196,7 +6240,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="601" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="601" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F601" s="2" t="s">
         <v>590</v>
       </c>
@@ -6204,7 +6248,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="602" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="602" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F602" s="2" t="s">
         <v>592</v>
       </c>
@@ -6212,7 +6256,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="603" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="603" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F603" s="2" t="s">
         <v>596</v>
       </c>
@@ -6220,7 +6264,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="604" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="604" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F604" s="2" t="s">
         <v>597</v>
       </c>
@@ -6228,7 +6272,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="605" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="605" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F605" s="2" t="s">
         <v>598</v>
       </c>
@@ -6236,7 +6280,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="606" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="606" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F606" s="2" t="s">
         <v>600</v>
       </c>
@@ -6244,7 +6288,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="607" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="607" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F607" s="2" t="s">
         <v>601</v>
       </c>
@@ -6252,7 +6296,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="608" spans="6:7" x14ac:dyDescent="0.25">
+    <row r="608" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F608" s="2" t="s">
         <v>604</v>
       </c>
@@ -6260,7 +6304,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="609" spans="6:8" x14ac:dyDescent="0.25">
+    <row r="609" spans="6:8" x14ac:dyDescent="0.35">
       <c r="F609" s="2" t="s">
         <v>606</v>
       </c>
@@ -6268,7 +6312,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="611" spans="6:8" x14ac:dyDescent="0.25">
+    <row r="611" spans="6:8" x14ac:dyDescent="0.35">
       <c r="F611" s="2" t="s">
         <v>236</v>
       </c>
@@ -6276,179 +6320,234 @@
         <v>608</v>
       </c>
     </row>
-    <row r="612" spans="6:8" x14ac:dyDescent="0.25">
+    <row r="612" spans="6:8" x14ac:dyDescent="0.35">
       <c r="H612" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="616" spans="6:8" ht="21" x14ac:dyDescent="0.35">
+    <row r="616" spans="6:8" ht="21" x14ac:dyDescent="0.5">
       <c r="F616" s="45" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="617" spans="6:8" ht="21" x14ac:dyDescent="0.35">
+    <row r="617" spans="6:8" ht="21" x14ac:dyDescent="0.5">
       <c r="F617" s="46" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="618" spans="6:8" ht="21" x14ac:dyDescent="0.35">
+    <row r="618" spans="6:8" ht="21" x14ac:dyDescent="0.5">
       <c r="F618" s="46" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="619" spans="6:8" ht="21" x14ac:dyDescent="0.35">
+    <row r="619" spans="6:8" ht="21" x14ac:dyDescent="0.5">
       <c r="F619" s="46" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="624" spans="6:8" x14ac:dyDescent="0.25">
+    <row r="624" spans="6:8" x14ac:dyDescent="0.35">
       <c r="F624" s="2" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="625" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="625" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F625" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="626" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="626" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F626" s="2" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="628" spans="6:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="628" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F628" s="47" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="629" spans="6:6" ht="42" x14ac:dyDescent="0.35">
+    <row r="629" spans="6:6" ht="21" x14ac:dyDescent="0.5">
       <c r="F629" s="48" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="631" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="631" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F631" s="2" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="634" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="634" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F634" s="2" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="635" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="635" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F635" s="2" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="636" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="636" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F636" s="2" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="637" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="637" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F637" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="640" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="640" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F640" s="49" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="641" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="641" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F641" s="49" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="642" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="642" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F642" s="49" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="643" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="643" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F643" s="50" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="644" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="644" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F644" s="50" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="645" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="645" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F645" s="50" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="650" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="650" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F650" s="2" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="651" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="651" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F651" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="652" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="652" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F652" s="2" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="653" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="653" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F653" s="2" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="654" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="654" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F654" s="2" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="655" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="655" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F655" s="2" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="656" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="656" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F656" s="2" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="657" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="657" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F657" s="2" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="658" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="658" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F658" s="2" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="659" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="659" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F659" s="2" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="664" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="664" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F664" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="665" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="665" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F665" s="2" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="666" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="666" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F666" s="2" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="667" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="667" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F667" s="2" t="s">
         <v>638</v>
+      </c>
+    </row>
+    <row r="675" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F675" s="2" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="676" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F676" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="677" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F677" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="678" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F678" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="686" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F686" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="687" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F687" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="688" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F688" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="693" spans="6:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="F693" s="4" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="694" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F694" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="701" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F701" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="702" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F702" s="2" t="s">
+        <v>657</v>
       </c>
     </row>
   </sheetData>
@@ -6463,84 +6562,84 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97581F73-ACDD-44F9-985C-0540C21B38C5}">
   <dimension ref="A1:C79"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="20.25" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="21" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="98.140625" style="14" customWidth="1"/>
-    <col min="2" max="2" width="22.42578125" style="14" customWidth="1"/>
-    <col min="3" max="16384" width="8.7109375" style="14"/>
+    <col min="1" max="1" width="98.1796875" style="14" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" style="14" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="14" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="14" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="14" t="s">
         <v>47</v>
       </c>
@@ -6548,42 +6647,42 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="14" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="14" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="14" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="14" t="s">
         <v>56</v>
       </c>
@@ -6591,7 +6690,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="14" t="s">
         <v>56</v>
       </c>
@@ -6602,87 +6701,87 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="14" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="14" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="14" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="14" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="C54" s="14" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="14" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="14" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="14" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="14" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="14" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="14" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="14" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="14" t="s">
         <v>86</v>
       </c>
@@ -6695,143 +6794,143 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A56"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="98.7109375" style="4" customWidth="1"/>
-    <col min="2" max="16384" width="8.7109375" style="4"/>
+    <col min="1" max="1" width="98.7265625" style="4" customWidth="1"/>
+    <col min="2" max="16384" width="8.7265625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" s="12" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" s="12" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A29" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A31" s="26" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="32" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" s="18" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A32" s="27" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A33" s="18" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A37" s="4" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A39" s="20" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A46" s="4" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A47" s="4" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A48" s="4" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A49" s="4" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A50" s="4" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A51" s="4" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A56" s="25" t="s">
         <v>517</v>
       </c>
@@ -6848,54 +6947,54 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD312072-87FE-40B5-A445-1591614412BD}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="23.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="159.85546875" style="33" customWidth="1"/>
-    <col min="2" max="2" width="76.85546875" style="33" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="33"/>
+    <col min="1" max="1" width="159.81640625" style="33" customWidth="1"/>
+    <col min="2" max="2" width="76.81640625" style="33" customWidth="1"/>
+    <col min="3" max="16384" width="9.1796875" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="33" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="37" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" s="37" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="37" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="38" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" s="38" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="38" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="39" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" s="39" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="39" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="33" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="33" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="33" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="33" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="33" t="s">
         <v>255</v>
       </c>
@@ -6906,7 +7005,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="33" t="s">
         <v>356</v>
       </c>
@@ -6914,12 +7013,12 @@
         <v>358</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="33" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="33" t="s">
         <v>508</v>
       </c>
@@ -6927,7 +7026,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="36" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" s="36" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="36" t="s">
         <v>527</v>
       </c>
@@ -6935,7 +7034,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="33" t="s">
         <v>553</v>
       </c>
@@ -6943,12 +7042,12 @@
         <v>554</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>587</v>
       </c>
@@ -6961,21 +7060,21 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82BFCEE3-ED03-49F6-AF6F-9D257DBB8787}">
   <dimension ref="A3:E5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.5703125" customWidth="1"/>
-    <col min="2" max="2" width="46.5703125" customWidth="1"/>
-    <col min="3" max="3" width="0.42578125" customWidth="1"/>
-    <col min="4" max="4" width="0.5703125" customWidth="1"/>
-    <col min="5" max="5" width="58.85546875" customWidth="1"/>
+    <col min="1" max="1" width="30.54296875" customWidth="1"/>
+    <col min="2" max="2" width="46.54296875" customWidth="1"/>
+    <col min="3" max="3" width="0.453125" customWidth="1"/>
+    <col min="4" max="4" width="0.54296875" customWidth="1"/>
+    <col min="5" max="5" width="58.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>533</v>
       </c>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905E7D07-9229-4A92-9E37-0E7AA8CF6CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F4A7A8-1C78-414D-B842-FFC096F649B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -191,7 +191,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="702">
   <si>
     <t>NextJS</t>
   </si>
@@ -2465,6 +2465,138 @@
   </si>
   <si>
     <t>Cloud Watch Application Insight</t>
+  </si>
+  <si>
+    <t>IAM Permission = one specific action you are allowed to perform.   "What can I do?"     an identity that can be assumed</t>
+  </si>
+  <si>
+    <t>IAM Policy = a document that contains one or more permissions.   permissions attached to that role</t>
+  </si>
+  <si>
+    <t>Role + Permissions Policy = permissions the role has</t>
+  </si>
+  <si>
+    <t>Role + Trust Policy = who is allowed to assume the role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  AWS PrivateLink   Private Endpoint(3rd type of API Gateway)</t>
+  </si>
+  <si>
+    <t>AWS Security &amp; Encryption   (KMS, Encryption SDK, SSM Parameter Store)</t>
+  </si>
+  <si>
+    <t>Encryption in flight (TLS / SSL)</t>
+  </si>
+  <si>
+    <t>Server-side encryption at rest</t>
+  </si>
+  <si>
+    <t>Client-side encryption</t>
+  </si>
+  <si>
+    <t>AWS KMS (Key Management Service)</t>
+  </si>
+  <si>
+    <t>KMS Keys Types</t>
+  </si>
+  <si>
+    <t>Copying Snapshots across regions</t>
+  </si>
+  <si>
+    <t>KMS Key Policies</t>
+  </si>
+  <si>
+    <t>Copying Snapshots across accounts</t>
+  </si>
+  <si>
+    <t>KMS Multi-Region Keys</t>
+  </si>
+  <si>
+    <t>DynamoDB Global Tables and KMS MultiRegion Keys Client-Side encryption</t>
+  </si>
+  <si>
+    <t>Global Aurora and KMS Multi-Region Keys Client-Side encryption</t>
+  </si>
+  <si>
+    <t>S3 Replication Encryption Considerations</t>
+  </si>
+  <si>
+    <t>AMI Sharing Process Encrypted via KMS</t>
+  </si>
+  <si>
+    <t>SSM Parameter Store</t>
+  </si>
+  <si>
+    <t>SSM Parameter Store Hierarchy</t>
+  </si>
+  <si>
+    <t>Standard and advanced parameter tiers</t>
+  </si>
+  <si>
+    <t>Parameters Policies (for advanced parameters)</t>
+  </si>
+  <si>
+    <t>AWS Secrets Manager – Multi-Region Secrets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Certificate Manager (ACM) </t>
+  </si>
+  <si>
+    <t>ACM  – Requesting Public Certificates</t>
+  </si>
+  <si>
+    <t>ACM – Importing Public Certificates</t>
+  </si>
+  <si>
+    <t>ACM – Integration with ALB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API Gateway - Endpoint Types </t>
+  </si>
+  <si>
+    <t>ACM – Integration with API Gateway</t>
+  </si>
+  <si>
+    <t>AWS WAF – Web Application Firewall</t>
+  </si>
+  <si>
+    <t>WAF – Fixed IP while using WAF with a Load  Balancer</t>
+  </si>
+  <si>
+    <t>AWS Shield: protect from DDoS attack</t>
+  </si>
+  <si>
+    <t>AWS Firewall Manager</t>
+  </si>
+  <si>
+    <t>WAF vs. Firewall Manager vs. Shield</t>
+  </si>
+  <si>
+    <t>AWS Best Practices for DDoS Resiliency  Edge Location Mitigation (BP1, BP3)</t>
+  </si>
+  <si>
+    <t>AWS Best Practices for DDoS Resiliency Best pratices for DDoS mitigation</t>
+  </si>
+  <si>
+    <t>AWS Best Practices for DDoS Resiliency Application Layer Defense</t>
+  </si>
+  <si>
+    <t>AWS Best Practices for DDoS Resiliency Attack surface reduction</t>
+  </si>
+  <si>
+    <t>Amazon GuardDuty</t>
+  </si>
+  <si>
+    <t>Amazon Inspector</t>
+  </si>
+  <si>
+    <t>AWS Macie</t>
+  </si>
+  <si>
+    <t>Amazon VPC</t>
+  </si>
+  <si>
+    <t>Understanding CIDR – IPv4</t>
   </si>
 </sst>
 </file>
@@ -2745,7 +2877,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2835,6 +2967,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3421,7 +3554,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD904FA-0FAD-46CD-8773-AE594AFC6DAB}">
-  <dimension ref="B10:H702"/>
+  <dimension ref="B10:H768"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="8.7265625" customWidth="1"/>
@@ -6548,6 +6681,241 @@
     <row r="702" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F702" s="2" t="s">
         <v>657</v>
+      </c>
+    </row>
+    <row r="708" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F708" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="709" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F709" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="711" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F711" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="714" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F714" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="718" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F718" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="724" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F724" s="51" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="725" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F725" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="726" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F726" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="727" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F727" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="728" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F728" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="729" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F729" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="730" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F730" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="731" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F731" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="732" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F732" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="733" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F733" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="734" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F734" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="735" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F735" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="736" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F736" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="737" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F737" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="738" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F738" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="739" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F739" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="740" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F740" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="741" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F741" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="742" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F742" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="743" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F743" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="744" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F744" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="745" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F745" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="746" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F746" s="2" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="747" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F747" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="748" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F748" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="749" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F749" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="750" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F750" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="751" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F751" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="752" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F752" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="753" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F753" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="754" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F754" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="755" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F755" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="756" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F756" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="757" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F757" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="758" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F758" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="759" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F759" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="760" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F760" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="761" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F761" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="762" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F762" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="763" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F763" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="767" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F767" s="51" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="768" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F768" s="2" t="s">
+        <v>701</v>
       </c>
     </row>
   </sheetData>

--- a/Lookup.xlsx
+++ b/Lookup.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F4A7A8-1C78-414D-B842-FFC096F649B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B5020E-A99B-4A36-A30F-5DADB85F1267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="LYNUX COMMADS" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -186,12 +187,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="F721" authorId="0" shapeId="0" xr:uid="{263E8C41-D7B8-43E1-8E6B-F27277BD6A6D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+IP Multicast is a networking technique used to send one copy of data from a sender to multiple receivers simultaneously.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="794">
   <si>
     <t>NextJS</t>
   </si>
@@ -2593,10 +2618,286 @@
     <t>AWS Macie</t>
   </si>
   <si>
-    <t>Amazon VPC</t>
-  </si>
-  <si>
     <t>Understanding CIDR – IPv4</t>
+  </si>
+  <si>
+    <t>RAM</t>
+  </si>
+  <si>
+    <t>Resource Access Manager</t>
+  </si>
+  <si>
+    <t>IP Multicast</t>
+  </si>
+  <si>
+    <t>ECMP = Equal-cost multi-path routing</t>
+  </si>
+  <si>
+    <t>AWS Transit Gateway     == VPN to transit gateway</t>
+  </si>
+  <si>
+    <t>RDS My SQL : AWS  INSTALLS MYSQL FOR YOU ON EC2 INSTANCE INTERNALLY.</t>
+  </si>
+  <si>
+    <t>AWS Application Discovery Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ADS AWS Application Discovery Service</t>
+  </si>
+  <si>
+    <t>VPC Componetn Diagram</t>
+  </si>
+  <si>
+    <t>Understanding CIDR - Subnet Mak</t>
+  </si>
+  <si>
+    <t>Understanding CIDR – Little Exercise</t>
+  </si>
+  <si>
+    <t>Public VS Private (IPV4)</t>
+  </si>
+  <si>
+    <t>Default VPC Walkthrough</t>
+  </si>
+  <si>
+    <t>VPC in AWS - IPv4</t>
+  </si>
+  <si>
+    <t>VPS Subnet - IPv4</t>
+  </si>
+  <si>
+    <t>Adding Internet Gateway</t>
+  </si>
+  <si>
+    <t>Editing Routtable</t>
+  </si>
+  <si>
+    <t>Bastion Hosts</t>
+  </si>
+  <si>
+    <t>NAT instance ( Outdated)</t>
+  </si>
+  <si>
+    <t>NAT instance - comments</t>
+  </si>
+  <si>
+    <t>NAT Gateway High availability</t>
+  </si>
+  <si>
+    <t>Security Grooups and NACLs</t>
+  </si>
+  <si>
+    <t>NACL, Defulat NACL</t>
+  </si>
+  <si>
+    <t>Ephemeral Ports</t>
+  </si>
+  <si>
+    <t>Creating NACL rules for eah target subnets CIDR</t>
+  </si>
+  <si>
+    <t>Security Groups vs NACL's</t>
+  </si>
+  <si>
+    <t>VPC EndPoint ( AWS Private Link )</t>
+  </si>
+  <si>
+    <t>Types of End Points</t>
+  </si>
+  <si>
+    <t>Gateway or Interface Endpoint for S3</t>
+  </si>
+  <si>
+    <t>Lambada in VPC accessing DynamoDB</t>
+  </si>
+  <si>
+    <t>VPC Flow logs</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>VPC Flow log syntax</t>
+  </si>
+  <si>
+    <t>VPC Flow log - Troubleshooting SG and NACL issues</t>
+  </si>
+  <si>
+    <t>VPC Flow logs - Architectures</t>
+  </si>
+  <si>
+    <t>AWS Site-to-Site VPN</t>
+  </si>
+  <si>
+    <t>AWS Site-to-Site VPN Connection</t>
+  </si>
+  <si>
+    <t>AWS VPN Cloudhub</t>
+  </si>
+  <si>
+    <t>Direct Connect DX</t>
+  </si>
+  <si>
+    <t>Direct Connect Diagram</t>
+  </si>
+  <si>
+    <t>Direct Connect Gateway</t>
+  </si>
+  <si>
+    <t>Direct connecton types</t>
+  </si>
+  <si>
+    <t>Direct connecton encryption</t>
+  </si>
+  <si>
+    <t>Direct connection Resiliency</t>
+  </si>
+  <si>
+    <t>Site-to-Site VPN connection as a backup</t>
+  </si>
+  <si>
+    <t>Network topologies can be become complicated</t>
+  </si>
+  <si>
+    <t>Trasit Gateway</t>
+  </si>
+  <si>
+    <t>Transit Gateway : Site-to-Site VPN ECMP</t>
+  </si>
+  <si>
+    <t>Trasit Gateway throughput with ECNP</t>
+  </si>
+  <si>
+    <t>Transit Gateway : Share Direct Connect between multiple accounts</t>
+  </si>
+  <si>
+    <t>VPC Traffic mirroring</t>
+  </si>
+  <si>
+    <t>What is IPv6</t>
+  </si>
+  <si>
+    <t>IPv6 in VPC</t>
+  </si>
+  <si>
+    <t>IPv4 Troubleshooting</t>
+  </si>
+  <si>
+    <t>Egress-Only Internet Gateway</t>
+  </si>
+  <si>
+    <t>Network Protection on aws</t>
+  </si>
+  <si>
+    <t>AWS Network FireWall</t>
+  </si>
+  <si>
+    <t>Disaster Recovery and Migration</t>
+  </si>
+  <si>
+    <t>Disaster recovery overview</t>
+  </si>
+  <si>
+    <t>RPO RTO</t>
+  </si>
+  <si>
+    <t>Disaster Recovery Strategies</t>
+  </si>
+  <si>
+    <t>Backup and Restore</t>
+  </si>
+  <si>
+    <t>Pilot Light</t>
+  </si>
+  <si>
+    <t>Warm standby</t>
+  </si>
+  <si>
+    <t>MultiSite / Host site Approach</t>
+  </si>
+  <si>
+    <t>ALL AWS Multiregion</t>
+  </si>
+  <si>
+    <t>Disaster Recovery Tips</t>
+  </si>
+  <si>
+    <t>DMS - Data base migraion service</t>
+  </si>
+  <si>
+    <t>DMS Source and tags</t>
+  </si>
+  <si>
+    <t>DMS Continuous replication</t>
+  </si>
+  <si>
+    <t>AWS DBS - Multi AZ Deployment</t>
+  </si>
+  <si>
+    <t>RDS and Aurora MYSQL Migration</t>
+  </si>
+  <si>
+    <t>RDS and Aurora POSTGRE Migration</t>
+  </si>
+  <si>
+    <t>On-Premise strategy with AWS</t>
+  </si>
+  <si>
+    <t>AWS Backup</t>
+  </si>
+  <si>
+    <t>AWS Backup valut Lock</t>
+  </si>
+  <si>
+    <t>AWS Application Migration service</t>
+  </si>
+  <si>
+    <t>Vmware Cloud on AWS</t>
+  </si>
+  <si>
+    <t>Trasforming large data in to AWS</t>
+  </si>
+  <si>
+    <t>More solution Architecture</t>
+  </si>
+  <si>
+    <t>Used For</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>AWS Step Functions</t>
+  </si>
+  <si>
+    <t>Workflow orchestration</t>
+  </si>
+  <si>
+    <t>Coordinate multiple AWS services and application steps</t>
+  </si>
+  <si>
+    <t>Order processing workflow</t>
+  </si>
+  <si>
+    <t>Infrastructure as Code (IaC)</t>
+  </si>
+  <si>
+    <t>Create and manage AWS resources automatically</t>
+  </si>
+  <si>
+    <t>Create VPC, EC2, RDS using a template</t>
+  </si>
+  <si>
+    <t>AWS Elastic Beanstalk</t>
+  </si>
+  <si>
+    <t>Application deployment platform</t>
+  </si>
+  <si>
+    <t>Deploy and manage applications without managing infrastructure details</t>
+  </si>
+  <si>
+    <t>Deploy a Java Spring Boot application</t>
   </si>
 </sst>
 </file>
@@ -2748,7 +3049,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2863,6 +3164,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2877,7 +3190,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2968,6 +3281,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3554,12 +3875,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD904FA-0FAD-46CD-8773-AE594AFC6DAB}">
-  <dimension ref="B10:H768"/>
+  <dimension ref="B10:L849"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="8.7265625" customWidth="1"/>
-    <col min="6" max="6" width="162.81640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="58.7265625" customWidth="1"/>
+    <col min="6" max="6" width="58.36328125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="48.90625" customWidth="1"/>
+    <col min="8" max="8" width="75.26953125" customWidth="1"/>
+    <col min="9" max="9" width="37.81640625" customWidth="1"/>
+    <col min="10" max="10" width="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="10" spans="6:6" ht="409.5" x14ac:dyDescent="0.55000000000000004">
@@ -6083,6 +6407,14 @@
         <v>552</v>
       </c>
     </row>
+    <row r="505" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F505" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="G505" t="s">
+        <v>702</v>
+      </c>
+    </row>
     <row r="513" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F513" s="21" t="s">
         <v>495</v>
@@ -6309,6 +6641,11 @@
         <v>570</v>
       </c>
     </row>
+    <row r="576" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F576" t="s">
+        <v>708</v>
+      </c>
+    </row>
     <row r="581" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F581" s="40" t="s">
         <v>571</v>
@@ -6478,6 +6815,11 @@
         <v>629</v>
       </c>
     </row>
+    <row r="622" spans="6:8" x14ac:dyDescent="0.35">
+      <c r="F622" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
     <row r="624" spans="6:8" x14ac:dyDescent="0.35">
       <c r="F624" s="2" t="s">
         <v>615</v>
@@ -6608,6 +6950,11 @@
         <v>644</v>
       </c>
     </row>
+    <row r="660" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F660" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
     <row r="664" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F664" t="s">
         <v>634</v>
@@ -6663,104 +7010,175 @@
         <v>652</v>
       </c>
     </row>
-    <row r="693" spans="6:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="693" spans="6:12" ht="18.5" x14ac:dyDescent="0.45">
       <c r="F693" s="4" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="694" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="694" spans="6:12" x14ac:dyDescent="0.35">
       <c r="F694" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="701" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F701" s="2" t="s">
+    <row r="697" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F697" s="52" t="s">
+        <v>495</v>
+      </c>
+      <c r="G697" s="53" t="s">
+        <v>496</v>
+      </c>
+      <c r="H697" s="53" t="s">
+        <v>781</v>
+      </c>
+      <c r="I697" s="53" t="s">
+        <v>782</v>
+      </c>
+      <c r="J697" s="53"/>
+    </row>
+    <row r="698" spans="6:12" ht="21" x14ac:dyDescent="0.5">
+      <c r="F698" s="55" t="s">
+        <v>783</v>
+      </c>
+      <c r="G698" s="54" t="s">
+        <v>784</v>
+      </c>
+      <c r="H698" s="54" t="s">
+        <v>785</v>
+      </c>
+      <c r="I698" s="54" t="s">
+        <v>786</v>
+      </c>
+      <c r="J698" s="54"/>
+      <c r="K698" s="54"/>
+      <c r="L698" s="54"/>
+    </row>
+    <row r="699" spans="6:12" ht="21" x14ac:dyDescent="0.5">
+      <c r="F699" s="55" t="s">
+        <v>584</v>
+      </c>
+      <c r="G699" s="54" t="s">
+        <v>787</v>
+      </c>
+      <c r="H699" s="54" t="s">
+        <v>788</v>
+      </c>
+      <c r="I699" s="54" t="s">
+        <v>789</v>
+      </c>
+      <c r="J699" s="54"/>
+      <c r="K699" s="54"/>
+      <c r="L699" s="54"/>
+    </row>
+    <row r="700" spans="6:12" ht="21" x14ac:dyDescent="0.5">
+      <c r="F700" s="55" t="s">
+        <v>790</v>
+      </c>
+      <c r="G700" s="54" t="s">
+        <v>791</v>
+      </c>
+      <c r="H700" s="54" t="s">
+        <v>792</v>
+      </c>
+      <c r="I700" s="54" t="s">
+        <v>793</v>
+      </c>
+      <c r="J700" s="54"/>
+      <c r="K700" s="54"/>
+      <c r="L700" s="54"/>
+    </row>
+    <row r="702" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F702" s="2" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="702" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F702" s="2" t="s">
+    <row r="703" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F703" s="2" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="708" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F708" t="s">
+    <row r="709" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F709" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="709" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F709" s="2" t="s">
+    <row r="710" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F710" s="2" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="711" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F711" s="2" t="s">
+    <row r="712" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F712" s="2" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="714" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F714" t="s">
+    <row r="715" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F715" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="718" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F718" t="s">
+    <row r="719" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F719" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="724" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F724" s="51" t="s">
+    <row r="721" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F721" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="722" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F722" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="725" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F725" s="51" t="s">
         <v>663</v>
-      </c>
-    </row>
-    <row r="725" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F725" s="2" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="726" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F726" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="727" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F727" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="728" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F728" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="729" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F729" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="730" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F730" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="731" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F731" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="732" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F732" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="733" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F733" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="734" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F734" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="735" spans="6:6" x14ac:dyDescent="0.35">
@@ -6770,152 +7188,537 @@
     </row>
     <row r="736" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F736" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="737" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F737" s="2" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="737" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F737" t="s">
+    <row r="738" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F738" t="s">
         <v>674</v>
-      </c>
-    </row>
-    <row r="738" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F738" s="2" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="739" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F739" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="740" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F740" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="741" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F741" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="742" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F742" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="743" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F743" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="744" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F744" s="2" t="s">
-        <v>364</v>
+        <v>680</v>
       </c>
     </row>
     <row r="745" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F745" s="2" t="s">
-        <v>681</v>
+        <v>364</v>
       </c>
     </row>
     <row r="746" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F746" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="747" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F747" s="2" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="748" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F748" s="2" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="748" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F748" t="s">
+    <row r="749" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F749" t="s">
         <v>684</v>
-      </c>
-    </row>
-    <row r="749" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F749" s="2" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="750" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F750" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="751" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F751" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="752" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F752" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="753" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F753" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="754" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F754" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="755" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F755" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="756" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F756" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="757" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F757" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="758" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F758" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="759" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F759" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="760" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F760" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="761" spans="6:6" x14ac:dyDescent="0.35">
       <c r="F761" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="762" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F762" s="2" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="762" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F762" t="s">
+    <row r="763" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F763" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="763" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F763" s="2" t="s">
+    <row r="764" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F764" s="2" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="767" spans="6:6" ht="21" x14ac:dyDescent="0.5">
-      <c r="F767" s="51" t="s">
+    <row r="768" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F768" s="51" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="769" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F769" s="2" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="768" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F768" s="2" t="s">
-        <v>701</v>
+    <row r="770" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F770" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="771" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F771" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="772" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F772" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="773" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F773" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="774" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F774" s="2" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="775" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F775" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="776" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F776" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="777" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F777" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="778" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F778" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="779" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F779" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="780" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F780" s="2" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="781" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F781" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="782" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F782" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="783" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F783" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="784" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F784" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="785" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F785" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="786" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F786" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="787" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F787" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="788" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F788" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="789" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F789" s="2" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="790" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F790" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="791" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F791" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="792" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F792" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="793" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F793" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="794" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F794" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="795" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F795" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="796" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F796" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="797" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F797" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="798" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F798" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="799" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F799" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="800" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F800" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="801" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F801" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="802" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F802" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="803" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F803" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="804" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F804" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="805" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F805" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="806" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F806" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="807" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F807" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="808" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F808" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="809" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F809" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="810" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F810" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="811" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F811" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="812" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F812" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="813" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F813" s="2" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="814" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F814" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="815" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F815" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="816" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F816" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="817" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F817" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="818" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F818" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="819" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F819" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="820" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F820" s="2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="824" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F824" s="15" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="825" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F825" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="826" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F826" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="827" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F827" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="828" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F828" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="829" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F829" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="830" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F830" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="831" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F831" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="832" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F832" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="833" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F833" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="834" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F834" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="835" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F835" s="2" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="836" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F836" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="837" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F837" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="838" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F838" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="839" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F839" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="840" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F840" s="2" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="841" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F841" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="842" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F842" s="2" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="843" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F843" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="844" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F844" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="845" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F845" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="846" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F846" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="847" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F847" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="849" spans="6:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="F849" s="15" t="s">
+        <v>780</v>
       </c>
     </row>
   </sheetData>
